--- a/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
+++ b/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rmhc\front_0624\docs\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B4B1EEF7-7F04-48BA-B290-E864A4274275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F7AC6E88-C3ED-44F5-9C07-71DD3828AA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71100" yWindow="165" windowWidth="43980" windowHeight="29370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67740" yWindow="390" windowWidth="43980" windowHeight="29370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="5" r:id="rId1"/>
@@ -10966,31 +10966,31 @@
       <c r="L53" s="61"/>
     </row>
     <row r="54" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B54" s="53">
+      <c r="B54" s="132">
         <v>50</v>
       </c>
-      <c r="C54" s="99"/>
-      <c r="D54" s="65" t="s">
+      <c r="C54" s="138"/>
+      <c r="D54" s="139" t="s">
         <v>395</v>
       </c>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61" t="s">
+      <c r="E54" s="133"/>
+      <c r="F54" s="133"/>
+      <c r="G54" s="133" t="s">
         <v>395</v>
       </c>
-      <c r="H54" s="58" t="s">
+      <c r="H54" s="136" t="s">
         <v>393</v>
       </c>
-      <c r="I54" s="70" t="s">
+      <c r="I54" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="J54" s="68" t="s">
+      <c r="J54" s="137" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="61" t="s">
+      <c r="K54" s="133" t="s">
         <v>394</v>
       </c>
-      <c r="L54" s="61" t="s">
+      <c r="L54" s="133" t="s">
         <v>392</v>
       </c>
     </row>

--- a/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
+++ b/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rmhc\front_0624\docs\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F7AC6E88-C3ED-44F5-9C07-71DD3828AA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E90D1B7-DC0E-4FDA-ABDC-CC2B352653D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67740" yWindow="390" windowWidth="43980" windowHeight="29370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="840" windowWidth="42210" windowHeight="26775" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,6 @@
     <definedName name="일정표기준">[1]MasterSchedule!$AK$43:$AK$44</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3432,7 +3431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3723,18 +3722,12 @@
     <xf numFmtId="0" fontId="28" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3918,11 +3911,74 @@
     <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3935,69 +3991,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4427,42 +4420,42 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="157" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="159"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="159"/>
-      <c r="E5" s="159"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
-      <c r="I5" s="159"/>
-      <c r="J5" s="159"/>
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="160"/>
-      <c r="B6" s="160"/>
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="160"/>
+      <c r="A6" s="158"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="158"/>
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="161"/>
-      <c r="B7" s="161"/>
-      <c r="C7" s="161"/>
-      <c r="D7" s="161"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="159"/>
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="5"/>
@@ -4813,32 +4806,32 @@
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
-      <c r="A37" s="162">
+      <c r="A37" s="160">
         <v>46118</v>
       </c>
-      <c r="B37" s="162"/>
-      <c r="C37" s="162"/>
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="160"/>
+      <c r="J37" s="160"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="162" t="s">
+      <c r="A38" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="162"/>
-      <c r="C38" s="162"/>
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
+      <c r="B38" s="160"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
+      <c r="J38" s="160"/>
     </row>
     <row r="39" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="5"/>
@@ -4865,52 +4858,52 @@
       <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="158"/>
-      <c r="B41" s="158"/>
-      <c r="C41" s="158"/>
-      <c r="D41" s="158"/>
-      <c r="E41" s="158"/>
-      <c r="F41" s="158"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="158"/>
-      <c r="J41" s="158"/>
+      <c r="A41" s="156"/>
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="156"/>
+      <c r="I41" s="156"/>
+      <c r="J41" s="156"/>
     </row>
     <row r="42" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="158"/>
-      <c r="B42" s="158"/>
-      <c r="C42" s="158"/>
-      <c r="D42" s="158"/>
-      <c r="E42" s="158"/>
-      <c r="F42" s="158"/>
-      <c r="G42" s="158"/>
-      <c r="H42" s="158"/>
-      <c r="I42" s="158"/>
-      <c r="J42" s="158"/>
+      <c r="A42" s="156"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="156"/>
+      <c r="D42" s="156"/>
+      <c r="E42" s="156"/>
+      <c r="F42" s="156"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="156"/>
+      <c r="I42" s="156"/>
+      <c r="J42" s="156"/>
     </row>
     <row r="43" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="158"/>
-      <c r="B43" s="158"/>
-      <c r="C43" s="158"/>
-      <c r="D43" s="158"/>
-      <c r="E43" s="158"/>
-      <c r="F43" s="158"/>
-      <c r="G43" s="158"/>
-      <c r="H43" s="158"/>
-      <c r="I43" s="158"/>
-      <c r="J43" s="158"/>
+      <c r="A43" s="156"/>
+      <c r="B43" s="156"/>
+      <c r="C43" s="156"/>
+      <c r="D43" s="156"/>
+      <c r="E43" s="156"/>
+      <c r="F43" s="156"/>
+      <c r="G43" s="156"/>
+      <c r="H43" s="156"/>
+      <c r="I43" s="156"/>
+      <c r="J43" s="156"/>
     </row>
     <row r="44" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="158"/>
-      <c r="B44" s="158"/>
-      <c r="C44" s="158"/>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="158"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="158"/>
-      <c r="I44" s="158"/>
-      <c r="J44" s="158"/>
+      <c r="A44" s="156"/>
+      <c r="B44" s="156"/>
+      <c r="C44" s="156"/>
+      <c r="D44" s="156"/>
+      <c r="E44" s="156"/>
+      <c r="F44" s="156"/>
+      <c r="G44" s="156"/>
+      <c r="H44" s="156"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="156"/>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
       <c r="A45" s="7"/>
@@ -4960,37 +4953,37 @@
   <sheetData>
     <row r="1" spans="2:10"/>
     <row r="2" spans="2:10">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="174"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="173"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="175"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="177"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="177" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="179"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="14" t="s">
         <v>3</v>
       </c>
@@ -4998,20 +4991,20 @@
       <c r="G4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="180" t="s">
+      <c r="H4" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="180"/>
-      <c r="J4" s="181"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="180"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="182" t="s">
+      <c r="C5" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="182"/>
+      <c r="D5" s="181"/>
       <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
@@ -5021,24 +5014,24 @@
       <c r="G5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="183" t="s">
+      <c r="H5" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="183"/>
     </row>
     <row r="6" spans="2:10" ht="56.1" customHeight="1">
-      <c r="B6" s="165" t="s">
+      <c r="B6" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="165"/>
-      <c r="J6" s="165"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="20" t="s">
@@ -5047,18 +5040,18 @@
       <c r="C7" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="166" t="s">
+      <c r="D7" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="166"/>
-      <c r="F7" s="167" t="s">
+      <c r="E7" s="185"/>
+      <c r="F7" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="168"/>
-      <c r="H7" s="166" t="s">
+      <c r="G7" s="187"/>
+      <c r="H7" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="166"/>
+      <c r="I7" s="185"/>
       <c r="J7" s="22" t="s">
         <v>17</v>
       </c>
@@ -5070,18 +5063,18 @@
       <c r="C8" s="43">
         <v>46118</v>
       </c>
-      <c r="D8" s="164" t="s">
+      <c r="D8" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="164"/>
-      <c r="F8" s="163" t="s">
+      <c r="E8" s="168"/>
+      <c r="F8" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="163"/>
-      <c r="H8" s="169" t="s">
+      <c r="G8" s="169"/>
+      <c r="H8" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="170"/>
+      <c r="I8" s="164"/>
       <c r="J8" s="25"/>
     </row>
     <row r="9" spans="2:10" ht="18.75" customHeight="1">
@@ -5089,23 +5082,23 @@
       <c r="C9" s="43">
         <v>46178</v>
       </c>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="163" t="s">
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="169" t="s">
         <v>633</v>
       </c>
-      <c r="G9" s="163"/>
-      <c r="H9" s="169"/>
-      <c r="I9" s="170"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="163"/>
+      <c r="I9" s="164"/>
       <c r="J9" s="26"/>
     </row>
     <row r="10" spans="2:10" ht="18.75" customHeight="1">
       <c r="B10" s="23"/>
       <c r="C10" s="43"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="171"/>
-      <c r="G10" s="163"/>
+      <c r="D10" s="168"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="169"/>
       <c r="H10" s="49"/>
       <c r="I10" s="50"/>
       <c r="J10" s="26"/>
@@ -5113,10 +5106,10 @@
     <row r="11" spans="2:10" ht="18.75" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="43"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="163"/>
-      <c r="G11" s="163"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="168"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="169"/>
       <c r="H11" s="49"/>
       <c r="I11" s="50"/>
       <c r="J11" s="26"/>
@@ -5124,10 +5117,10 @@
     <row r="12" spans="2:10" ht="18.75" customHeight="1">
       <c r="B12" s="23"/>
       <c r="C12" s="43"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
       <c r="H12" s="49"/>
       <c r="I12" s="50"/>
       <c r="J12" s="26"/>
@@ -5135,63 +5128,63 @@
     <row r="13" spans="2:10" ht="18.75" customHeight="1">
       <c r="B13" s="23"/>
       <c r="C13" s="43"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="171"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="170"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="163"/>
+      <c r="I13" s="164"/>
       <c r="J13" s="26"/>
     </row>
     <row r="14" spans="2:10" ht="18.75" customHeight="1">
       <c r="B14" s="23"/>
       <c r="C14" s="43"/>
-      <c r="F14" s="163"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="170"/>
+      <c r="F14" s="169"/>
+      <c r="G14" s="169"/>
+      <c r="H14" s="163"/>
+      <c r="I14" s="164"/>
       <c r="J14" s="26"/>
     </row>
     <row r="15" spans="2:10" ht="18.75" customHeight="1">
       <c r="B15" s="23"/>
       <c r="C15" s="43"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="164"/>
-      <c r="F15" s="163"/>
-      <c r="G15" s="163"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="170"/>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="169"/>
+      <c r="H15" s="163"/>
+      <c r="I15" s="164"/>
       <c r="J15" s="26"/>
     </row>
     <row r="16" spans="2:10" ht="18.75" customHeight="1">
       <c r="B16" s="23"/>
       <c r="C16" s="43"/>
-      <c r="D16" s="164"/>
-      <c r="E16" s="164"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="170"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="163"/>
+      <c r="I16" s="164"/>
       <c r="J16" s="26"/>
     </row>
     <row r="17" spans="2:10" ht="18.75" customHeight="1">
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="164"/>
-      <c r="E17" s="164"/>
-      <c r="F17" s="163"/>
-      <c r="G17" s="163"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="170"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="169"/>
+      <c r="H17" s="163"/>
+      <c r="I17" s="164"/>
       <c r="J17" s="26"/>
     </row>
     <row r="18" spans="2:10" ht="18.75" customHeight="1">
       <c r="B18" s="23"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="163"/>
-      <c r="G18" s="163"/>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="169"/>
+      <c r="G18" s="169"/>
       <c r="H18" s="49"/>
       <c r="I18" s="50"/>
       <c r="J18" s="26"/>
@@ -5199,10 +5192,10 @@
     <row r="19" spans="2:10" ht="18.75" customHeight="1">
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="163"/>
-      <c r="G19" s="163"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="169"/>
       <c r="H19" s="49"/>
       <c r="I19" s="50"/>
       <c r="J19" s="26"/>
@@ -5210,10 +5203,10 @@
     <row r="20" spans="2:10" ht="18.75" customHeight="1">
       <c r="B20" s="23"/>
       <c r="C20" s="24"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="163"/>
-      <c r="G20" s="163"/>
+      <c r="D20" s="168"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="169"/>
       <c r="H20" s="49"/>
       <c r="I20" s="50"/>
       <c r="J20" s="26"/>
@@ -5221,8 +5214,8 @@
     <row r="21" spans="2:10" ht="18.75" customHeight="1">
       <c r="B21" s="23"/>
       <c r="C21" s="24"/>
-      <c r="F21" s="163"/>
-      <c r="G21" s="163"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
       <c r="H21" s="49"/>
       <c r="I21" s="50"/>
       <c r="J21" s="26"/>
@@ -5230,10 +5223,10 @@
     <row r="22" spans="2:10" ht="18.75" customHeight="1">
       <c r="B22" s="23"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="163"/>
-      <c r="G22" s="163"/>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="169"/>
       <c r="H22" s="49"/>
       <c r="I22" s="50"/>
       <c r="J22" s="26"/>
@@ -5241,10 +5234,10 @@
     <row r="23" spans="2:10" ht="18.75" customHeight="1">
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="163"/>
-      <c r="G23" s="163"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
       <c r="H23" s="49"/>
       <c r="I23" s="50"/>
       <c r="J23" s="26"/>
@@ -5252,92 +5245,92 @@
     <row r="24" spans="2:10" ht="18.75" customHeight="1">
       <c r="B24" s="23"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="163"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="170"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="169"/>
+      <c r="H24" s="163"/>
+      <c r="I24" s="164"/>
       <c r="J24" s="26"/>
     </row>
     <row r="25" spans="2:10" ht="18.75" customHeight="1">
       <c r="B25" s="23"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="164"/>
-      <c r="E25" s="164"/>
-      <c r="F25" s="163"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="170"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="163"/>
+      <c r="I25" s="164"/>
       <c r="J25" s="26"/>
     </row>
     <row r="26" spans="2:10" ht="18.75" customHeight="1">
       <c r="B26" s="23"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="163"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="170"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="163"/>
+      <c r="I26" s="164"/>
       <c r="J26" s="26"/>
     </row>
     <row r="27" spans="2:10" ht="18.75" customHeight="1">
       <c r="B27" s="23"/>
       <c r="C27" s="24"/>
-      <c r="D27" s="164"/>
-      <c r="E27" s="164"/>
-      <c r="F27" s="163"/>
-      <c r="G27" s="163"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="170"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="169"/>
+      <c r="G27" s="169"/>
+      <c r="H27" s="163"/>
+      <c r="I27" s="164"/>
       <c r="J27" s="26"/>
     </row>
     <row r="28" spans="2:10" ht="18.75" customHeight="1">
       <c r="B28" s="23"/>
       <c r="C28" s="24"/>
-      <c r="D28" s="164"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="163"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="170"/>
+      <c r="D28" s="168"/>
+      <c r="E28" s="168"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="169"/>
+      <c r="H28" s="163"/>
+      <c r="I28" s="164"/>
       <c r="J28" s="26"/>
     </row>
     <row r="29" spans="2:10" ht="18.75" customHeight="1">
       <c r="B29" s="23"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="164"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="163"/>
-      <c r="G29" s="163"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="170"/>
+      <c r="D29" s="168"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="169"/>
+      <c r="H29" s="163"/>
+      <c r="I29" s="164"/>
       <c r="J29" s="26"/>
     </row>
     <row r="30" spans="2:10" ht="18.75" customHeight="1">
       <c r="B30" s="27"/>
       <c r="C30" s="28"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="186"/>
-      <c r="G30" s="186"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="170"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="163"/>
+      <c r="I30" s="164"/>
       <c r="J30" s="29"/>
     </row>
     <row r="31" spans="2:10" ht="76.5" customHeight="1">
-      <c r="B31" s="187" t="s">
+      <c r="B31" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="188"/>
-      <c r="D31" s="188"/>
-      <c r="E31" s="188"/>
-      <c r="F31" s="188"/>
-      <c r="G31" s="188"/>
-      <c r="H31" s="188"/>
-      <c r="I31" s="188"/>
-      <c r="J31" s="189"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="167"/>
     </row>
     <row r="32" spans="2:10">
       <c r="B32" s="30"/>
@@ -5502,22 +5495,42 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
@@ -5534,42 +5547,22 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B2:J3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5600,17 +5593,17 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="155" t="s">
         <v>256</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -7370,17 +7363,17 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="155" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -8792,15 +8785,15 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:9" ht="33.75" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="155" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
     </row>
     <row r="3" spans="2:9" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -9566,18 +9559,18 @@
       <c r="F1" s="44"/>
     </row>
     <row r="2" spans="2:14" ht="33.75" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="155" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
     </row>
     <row r="3" spans="2:14" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -9622,292 +9615,292 @@
       </c>
     </row>
     <row r="5" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B5" s="53">
+      <c r="B5" s="130">
         <v>1</v>
       </c>
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="61"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58" t="s">
+      <c r="D5" s="131"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134" t="s">
         <v>280</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="134" t="s">
         <v>281</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58" t="s">
+      <c r="K5" s="134"/>
+      <c r="L5" s="134" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B6" s="53">
+      <c r="B6" s="130">
         <v>2</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="61" t="s">
+      <c r="C6" s="136"/>
+      <c r="D6" s="131" t="s">
         <v>376</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="58" t="s">
+      <c r="E6" s="132"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="134" t="s">
         <v>377</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="134" t="s">
         <v>378</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="135" t="s">
         <v>372</v>
       </c>
-      <c r="J6" s="68" t="s">
+      <c r="J6" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="K6" s="134" t="s">
         <v>379</v>
       </c>
-      <c r="L6" s="58"/>
+      <c r="L6" s="134"/>
     </row>
     <row r="7" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B7" s="132">
+      <c r="B7" s="130">
         <v>3</v>
       </c>
-      <c r="C7" s="133" t="s">
+      <c r="C7" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="134"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="136" t="s">
+      <c r="D7" s="132"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="136" t="s">
+      <c r="H7" s="134" t="s">
         <v>282</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="137" t="s">
+      <c r="J7" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="136" t="s">
+      <c r="K7" s="134" t="s">
         <v>259</v>
       </c>
-      <c r="L7" s="136" t="s">
+      <c r="L7" s="134" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B8" s="132">
+      <c r="B8" s="130">
         <v>4</v>
       </c>
-      <c r="C8" s="138"/>
-      <c r="D8" s="133" t="s">
+      <c r="C8" s="136"/>
+      <c r="D8" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="135" t="s">
+      <c r="E8" s="133" t="s">
         <v>267</v>
       </c>
-      <c r="F8" s="135"/>
-      <c r="G8" s="136" t="s">
+      <c r="F8" s="133"/>
+      <c r="G8" s="134" t="s">
         <v>283</v>
       </c>
-      <c r="H8" s="136" t="s">
+      <c r="H8" s="134" t="s">
         <v>285</v>
       </c>
-      <c r="I8" s="137" t="s">
+      <c r="I8" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="137" t="s">
+      <c r="J8" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K8" s="136" t="s">
+      <c r="K8" s="134" t="s">
         <v>264</v>
       </c>
-      <c r="L8" s="136" t="s">
+      <c r="L8" s="134" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B9" s="132">
+      <c r="B9" s="130">
         <v>5</v>
       </c>
-      <c r="C9" s="138"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="135" t="s">
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="133" t="s">
         <v>263</v>
       </c>
-      <c r="F9" s="135"/>
-      <c r="G9" s="136" t="s">
+      <c r="F9" s="133"/>
+      <c r="G9" s="134" t="s">
         <v>284</v>
       </c>
-      <c r="H9" s="136" t="s">
+      <c r="H9" s="134" t="s">
         <v>286</v>
       </c>
-      <c r="I9" s="137" t="s">
+      <c r="I9" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="137" t="s">
+      <c r="J9" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="136" t="s">
+      <c r="K9" s="134" t="s">
         <v>265</v>
       </c>
-      <c r="L9" s="136" t="s">
+      <c r="L9" s="134" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="10" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B10" s="132">
+      <c r="B10" s="130">
         <v>6</v>
       </c>
-      <c r="C10" s="138"/>
-      <c r="D10" s="133" t="s">
+      <c r="C10" s="136"/>
+      <c r="D10" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="135" t="s">
+      <c r="E10" s="133" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="135"/>
-      <c r="G10" s="136" t="s">
+      <c r="F10" s="133"/>
+      <c r="G10" s="134" t="s">
         <v>287</v>
       </c>
-      <c r="H10" s="136" t="s">
+      <c r="H10" s="134" t="s">
         <v>288</v>
       </c>
-      <c r="I10" s="137" t="s">
+      <c r="I10" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="137" t="s">
+      <c r="J10" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="136" t="s">
+      <c r="K10" s="134" t="s">
         <v>277</v>
       </c>
-      <c r="L10" s="136" t="s">
+      <c r="L10" s="134" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B11" s="132">
+      <c r="B11" s="130">
         <v>7</v>
       </c>
-      <c r="C11" s="138"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="135" t="s">
+      <c r="C11" s="136"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="133" t="s">
         <v>269</v>
       </c>
-      <c r="F11" s="135"/>
-      <c r="G11" s="136" t="s">
+      <c r="F11" s="133"/>
+      <c r="G11" s="134" t="s">
         <v>289</v>
       </c>
-      <c r="H11" s="136" t="s">
+      <c r="H11" s="134" t="s">
         <v>292</v>
       </c>
-      <c r="I11" s="137" t="s">
+      <c r="I11" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="137" t="s">
+      <c r="J11" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136" t="s">
+      <c r="K11" s="134"/>
+      <c r="L11" s="134" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="12" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B12" s="132">
+      <c r="B12" s="130">
         <v>8</v>
       </c>
-      <c r="C12" s="138"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="135" t="s">
+      <c r="C12" s="136"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="133" t="s">
         <v>270</v>
       </c>
-      <c r="F12" s="135"/>
-      <c r="G12" s="136" t="s">
+      <c r="F12" s="133"/>
+      <c r="G12" s="134" t="s">
         <v>290</v>
       </c>
-      <c r="H12" s="136" t="s">
+      <c r="H12" s="134" t="s">
         <v>291</v>
       </c>
-      <c r="I12" s="137" t="s">
+      <c r="I12" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="137" t="s">
+      <c r="J12" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="136"/>
-      <c r="L12" s="136" t="s">
+      <c r="K12" s="134"/>
+      <c r="L12" s="134" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="13" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B13" s="132">
+      <c r="B13" s="130">
         <v>9</v>
       </c>
-      <c r="C13" s="138"/>
-      <c r="D13" s="136" t="s">
+      <c r="C13" s="136"/>
+      <c r="D13" s="134" t="s">
         <v>370</v>
       </c>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="136" t="s">
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="134" t="s">
         <v>371</v>
       </c>
-      <c r="H13" s="136" t="s">
+      <c r="H13" s="134" t="s">
         <v>375</v>
       </c>
-      <c r="I13" s="137" t="s">
+      <c r="I13" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="137" t="s">
+      <c r="J13" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="136" t="s">
+      <c r="K13" s="134" t="s">
         <v>373</v>
       </c>
-      <c r="L13" s="136" t="s">
+      <c r="L13" s="134" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="14" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B14" s="132">
+      <c r="B14" s="130">
         <v>10</v>
       </c>
-      <c r="C14" s="133" t="s">
+      <c r="C14" s="131" t="s">
         <v>580</v>
       </c>
-      <c r="D14" s="135" t="s">
+      <c r="D14" s="133" t="s">
         <v>599</v>
       </c>
-      <c r="E14" s="133" t="s">
+      <c r="E14" s="131" t="s">
         <v>589</v>
       </c>
-      <c r="F14" s="135"/>
-      <c r="G14" s="136" t="s">
+      <c r="F14" s="133"/>
+      <c r="G14" s="134" t="s">
         <v>588</v>
       </c>
-      <c r="H14" s="136" t="s">
+      <c r="H14" s="134" t="s">
         <v>581</v>
       </c>
-      <c r="I14" s="137" t="s">
+      <c r="I14" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="137" t="s">
+      <c r="J14" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="136" t="s">
+      <c r="K14" s="134" t="s">
         <v>583</v>
       </c>
-      <c r="L14" s="136" t="s">
+      <c r="L14" s="134" t="s">
         <v>582</v>
       </c>
       <c r="N14" s="60" t="s">
@@ -9915,1188 +9908,1188 @@
       </c>
     </row>
     <row r="15" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B15" s="132">
+      <c r="B15" s="130">
         <v>11</v>
       </c>
-      <c r="C15" s="139"/>
-      <c r="D15" s="134" t="s">
+      <c r="C15" s="137"/>
+      <c r="D15" s="132" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136" t="s">
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134" t="s">
         <v>344</v>
       </c>
-      <c r="I15" s="137" t="s">
+      <c r="I15" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="137" t="s">
+      <c r="J15" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="136" t="s">
+      <c r="K15" s="134" t="s">
         <v>584</v>
       </c>
-      <c r="L15" s="136"/>
+      <c r="L15" s="134"/>
     </row>
     <row r="16" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B16" s="132">
+      <c r="B16" s="130">
         <v>12</v>
       </c>
-      <c r="C16" s="139"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="135" t="s">
+      <c r="C16" s="137"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="F16" s="135"/>
-      <c r="G16" s="136" t="s">
+      <c r="F16" s="133"/>
+      <c r="G16" s="134" t="s">
         <v>389</v>
       </c>
-      <c r="H16" s="136" t="s">
+      <c r="H16" s="134" t="s">
         <v>459</v>
       </c>
-      <c r="I16" s="137" t="s">
+      <c r="I16" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="137" t="s">
+      <c r="J16" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K16" s="136" t="s">
+      <c r="K16" s="134" t="s">
         <v>585</v>
       </c>
-      <c r="L16" s="136"/>
+      <c r="L16" s="134"/>
     </row>
     <row r="17" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B17" s="132">
+      <c r="B17" s="130">
         <v>13</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="135" t="s">
+      <c r="C17" s="141"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="F17" s="135"/>
-      <c r="G17" s="136" t="s">
+      <c r="F17" s="133"/>
+      <c r="G17" s="134" t="s">
         <v>388</v>
       </c>
-      <c r="H17" s="136" t="s">
+      <c r="H17" s="134" t="s">
         <v>460</v>
       </c>
-      <c r="I17" s="137" t="s">
+      <c r="I17" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="137" t="s">
+      <c r="J17" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="136" t="s">
+      <c r="K17" s="134" t="s">
         <v>586</v>
       </c>
-      <c r="L17" s="136"/>
+      <c r="L17" s="134"/>
       <c r="N17" s="60" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="18" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B18" s="132">
+      <c r="B18" s="130">
         <v>14</v>
       </c>
-      <c r="C18" s="139" t="s">
+      <c r="C18" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="139"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="136" t="s">
+      <c r="D18" s="137"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="136" t="s">
+      <c r="H18" s="134" t="s">
         <v>293</v>
       </c>
-      <c r="I18" s="137" t="s">
+      <c r="I18" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="137" t="s">
+      <c r="J18" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="136" t="s">
+      <c r="K18" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="L18" s="136" t="s">
+      <c r="L18" s="134" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B19" s="132">
+      <c r="B19" s="130">
         <v>15</v>
       </c>
-      <c r="C19" s="138"/>
-      <c r="D19" s="133" t="s">
+      <c r="C19" s="136"/>
+      <c r="D19" s="131" t="s">
         <v>278</v>
       </c>
-      <c r="E19" s="135" t="s">
+      <c r="E19" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="F19" s="135"/>
-      <c r="G19" s="136" t="s">
+      <c r="F19" s="133"/>
+      <c r="G19" s="134" t="s">
         <v>295</v>
       </c>
-      <c r="H19" s="136" t="s">
+      <c r="H19" s="134" t="s">
         <v>296</v>
       </c>
-      <c r="I19" s="137" t="s">
+      <c r="I19" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="137" t="s">
+      <c r="J19" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="136" t="s">
+      <c r="K19" s="134" t="s">
         <v>277</v>
       </c>
-      <c r="L19" s="136" t="s">
+      <c r="L19" s="134" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="20" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B20" s="132">
+      <c r="B20" s="130">
         <v>16</v>
       </c>
-      <c r="C20" s="138"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="146" t="s">
+      <c r="C20" s="136"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="144" t="s">
         <v>274</v>
       </c>
-      <c r="F20" s="146"/>
-      <c r="G20" s="147" t="s">
+      <c r="F20" s="144"/>
+      <c r="G20" s="145" t="s">
         <v>297</v>
       </c>
-      <c r="H20" s="136" t="s">
+      <c r="H20" s="134" t="s">
         <v>298</v>
       </c>
-      <c r="I20" s="137" t="s">
+      <c r="I20" s="135" t="s">
         <v>382</v>
       </c>
-      <c r="J20" s="137" t="s">
+      <c r="J20" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="136" t="s">
+      <c r="K20" s="134" t="s">
         <v>380</v>
       </c>
-      <c r="L20" s="136" t="s">
+      <c r="L20" s="134" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="21" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B21" s="132">
+      <c r="B21" s="130">
         <v>17</v>
       </c>
-      <c r="C21" s="138"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="146" t="s">
+      <c r="C21" s="136"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="144" t="s">
         <v>381</v>
       </c>
-      <c r="F21" s="146"/>
-      <c r="G21" s="148" t="s">
+      <c r="F21" s="144"/>
+      <c r="G21" s="146" t="s">
         <v>294</v>
       </c>
-      <c r="H21" s="149" t="s">
+      <c r="H21" s="147" t="s">
         <v>300</v>
       </c>
-      <c r="I21" s="137" t="s">
+      <c r="I21" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="137" t="s">
+      <c r="J21" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="136" t="s">
+      <c r="K21" s="134" t="s">
         <v>461</v>
       </c>
-      <c r="L21" s="136" t="s">
+      <c r="L21" s="134" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="22" spans="2:14" s="60" customFormat="1" ht="43.5" customHeight="1">
-      <c r="B22" s="132">
+      <c r="B22" s="130">
         <v>18</v>
       </c>
-      <c r="C22" s="133" t="s">
+      <c r="C22" s="131" t="s">
         <v>279</v>
       </c>
-      <c r="D22" s="145"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="148" t="s">
+      <c r="D22" s="143"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="H22" s="136" t="s">
+      <c r="H22" s="134" t="s">
         <v>299</v>
       </c>
-      <c r="I22" s="137" t="s">
+      <c r="I22" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="137" t="s">
+      <c r="J22" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="136" t="s">
+      <c r="K22" s="134" t="s">
         <v>575</v>
       </c>
-      <c r="L22" s="136" t="s">
+      <c r="L22" s="134" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="23" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="132">
+      <c r="B23" s="130">
         <v>19</v>
       </c>
-      <c r="C23" s="138"/>
-      <c r="D23" s="133" t="s">
+      <c r="C23" s="136"/>
+      <c r="D23" s="131" t="s">
         <v>220</v>
       </c>
-      <c r="E23" s="135"/>
-      <c r="F23" s="135"/>
-      <c r="G23" s="136" t="s">
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="134" t="s">
         <v>362</v>
       </c>
-      <c r="H23" s="136" t="s">
+      <c r="H23" s="134" t="s">
         <v>455</v>
       </c>
-      <c r="I23" s="137" t="s">
+      <c r="I23" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="137" t="s">
+      <c r="J23" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="136" t="s">
+      <c r="K23" s="134" t="s">
         <v>576</v>
       </c>
-      <c r="L23" s="136" t="s">
+      <c r="L23" s="134" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="24" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B24" s="132">
+      <c r="B24" s="130">
         <v>20</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="135" t="s">
+      <c r="C24" s="136"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136" t="s">
+      <c r="F24" s="133"/>
+      <c r="G24" s="134" t="s">
         <v>180</v>
       </c>
-      <c r="H24" s="136" t="s">
+      <c r="H24" s="134" t="s">
         <v>457</v>
       </c>
-      <c r="I24" s="137" t="s">
+      <c r="I24" s="135" t="s">
         <v>454</v>
       </c>
-      <c r="J24" s="137" t="s">
+      <c r="J24" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="136"/>
-      <c r="L24" s="136" t="s">
+      <c r="K24" s="134"/>
+      <c r="L24" s="134" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B25" s="132">
+      <c r="B25" s="130">
         <v>21</v>
       </c>
-      <c r="C25" s="138"/>
-      <c r="D25" s="139" t="s">
+      <c r="C25" s="136"/>
+      <c r="D25" s="137" t="s">
         <v>453</v>
       </c>
-      <c r="E25" s="135" t="s">
+      <c r="E25" s="133" t="s">
         <v>346</v>
       </c>
-      <c r="F25" s="135"/>
-      <c r="G25" s="136" t="s">
+      <c r="F25" s="133"/>
+      <c r="G25" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="H25" s="136" t="s">
+      <c r="H25" s="134" t="s">
         <v>456</v>
       </c>
-      <c r="I25" s="137" t="s">
+      <c r="I25" s="135" t="s">
         <v>454</v>
       </c>
-      <c r="J25" s="137" t="s">
+      <c r="J25" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K25" s="136"/>
-      <c r="L25" s="136" t="s">
+      <c r="K25" s="134"/>
+      <c r="L25" s="134" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="26" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B26" s="132">
+      <c r="B26" s="130">
         <v>22</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="135" t="s">
+      <c r="C26" s="136"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="133" t="s">
         <v>347</v>
       </c>
-      <c r="F26" s="135"/>
-      <c r="G26" s="136" t="s">
+      <c r="F26" s="133"/>
+      <c r="G26" s="134" t="s">
         <v>364</v>
       </c>
-      <c r="H26" s="136" t="s">
+      <c r="H26" s="134" t="s">
         <v>458</v>
       </c>
-      <c r="I26" s="137" t="s">
+      <c r="I26" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="137" t="s">
+      <c r="J26" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K26" s="136" t="s">
+      <c r="K26" s="134" t="s">
         <v>577</v>
       </c>
-      <c r="L26" s="136" t="s">
+      <c r="L26" s="134" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="27" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B27" s="132">
+      <c r="B27" s="130">
         <v>23</v>
       </c>
-      <c r="C27" s="138"/>
-      <c r="D27" s="139" t="s">
+      <c r="C27" s="136"/>
+      <c r="D27" s="137" t="s">
         <v>462</v>
       </c>
-      <c r="E27" s="135" t="s">
+      <c r="E27" s="133" t="s">
         <v>463</v>
       </c>
-      <c r="F27" s="135"/>
-      <c r="G27" s="136" t="s">
+      <c r="F27" s="133"/>
+      <c r="G27" s="134" t="s">
         <v>465</v>
       </c>
-      <c r="H27" s="136" t="s">
+      <c r="H27" s="134" t="s">
         <v>468</v>
       </c>
-      <c r="I27" s="137" t="s">
+      <c r="I27" s="135" t="s">
         <v>372</v>
       </c>
-      <c r="J27" s="137" t="s">
+      <c r="J27" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K27" s="136" t="s">
+      <c r="K27" s="134" t="s">
         <v>467</v>
       </c>
-      <c r="L27" s="136"/>
+      <c r="L27" s="134"/>
     </row>
     <row r="28" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B28" s="132">
+      <c r="B28" s="130">
         <v>24</v>
       </c>
-      <c r="C28" s="138"/>
-      <c r="D28" s="143"/>
-      <c r="E28" s="135" t="s">
+      <c r="C28" s="136"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="133" t="s">
         <v>464</v>
       </c>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136" t="s">
+      <c r="F28" s="133"/>
+      <c r="G28" s="134" t="s">
         <v>466</v>
       </c>
-      <c r="H28" s="136" t="s">
+      <c r="H28" s="134" t="s">
         <v>469</v>
       </c>
-      <c r="I28" s="137" t="s">
+      <c r="I28" s="135" t="s">
         <v>372</v>
       </c>
-      <c r="J28" s="137" t="s">
+      <c r="J28" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="136" t="s">
+      <c r="K28" s="134" t="s">
         <v>467</v>
       </c>
-      <c r="L28" s="136"/>
+      <c r="L28" s="134"/>
     </row>
     <row r="29" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B29" s="132">
+      <c r="B29" s="130">
         <v>25</v>
       </c>
-      <c r="C29" s="139"/>
-      <c r="D29" s="146" t="s">
+      <c r="C29" s="137"/>
+      <c r="D29" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="135"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="136" t="s">
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="134" t="s">
         <v>360</v>
       </c>
-      <c r="H29" s="136" t="s">
+      <c r="H29" s="134" t="s">
         <v>342</v>
       </c>
-      <c r="I29" s="137" t="s">
+      <c r="I29" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="137" t="s">
+      <c r="J29" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K29" s="136" t="s">
+      <c r="K29" s="134" t="s">
         <v>222</v>
       </c>
-      <c r="L29" s="136" t="s">
+      <c r="L29" s="134" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="30" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B30" s="132">
+      <c r="B30" s="130">
         <v>26</v>
       </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="135" t="s">
+      <c r="C30" s="137"/>
+      <c r="D30" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="136" t="s">
+      <c r="E30" s="133"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="134" t="s">
         <v>361</v>
       </c>
-      <c r="H30" s="136" t="s">
+      <c r="H30" s="134" t="s">
         <v>343</v>
       </c>
-      <c r="I30" s="137" t="s">
+      <c r="I30" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="137" t="s">
+      <c r="J30" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K30" s="150" t="s">
+      <c r="K30" s="148" t="s">
         <v>578</v>
       </c>
-      <c r="L30" s="136" t="s">
+      <c r="L30" s="134" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="0" hidden="1" customHeight="1">
-      <c r="B31" s="132">
+      <c r="B31" s="130">
         <v>27</v>
       </c>
-      <c r="C31" s="151"/>
-      <c r="D31" s="151"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="151"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="152"/>
-      <c r="K31" s="151"/>
-      <c r="L31" s="151"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="149"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="149"/>
     </row>
     <row r="32" spans="2:14" ht="0" hidden="1" customHeight="1">
-      <c r="B32" s="132">
+      <c r="B32" s="130">
         <v>28</v>
       </c>
-      <c r="C32" s="151"/>
-      <c r="D32" s="151"/>
-      <c r="E32" s="151"/>
-      <c r="F32" s="151"/>
-      <c r="G32" s="151"/>
-      <c r="H32" s="151"/>
-      <c r="I32" s="152"/>
-      <c r="J32" s="152"/>
-      <c r="K32" s="151"/>
-      <c r="L32" s="151"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="149"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="149"/>
+      <c r="L32" s="149"/>
     </row>
     <row r="33" spans="2:13" ht="0" hidden="1" customHeight="1">
-      <c r="B33" s="132">
+      <c r="B33" s="130">
         <v>29</v>
       </c>
-      <c r="C33" s="151"/>
-      <c r="D33" s="151"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="152"/>
-      <c r="J33" s="152"/>
-      <c r="K33" s="151"/>
-      <c r="L33" s="151"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="149"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="149"/>
     </row>
     <row r="34" spans="2:13" ht="0" hidden="1" customHeight="1">
-      <c r="B34" s="132">
+      <c r="B34" s="130">
         <v>30</v>
       </c>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="151"/>
-      <c r="H34" s="151"/>
-      <c r="I34" s="152"/>
-      <c r="J34" s="152"/>
-      <c r="K34" s="151"/>
-      <c r="L34" s="151"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
+      <c r="F34" s="149"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="149"/>
+      <c r="I34" s="150"/>
+      <c r="J34" s="150"/>
+      <c r="K34" s="149"/>
+      <c r="L34" s="149"/>
     </row>
     <row r="35" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="132">
+      <c r="B35" s="130">
         <v>31</v>
       </c>
-      <c r="C35" s="138"/>
-      <c r="D35" s="133" t="s">
+      <c r="C35" s="136"/>
+      <c r="D35" s="131" t="s">
         <v>219</v>
       </c>
-      <c r="E35" s="153" t="s">
+      <c r="E35" s="151" t="s">
         <v>630</v>
       </c>
-      <c r="F35" s="153"/>
-      <c r="G35" s="154" t="s">
+      <c r="F35" s="151"/>
+      <c r="G35" s="152" t="s">
         <v>629</v>
       </c>
-      <c r="H35" s="154" t="s">
+      <c r="H35" s="152" t="s">
         <v>344</v>
       </c>
-      <c r="I35" s="155" t="s">
+      <c r="I35" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="155" t="s">
+      <c r="J35" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="K35" s="154" t="s">
+      <c r="K35" s="152" t="s">
         <v>579</v>
       </c>
-      <c r="L35" s="154" t="s">
+      <c r="L35" s="152" t="s">
         <v>353</v>
       </c>
-      <c r="M35" s="116" t="s">
+      <c r="M35" s="114" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B36" s="132">
+      <c r="B36" s="130">
         <v>32</v>
       </c>
-      <c r="C36" s="138"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="135" t="s">
+      <c r="C36" s="136"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136" t="s">
+      <c r="F36" s="133"/>
+      <c r="G36" s="134" t="s">
         <v>389</v>
       </c>
-      <c r="H36" s="136" t="s">
+      <c r="H36" s="134" t="s">
         <v>459</v>
       </c>
-      <c r="I36" s="137" t="s">
+      <c r="I36" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="137" t="s">
+      <c r="J36" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K36" s="136"/>
-      <c r="L36" s="136" t="s">
+      <c r="K36" s="134"/>
+      <c r="L36" s="134" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="37" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B37" s="132">
+      <c r="B37" s="130">
         <v>33</v>
       </c>
-      <c r="C37" s="138"/>
-      <c r="D37" s="143"/>
-      <c r="E37" s="135" t="s">
+      <c r="C37" s="136"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="F37" s="135"/>
-      <c r="G37" s="136" t="s">
+      <c r="F37" s="133"/>
+      <c r="G37" s="134" t="s">
         <v>388</v>
       </c>
-      <c r="H37" s="136" t="s">
+      <c r="H37" s="134" t="s">
         <v>460</v>
       </c>
-      <c r="I37" s="137" t="s">
+      <c r="I37" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="137" t="s">
+      <c r="J37" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K37" s="136"/>
-      <c r="L37" s="136" t="s">
+      <c r="K37" s="134"/>
+      <c r="L37" s="134" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="38" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B38" s="53">
+      <c r="B38" s="130">
         <v>34</v>
       </c>
-      <c r="C38" s="101"/>
-      <c r="D38" s="76" t="s">
+      <c r="C38" s="141"/>
+      <c r="D38" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="58" t="s">
+      <c r="E38" s="133"/>
+      <c r="F38" s="133"/>
+      <c r="G38" s="134" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="58" t="s">
+      <c r="H38" s="134" t="s">
         <v>345</v>
       </c>
-      <c r="I38" s="68" t="s">
+      <c r="I38" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J38" s="68" t="s">
+      <c r="J38" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="K38" s="134" t="s">
         <v>587</v>
       </c>
-      <c r="L38" s="58" t="s">
+      <c r="L38" s="134" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B39" s="53">
+      <c r="B39" s="130">
         <v>35</v>
       </c>
-      <c r="C39" s="98" t="s">
+      <c r="C39" s="142" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="63" t="s">
+      <c r="D39" s="141" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58" t="s">
+      <c r="E39" s="134"/>
+      <c r="F39" s="134"/>
+      <c r="G39" s="134" t="s">
         <v>301</v>
       </c>
-      <c r="H39" s="58" t="s">
+      <c r="H39" s="134" t="s">
         <v>302</v>
       </c>
-      <c r="I39" s="68" t="s">
+      <c r="I39" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="68"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58" t="s">
+      <c r="J39" s="135"/>
+      <c r="K39" s="134"/>
+      <c r="L39" s="134" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B40" s="53">
+      <c r="B40" s="130">
         <v>36</v>
       </c>
-      <c r="C40" s="99"/>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="136"/>
+      <c r="D40" s="134" t="s">
         <v>44</v>
       </c>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58" t="s">
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="134" t="s">
         <v>303</v>
       </c>
-      <c r="H40" s="58" t="s">
+      <c r="H40" s="134" t="s">
         <v>304</v>
       </c>
-      <c r="I40" s="68" t="s">
+      <c r="I40" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J40" s="68"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58" t="s">
+      <c r="J40" s="135"/>
+      <c r="K40" s="134"/>
+      <c r="L40" s="134" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B41" s="53">
+      <c r="B41" s="130">
         <v>37</v>
       </c>
-      <c r="C41" s="99"/>
-      <c r="D41" s="58" t="s">
+      <c r="C41" s="136"/>
+      <c r="D41" s="134" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58" t="s">
+      <c r="E41" s="134"/>
+      <c r="F41" s="134"/>
+      <c r="G41" s="134" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="58" t="s">
+      <c r="H41" s="134" t="s">
         <v>305</v>
       </c>
-      <c r="I41" s="68" t="s">
+      <c r="I41" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J41" s="68"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58" t="s">
+      <c r="J41" s="135"/>
+      <c r="K41" s="134"/>
+      <c r="L41" s="134" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="42" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B42" s="53">
+      <c r="B42" s="130">
         <v>38</v>
       </c>
-      <c r="C42" s="99"/>
-      <c r="D42" s="58" t="s">
+      <c r="C42" s="136"/>
+      <c r="D42" s="134" t="s">
         <v>367</v>
       </c>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58" t="s">
+      <c r="E42" s="134"/>
+      <c r="F42" s="134"/>
+      <c r="G42" s="134" t="s">
         <v>368</v>
       </c>
-      <c r="H42" s="58" t="s">
+      <c r="H42" s="134" t="s">
         <v>306</v>
       </c>
-      <c r="I42" s="68" t="s">
+      <c r="I42" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="68"/>
-      <c r="K42" s="58" t="s">
+      <c r="J42" s="135"/>
+      <c r="K42" s="134" t="s">
         <v>369</v>
       </c>
-      <c r="L42" s="58" t="s">
+      <c r="L42" s="134" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="43" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B43" s="53">
+      <c r="B43" s="130">
         <v>39</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="58" t="s">
+      <c r="C43" s="136"/>
+      <c r="D43" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58" t="s">
+      <c r="E43" s="134"/>
+      <c r="F43" s="134"/>
+      <c r="G43" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="H43" s="58" t="s">
+      <c r="H43" s="134" t="s">
         <v>307</v>
       </c>
-      <c r="I43" s="68" t="s">
+      <c r="I43" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J43" s="68"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58" t="s">
+      <c r="J43" s="135"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="44" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B44" s="53">
+      <c r="B44" s="130">
         <v>40</v>
       </c>
-      <c r="C44" s="98" t="s">
+      <c r="C44" s="142" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="58" t="s">
+      <c r="D44" s="134" t="s">
         <v>470</v>
       </c>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58" t="s">
+      <c r="E44" s="134"/>
+      <c r="F44" s="134"/>
+      <c r="G44" s="134" t="s">
         <v>474</v>
       </c>
-      <c r="H44" s="58" t="s">
+      <c r="H44" s="134" t="s">
         <v>314</v>
       </c>
-      <c r="I44" s="68" t="s">
+      <c r="I44" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J44" s="68" t="s">
+      <c r="J44" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K44" s="58"/>
-      <c r="L44" s="58" t="s">
+      <c r="K44" s="134"/>
+      <c r="L44" s="134" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="45" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B45" s="132">
+      <c r="B45" s="130">
         <v>41</v>
       </c>
-      <c r="C45" s="138"/>
-      <c r="D45" s="136" t="s">
+      <c r="C45" s="136"/>
+      <c r="D45" s="134" t="s">
         <v>607</v>
       </c>
-      <c r="E45" s="136"/>
-      <c r="F45" s="136"/>
-      <c r="G45" s="136" t="s">
+      <c r="E45" s="134"/>
+      <c r="F45" s="134"/>
+      <c r="G45" s="134" t="s">
         <v>475</v>
       </c>
-      <c r="H45" s="136" t="s">
+      <c r="H45" s="134" t="s">
         <v>315</v>
       </c>
-      <c r="I45" s="137" t="s">
+      <c r="I45" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="137" t="s">
+      <c r="J45" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K45" s="136" t="s">
+      <c r="K45" s="134" t="s">
         <v>419</v>
       </c>
-      <c r="L45" s="136" t="s">
+      <c r="L45" s="134" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="46" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B46" s="132">
+      <c r="B46" s="130">
         <v>42</v>
       </c>
-      <c r="C46" s="138"/>
-      <c r="D46" s="136" t="s">
+      <c r="C46" s="136"/>
+      <c r="D46" s="134" t="s">
         <v>471</v>
       </c>
-      <c r="E46" s="136"/>
-      <c r="F46" s="136"/>
-      <c r="G46" s="136" t="s">
+      <c r="E46" s="134"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="134" t="s">
         <v>476</v>
       </c>
-      <c r="H46" s="136" t="s">
+      <c r="H46" s="134" t="s">
         <v>316</v>
       </c>
-      <c r="I46" s="137" t="s">
+      <c r="I46" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J46" s="137" t="s">
+      <c r="J46" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K46" s="136" t="s">
+      <c r="K46" s="134" t="s">
         <v>419</v>
       </c>
-      <c r="L46" s="136" t="s">
+      <c r="L46" s="134" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="47" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B47" s="132">
+      <c r="B47" s="130">
         <v>43</v>
       </c>
-      <c r="C47" s="138"/>
-      <c r="D47" s="133" t="s">
+      <c r="C47" s="136"/>
+      <c r="D47" s="131" t="s">
         <v>472</v>
       </c>
-      <c r="E47" s="136"/>
-      <c r="F47" s="136"/>
-      <c r="G47" s="136" t="s">
+      <c r="E47" s="134"/>
+      <c r="F47" s="134"/>
+      <c r="G47" s="134" t="s">
         <v>477</v>
       </c>
-      <c r="H47" s="136" t="s">
+      <c r="H47" s="134" t="s">
         <v>317</v>
       </c>
-      <c r="I47" s="137" t="s">
+      <c r="I47" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J47" s="137" t="s">
+      <c r="J47" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="136" t="s">
+      <c r="K47" s="134" t="s">
         <v>419</v>
       </c>
-      <c r="L47" s="136" t="s">
+      <c r="L47" s="134" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="48" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B48" s="132">
+      <c r="B48" s="130">
         <v>44</v>
       </c>
-      <c r="C48" s="138"/>
-      <c r="D48" s="133" t="s">
+      <c r="C48" s="136"/>
+      <c r="D48" s="131" t="s">
         <v>473</v>
       </c>
-      <c r="E48" s="136"/>
-      <c r="F48" s="136"/>
-      <c r="G48" s="136" t="s">
+      <c r="E48" s="134"/>
+      <c r="F48" s="134"/>
+      <c r="G48" s="134" t="s">
         <v>478</v>
       </c>
-      <c r="H48" s="136" t="s">
+      <c r="H48" s="134" t="s">
         <v>354</v>
       </c>
-      <c r="I48" s="137" t="s">
+      <c r="I48" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="137" t="s">
+      <c r="J48" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="136" t="s">
+      <c r="K48" s="134" t="s">
         <v>419</v>
       </c>
-      <c r="L48" s="136" t="s">
+      <c r="L48" s="134" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="49" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B49" s="132">
+      <c r="B49" s="130">
         <v>45</v>
       </c>
-      <c r="C49" s="144" t="s">
+      <c r="C49" s="142" t="s">
         <v>215</v>
       </c>
-      <c r="D49" s="136" t="s">
+      <c r="D49" s="134" t="s">
         <v>179</v>
       </c>
-      <c r="E49" s="135"/>
-      <c r="F49" s="135"/>
-      <c r="G49" s="136" t="s">
+      <c r="E49" s="133"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="134" t="s">
         <v>179</v>
       </c>
-      <c r="H49" s="136" t="s">
+      <c r="H49" s="134" t="s">
         <v>308</v>
       </c>
-      <c r="I49" s="137" t="s">
+      <c r="I49" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="137" t="s">
+      <c r="J49" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K49" s="136" t="s">
+      <c r="K49" s="134" t="s">
         <v>422</v>
       </c>
-      <c r="L49" s="136" t="s">
+      <c r="L49" s="134" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="50" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B50" s="132">
+      <c r="B50" s="130">
         <v>46</v>
       </c>
-      <c r="C50" s="138"/>
-      <c r="D50" s="136" t="s">
+      <c r="C50" s="136"/>
+      <c r="D50" s="134" t="s">
         <v>180</v>
       </c>
-      <c r="E50" s="135"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136" t="s">
+      <c r="E50" s="133"/>
+      <c r="F50" s="133"/>
+      <c r="G50" s="134" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="136" t="s">
+      <c r="H50" s="134" t="s">
         <v>309</v>
       </c>
-      <c r="I50" s="137" t="s">
+      <c r="I50" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J50" s="137" t="s">
+      <c r="J50" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K50" s="136" t="s">
+      <c r="K50" s="134" t="s">
         <v>422</v>
       </c>
-      <c r="L50" s="136"/>
+      <c r="L50" s="134"/>
     </row>
     <row r="51" spans="2:12" s="60" customFormat="1" ht="31.5" customHeight="1">
-      <c r="B51" s="53">
+      <c r="B51" s="130">
         <v>47</v>
       </c>
-      <c r="C51" s="99"/>
-      <c r="D51" s="61" t="s">
+      <c r="C51" s="136"/>
+      <c r="D51" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E51" s="62"/>
-      <c r="F51" s="62"/>
-      <c r="G51" s="58" t="s">
+      <c r="E51" s="133"/>
+      <c r="F51" s="133"/>
+      <c r="G51" s="134" t="s">
         <v>312</v>
       </c>
-      <c r="H51" s="58" t="s">
+      <c r="H51" s="134" t="s">
         <v>310</v>
       </c>
-      <c r="I51" s="68" t="s">
+      <c r="I51" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J51" s="68" t="s">
+      <c r="J51" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K51" s="58" t="s">
+      <c r="K51" s="134" t="s">
         <v>399</v>
       </c>
-      <c r="L51" s="58" t="s">
+      <c r="L51" s="134" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="52" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B52" s="53">
+      <c r="B52" s="130">
         <v>48</v>
       </c>
-      <c r="C52" s="99"/>
-      <c r="D52" s="61" t="s">
+      <c r="C52" s="136"/>
+      <c r="D52" s="131" t="s">
         <v>182</v>
       </c>
-      <c r="E52" s="75"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61" t="s">
+      <c r="E52" s="132"/>
+      <c r="F52" s="131"/>
+      <c r="G52" s="131" t="s">
         <v>313</v>
       </c>
-      <c r="H52" s="58" t="s">
+      <c r="H52" s="134" t="s">
         <v>311</v>
       </c>
-      <c r="I52" s="70" t="s">
+      <c r="I52" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J52" s="68" t="s">
+      <c r="J52" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K52" s="61" t="s">
+      <c r="K52" s="131" t="s">
         <v>405</v>
       </c>
-      <c r="L52" s="61" t="s">
+      <c r="L52" s="131" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="53" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B53" s="53">
+      <c r="B53" s="130">
         <v>49</v>
       </c>
-      <c r="C53" s="99"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="75" t="s">
+      <c r="C53" s="136"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="132" t="s">
         <v>400</v>
       </c>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61" t="s">
+      <c r="F53" s="131"/>
+      <c r="G53" s="131" t="s">
         <v>401</v>
       </c>
-      <c r="H53" s="58" t="s">
+      <c r="H53" s="134" t="s">
         <v>402</v>
       </c>
-      <c r="I53" s="70" t="s">
+      <c r="I53" s="154" t="s">
         <v>403</v>
       </c>
-      <c r="J53" s="68" t="s">
+      <c r="J53" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K53" s="61" t="s">
+      <c r="K53" s="131" t="s">
         <v>404</v>
       </c>
-      <c r="L53" s="61"/>
+      <c r="L53" s="131"/>
     </row>
     <row r="54" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B54" s="132">
+      <c r="B54" s="130">
         <v>50</v>
       </c>
-      <c r="C54" s="138"/>
-      <c r="D54" s="139" t="s">
+      <c r="C54" s="136"/>
+      <c r="D54" s="137" t="s">
         <v>395</v>
       </c>
-      <c r="E54" s="133"/>
-      <c r="F54" s="133"/>
-      <c r="G54" s="133" t="s">
+      <c r="E54" s="131"/>
+      <c r="F54" s="131"/>
+      <c r="G54" s="131" t="s">
         <v>395</v>
       </c>
-      <c r="H54" s="136" t="s">
+      <c r="H54" s="134" t="s">
         <v>393</v>
       </c>
-      <c r="I54" s="156" t="s">
+      <c r="I54" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J54" s="137" t="s">
+      <c r="J54" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="133" t="s">
+      <c r="K54" s="131" t="s">
         <v>394</v>
       </c>
-      <c r="L54" s="133" t="s">
+      <c r="L54" s="131" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="55" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B55" s="132">
+      <c r="B55" s="130">
         <v>51</v>
       </c>
-      <c r="C55" s="144" t="s">
+      <c r="C55" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="133" t="s">
+      <c r="D55" s="131" t="s">
         <v>185</v>
       </c>
-      <c r="E55" s="133"/>
-      <c r="F55" s="133"/>
-      <c r="G55" s="133" t="s">
+      <c r="E55" s="131"/>
+      <c r="F55" s="131"/>
+      <c r="G55" s="131" t="s">
         <v>318</v>
       </c>
-      <c r="H55" s="133" t="s">
+      <c r="H55" s="131" t="s">
         <v>321</v>
       </c>
-      <c r="I55" s="156" t="s">
+      <c r="I55" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J55" s="156"/>
-      <c r="K55" s="133"/>
-      <c r="L55" s="133" t="s">
+      <c r="J55" s="154"/>
+      <c r="K55" s="131"/>
+      <c r="L55" s="131" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="56" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B56" s="132">
+      <c r="B56" s="130">
         <v>52</v>
       </c>
-      <c r="C56" s="138"/>
-      <c r="D56" s="133" t="s">
+      <c r="C56" s="136"/>
+      <c r="D56" s="131" t="s">
         <v>187</v>
       </c>
-      <c r="E56" s="133"/>
-      <c r="F56" s="133"/>
-      <c r="G56" s="133" t="s">
+      <c r="E56" s="131"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="131" t="s">
         <v>319</v>
       </c>
-      <c r="H56" s="133" t="s">
+      <c r="H56" s="131" t="s">
         <v>322</v>
       </c>
-      <c r="I56" s="156" t="s">
+      <c r="I56" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J56" s="137" t="s">
+      <c r="J56" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K56" s="133" t="s">
+      <c r="K56" s="131" t="s">
         <v>366</v>
       </c>
-      <c r="L56" s="133" t="s">
+      <c r="L56" s="131" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="57" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B57" s="132">
+      <c r="B57" s="130">
         <v>53</v>
       </c>
-      <c r="C57" s="138"/>
-      <c r="D57" s="133" t="s">
+      <c r="C57" s="136"/>
+      <c r="D57" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="E57" s="133"/>
-      <c r="F57" s="133"/>
-      <c r="G57" s="133" t="s">
+      <c r="E57" s="131"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="131" t="s">
         <v>320</v>
       </c>
-      <c r="H57" s="133" t="s">
+      <c r="H57" s="131" t="s">
         <v>323</v>
       </c>
-      <c r="I57" s="156" t="s">
+      <c r="I57" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J57" s="156"/>
-      <c r="K57" s="133"/>
-      <c r="L57" s="133" t="s">
+      <c r="J57" s="154"/>
+      <c r="K57" s="131"/>
+      <c r="L57" s="131" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="58" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B58" s="132">
+      <c r="B58" s="130">
         <v>54</v>
       </c>
-      <c r="C58" s="138"/>
-      <c r="D58" s="136" t="s">
+      <c r="C58" s="136"/>
+      <c r="D58" s="134" t="s">
         <v>216</v>
       </c>
-      <c r="E58" s="133"/>
-      <c r="F58" s="133"/>
-      <c r="G58" s="133" t="s">
+      <c r="E58" s="131"/>
+      <c r="F58" s="131"/>
+      <c r="G58" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H58" s="133" t="s">
+      <c r="H58" s="131" t="s">
         <v>324</v>
       </c>
-      <c r="I58" s="156" t="s">
+      <c r="I58" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="J58" s="156"/>
-      <c r="K58" s="133"/>
-      <c r="L58" s="133" t="s">
+      <c r="J58" s="154"/>
+      <c r="K58" s="131"/>
+      <c r="L58" s="131" t="s">
         <v>217</v>
       </c>
     </row>
@@ -11104,7 +11097,7 @@
       <c r="B59" s="53">
         <v>55</v>
       </c>
-      <c r="C59" s="99"/>
+      <c r="C59" s="98"/>
       <c r="D59" s="61" t="s">
         <v>416</v>
       </c>
@@ -11126,189 +11119,189 @@
       <c r="L59" s="61"/>
     </row>
     <row r="60" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B60" s="132">
+      <c r="B60" s="130">
         <v>56</v>
       </c>
-      <c r="C60" s="144" t="s">
+      <c r="C60" s="142" t="s">
         <v>218</v>
       </c>
-      <c r="D60" s="133" t="s">
+      <c r="D60" s="131" t="s">
         <v>325</v>
       </c>
-      <c r="E60" s="135"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136" t="s">
+      <c r="E60" s="133"/>
+      <c r="F60" s="133"/>
+      <c r="G60" s="134" t="s">
         <v>325</v>
       </c>
-      <c r="H60" s="136" t="s">
+      <c r="H60" s="134" t="s">
         <v>327</v>
       </c>
-      <c r="I60" s="137" t="s">
+      <c r="I60" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J60" s="137" t="s">
+      <c r="J60" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K60" s="136"/>
-      <c r="L60" s="136" t="s">
+      <c r="K60" s="134"/>
+      <c r="L60" s="134" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B61" s="132">
+      <c r="B61" s="130">
         <v>57</v>
       </c>
-      <c r="C61" s="138"/>
-      <c r="D61" s="139"/>
-      <c r="E61" s="135" t="s">
+      <c r="C61" s="136"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="133" t="s">
         <v>326</v>
       </c>
-      <c r="F61" s="135"/>
-      <c r="G61" s="136" t="s">
+      <c r="F61" s="133"/>
+      <c r="G61" s="134" t="s">
         <v>329</v>
       </c>
-      <c r="H61" s="136" t="s">
+      <c r="H61" s="134" t="s">
         <v>328</v>
       </c>
-      <c r="I61" s="137" t="s">
+      <c r="I61" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J61" s="137" t="s">
+      <c r="J61" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K61" s="136"/>
-      <c r="L61" s="136" t="s">
+      <c r="K61" s="134"/>
+      <c r="L61" s="134" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="62" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B62" s="132">
+      <c r="B62" s="130">
         <v>58</v>
       </c>
-      <c r="C62" s="138"/>
-      <c r="D62" s="133" t="s">
+      <c r="C62" s="136"/>
+      <c r="D62" s="131" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="135"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="136" t="s">
+      <c r="E62" s="133"/>
+      <c r="F62" s="133"/>
+      <c r="G62" s="134" t="s">
         <v>330</v>
       </c>
-      <c r="H62" s="136" t="s">
+      <c r="H62" s="134" t="s">
         <v>332</v>
       </c>
-      <c r="I62" s="137" t="s">
+      <c r="I62" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J62" s="137" t="s">
+      <c r="J62" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K62" s="136"/>
-      <c r="L62" s="136" t="s">
+      <c r="K62" s="134"/>
+      <c r="L62" s="134" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="63" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B63" s="132">
+      <c r="B63" s="130">
         <v>59</v>
       </c>
-      <c r="C63" s="138"/>
-      <c r="D63" s="139"/>
-      <c r="E63" s="135" t="s">
+      <c r="C63" s="136"/>
+      <c r="D63" s="137"/>
+      <c r="E63" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="F63" s="135"/>
-      <c r="G63" s="136" t="s">
+      <c r="F63" s="133"/>
+      <c r="G63" s="134" t="s">
         <v>331</v>
       </c>
-      <c r="H63" s="136" t="s">
+      <c r="H63" s="134" t="s">
         <v>333</v>
       </c>
-      <c r="I63" s="137" t="s">
+      <c r="I63" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J63" s="137" t="s">
+      <c r="J63" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K63" s="136"/>
-      <c r="L63" s="136" t="s">
+      <c r="K63" s="134"/>
+      <c r="L63" s="134" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="64" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B64" s="132">
+      <c r="B64" s="130">
         <v>60</v>
       </c>
-      <c r="C64" s="133" t="s">
+      <c r="C64" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="135" t="s">
+      <c r="D64" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="E64" s="136"/>
-      <c r="F64" s="136"/>
-      <c r="G64" s="136" t="s">
+      <c r="E64" s="134"/>
+      <c r="F64" s="134"/>
+      <c r="G64" s="134" t="s">
         <v>335</v>
       </c>
-      <c r="H64" s="136" t="s">
+      <c r="H64" s="134" t="s">
         <v>334</v>
       </c>
-      <c r="I64" s="137" t="s">
+      <c r="I64" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="137"/>
-      <c r="K64" s="136"/>
-      <c r="L64" s="136" t="s">
+      <c r="J64" s="135"/>
+      <c r="K64" s="134"/>
+      <c r="L64" s="134" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="65" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B65" s="132">
+      <c r="B65" s="130">
         <v>61</v>
       </c>
-      <c r="C65" s="139"/>
-      <c r="D65" s="135" t="s">
+      <c r="C65" s="137"/>
+      <c r="D65" s="133" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="136"/>
-      <c r="F65" s="136"/>
-      <c r="G65" s="136" t="s">
+      <c r="E65" s="134"/>
+      <c r="F65" s="134"/>
+      <c r="G65" s="134" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="136" t="s">
+      <c r="H65" s="134" t="s">
         <v>406</v>
       </c>
-      <c r="I65" s="137" t="s">
+      <c r="I65" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J65" s="137"/>
-      <c r="K65" s="136"/>
-      <c r="L65" s="136" t="s">
+      <c r="J65" s="135"/>
+      <c r="K65" s="134"/>
+      <c r="L65" s="134" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="66" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B66" s="132">
+      <c r="B66" s="130">
         <v>62</v>
       </c>
-      <c r="C66" s="139"/>
-      <c r="D66" s="135" t="s">
+      <c r="C66" s="137"/>
+      <c r="D66" s="133" t="s">
         <v>226</v>
       </c>
-      <c r="E66" s="136"/>
-      <c r="F66" s="136"/>
-      <c r="G66" s="136" t="s">
+      <c r="E66" s="134"/>
+      <c r="F66" s="134"/>
+      <c r="G66" s="134" t="s">
         <v>336</v>
       </c>
-      <c r="H66" s="136" t="s">
+      <c r="H66" s="134" t="s">
         <v>409</v>
       </c>
-      <c r="I66" s="137" t="s">
+      <c r="I66" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J66" s="137"/>
-      <c r="K66" s="136"/>
-      <c r="L66" s="136" t="s">
+      <c r="J66" s="135"/>
+      <c r="K66" s="134"/>
+      <c r="L66" s="134" t="s">
         <v>204</v>
       </c>
     </row>
@@ -11316,7 +11309,7 @@
       <c r="B67" s="53">
         <v>63</v>
       </c>
-      <c r="C67" s="100"/>
+      <c r="C67" s="99"/>
       <c r="D67" s="62" t="s">
         <v>407</v>
       </c>
@@ -11342,169 +11335,169 @@
       </c>
     </row>
     <row r="68" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B68" s="132">
+      <c r="B68" s="130">
         <v>64</v>
       </c>
-      <c r="C68" s="139"/>
-      <c r="D68" s="135" t="s">
+      <c r="C68" s="137"/>
+      <c r="D68" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="E68" s="136"/>
-      <c r="F68" s="136"/>
-      <c r="G68" s="136"/>
-      <c r="H68" s="136"/>
-      <c r="I68" s="140" t="s">
+      <c r="E68" s="134"/>
+      <c r="F68" s="134"/>
+      <c r="G68" s="134"/>
+      <c r="H68" s="134"/>
+      <c r="I68" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="J68" s="140"/>
-      <c r="K68" s="141" t="s">
+      <c r="J68" s="138"/>
+      <c r="K68" s="139" t="s">
         <v>76</v>
       </c>
-      <c r="L68" s="136"/>
+      <c r="L68" s="134"/>
     </row>
     <row r="69" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B69" s="132">
+      <c r="B69" s="130">
         <v>65</v>
       </c>
-      <c r="C69" s="139"/>
-      <c r="D69" s="135" t="s">
+      <c r="C69" s="137"/>
+      <c r="D69" s="133" t="s">
         <v>205</v>
       </c>
-      <c r="E69" s="136"/>
-      <c r="F69" s="136"/>
-      <c r="G69" s="136"/>
-      <c r="H69" s="136"/>
-      <c r="I69" s="140" t="s">
+      <c r="E69" s="134"/>
+      <c r="F69" s="134"/>
+      <c r="G69" s="134"/>
+      <c r="H69" s="134"/>
+      <c r="I69" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="J69" s="140"/>
-      <c r="K69" s="136" t="s">
+      <c r="J69" s="138"/>
+      <c r="K69" s="134" t="s">
         <v>338</v>
       </c>
-      <c r="L69" s="136"/>
+      <c r="L69" s="134"/>
     </row>
     <row r="70" spans="2:12" s="60" customFormat="1" ht="34.5" customHeight="1">
-      <c r="B70" s="132">
+      <c r="B70" s="130">
         <v>66</v>
       </c>
-      <c r="C70" s="139"/>
-      <c r="D70" s="135" t="s">
+      <c r="C70" s="137"/>
+      <c r="D70" s="133" t="s">
         <v>207</v>
       </c>
-      <c r="E70" s="136"/>
-      <c r="F70" s="136"/>
-      <c r="G70" s="136" t="s">
+      <c r="E70" s="134"/>
+      <c r="F70" s="134"/>
+      <c r="G70" s="134" t="s">
         <v>340</v>
       </c>
-      <c r="H70" s="136" t="s">
+      <c r="H70" s="134" t="s">
         <v>411</v>
       </c>
-      <c r="I70" s="142" t="s">
+      <c r="I70" s="140" t="s">
         <v>339</v>
       </c>
-      <c r="J70" s="137" t="s">
+      <c r="J70" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="K70" s="136" t="s">
+      <c r="K70" s="134" t="s">
         <v>341</v>
       </c>
-      <c r="L70" s="136"/>
+      <c r="L70" s="134"/>
     </row>
     <row r="71" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B71" s="132">
+      <c r="B71" s="130">
         <v>67</v>
       </c>
-      <c r="C71" s="139"/>
-      <c r="D71" s="135" t="s">
+      <c r="C71" s="137"/>
+      <c r="D71" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="E71" s="136"/>
-      <c r="F71" s="136"/>
-      <c r="G71" s="136"/>
-      <c r="H71" s="136"/>
-      <c r="I71" s="140" t="s">
+      <c r="E71" s="134"/>
+      <c r="F71" s="134"/>
+      <c r="G71" s="134"/>
+      <c r="H71" s="134"/>
+      <c r="I71" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="J71" s="140"/>
-      <c r="K71" s="141" t="s">
+      <c r="J71" s="138"/>
+      <c r="K71" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="L71" s="136"/>
+      <c r="L71" s="134"/>
     </row>
     <row r="72" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B72" s="132">
+      <c r="B72" s="130">
         <v>68</v>
       </c>
-      <c r="C72" s="139"/>
-      <c r="D72" s="135" t="s">
+      <c r="C72" s="137"/>
+      <c r="D72" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="E72" s="136"/>
-      <c r="F72" s="136"/>
-      <c r="G72" s="136"/>
-      <c r="H72" s="136"/>
-      <c r="I72" s="140" t="s">
+      <c r="E72" s="134"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
+      <c r="H72" s="134"/>
+      <c r="I72" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="J72" s="140"/>
-      <c r="K72" s="141" t="s">
+      <c r="J72" s="138"/>
+      <c r="K72" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="L72" s="136"/>
+      <c r="L72" s="134"/>
     </row>
     <row r="73" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B73" s="132">
+      <c r="B73" s="130">
         <v>69</v>
       </c>
-      <c r="C73" s="143"/>
-      <c r="D73" s="135" t="s">
+      <c r="C73" s="141"/>
+      <c r="D73" s="133" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="136"/>
-      <c r="F73" s="136"/>
-      <c r="G73" s="136"/>
-      <c r="H73" s="136"/>
-      <c r="I73" s="140" t="s">
+      <c r="E73" s="134"/>
+      <c r="F73" s="134"/>
+      <c r="G73" s="134"/>
+      <c r="H73" s="134"/>
+      <c r="I73" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="J73" s="140"/>
-      <c r="K73" s="141" t="s">
+      <c r="J73" s="138"/>
+      <c r="K73" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="L73" s="136"/>
+      <c r="L73" s="134"/>
     </row>
     <row r="74" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B74" s="53">
+      <c r="B74" s="130">
         <v>70</v>
       </c>
-      <c r="C74" s="101" t="s">
+      <c r="C74" s="141" t="s">
         <v>223</v>
       </c>
-      <c r="D74" s="62" t="s">
+      <c r="D74" s="133" t="s">
         <v>224</v>
       </c>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58" t="s">
+      <c r="E74" s="134"/>
+      <c r="F74" s="134"/>
+      <c r="G74" s="134" t="s">
         <v>415</v>
       </c>
-      <c r="H74" s="58" t="s">
+      <c r="H74" s="134" t="s">
         <v>337</v>
       </c>
-      <c r="I74" s="68" t="s">
+      <c r="I74" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="J74" s="69"/>
-      <c r="K74" s="58" t="s">
+      <c r="J74" s="138"/>
+      <c r="K74" s="134" t="s">
         <v>225</v>
       </c>
-      <c r="L74" s="58"/>
+      <c r="L74" s="134"/>
     </row>
     <row r="75" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B75" s="53">
         <v>71</v>
       </c>
-      <c r="C75" s="102" t="s">
+      <c r="C75" s="100" t="s">
         <v>384</v>
       </c>
       <c r="D75" s="58" t="s">
@@ -11529,7 +11522,7 @@
       <c r="B76" s="53">
         <v>72</v>
       </c>
-      <c r="C76" s="102" t="s">
+      <c r="C76" s="100" t="s">
         <v>384</v>
       </c>
       <c r="D76" s="58" t="s">
@@ -11552,691 +11545,691 @@
     </row>
     <row r="77" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B77" s="77"/>
-      <c r="C77" s="103"/>
+      <c r="C77" s="101"/>
       <c r="I77" s="77"/>
       <c r="J77" s="77"/>
     </row>
     <row r="78" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B78" s="77"/>
-      <c r="C78" s="103"/>
+      <c r="C78" s="101"/>
       <c r="I78" s="77"/>
       <c r="J78" s="77"/>
     </row>
     <row r="79" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B79" s="77"/>
-      <c r="C79" s="103"/>
+      <c r="C79" s="101"/>
       <c r="I79" s="77"/>
       <c r="J79" s="77"/>
     </row>
     <row r="80" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B80" s="77"/>
-      <c r="C80" s="103"/>
+      <c r="C80" s="101"/>
       <c r="I80" s="77"/>
       <c r="J80" s="77"/>
     </row>
     <row r="81" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B81" s="77"/>
-      <c r="C81" s="103"/>
+      <c r="C81" s="101"/>
       <c r="I81" s="77"/>
       <c r="J81" s="77"/>
     </row>
     <row r="82" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B82" s="77"/>
-      <c r="C82" s="103"/>
+      <c r="C82" s="101"/>
       <c r="I82" s="77"/>
       <c r="J82" s="77"/>
     </row>
     <row r="83" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B83" s="77"/>
-      <c r="C83" s="103"/>
+      <c r="C83" s="101"/>
       <c r="I83" s="77"/>
       <c r="J83" s="77"/>
     </row>
     <row r="84" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B84" s="77"/>
-      <c r="C84" s="104"/>
+      <c r="C84" s="102"/>
       <c r="I84" s="52"/>
       <c r="J84" s="52"/>
     </row>
     <row r="85" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B85" s="52"/>
-      <c r="C85" s="104"/>
+      <c r="C85" s="102"/>
       <c r="I85" s="52"/>
       <c r="J85" s="52"/>
     </row>
     <row r="86" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B86" s="52"/>
-      <c r="C86" s="104"/>
+      <c r="C86" s="102"/>
       <c r="I86" s="52"/>
       <c r="J86" s="52"/>
     </row>
     <row r="87" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B87" s="52"/>
-      <c r="C87" s="104"/>
+      <c r="C87" s="102"/>
       <c r="I87" s="52"/>
       <c r="J87" s="52"/>
     </row>
     <row r="88" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B88" s="52"/>
-      <c r="C88" s="104"/>
+      <c r="C88" s="102"/>
       <c r="I88" s="52"/>
       <c r="J88" s="52"/>
     </row>
     <row r="89" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B89" s="52"/>
-      <c r="C89" s="104"/>
+      <c r="C89" s="102"/>
       <c r="I89" s="52"/>
       <c r="J89" s="52"/>
     </row>
     <row r="90" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B90" s="52"/>
-      <c r="C90" s="104"/>
+      <c r="C90" s="102"/>
       <c r="I90" s="52"/>
       <c r="J90" s="52"/>
     </row>
     <row r="91" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B91" s="52"/>
-      <c r="C91" s="104"/>
+      <c r="C91" s="102"/>
       <c r="I91" s="52"/>
       <c r="J91" s="52"/>
     </row>
     <row r="92" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B92" s="52"/>
-      <c r="C92" s="104"/>
+      <c r="C92" s="102"/>
       <c r="I92" s="52"/>
       <c r="J92" s="52"/>
     </row>
     <row r="93" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B93" s="52"/>
-      <c r="C93" s="104"/>
+      <c r="C93" s="102"/>
       <c r="I93" s="52"/>
       <c r="J93" s="52"/>
     </row>
     <row r="94" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B94" s="52"/>
-      <c r="C94" s="104"/>
+      <c r="C94" s="102"/>
       <c r="I94" s="52"/>
       <c r="J94" s="52"/>
     </row>
     <row r="95" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B95" s="52"/>
-      <c r="C95" s="104"/>
+      <c r="C95" s="102"/>
       <c r="I95" s="52"/>
       <c r="J95" s="52"/>
     </row>
     <row r="96" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B96" s="52"/>
-      <c r="C96" s="104"/>
+      <c r="C96" s="102"/>
       <c r="I96" s="52"/>
       <c r="J96" s="52"/>
     </row>
     <row r="97" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B97" s="52"/>
-      <c r="C97" s="104"/>
+      <c r="C97" s="102"/>
       <c r="I97" s="52"/>
       <c r="J97" s="52"/>
     </row>
     <row r="98" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B98" s="52"/>
-      <c r="C98" s="104"/>
+      <c r="C98" s="102"/>
       <c r="I98" s="52"/>
       <c r="J98" s="52"/>
     </row>
     <row r="99" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B99" s="52"/>
-      <c r="C99" s="104"/>
+      <c r="C99" s="102"/>
       <c r="I99" s="52"/>
       <c r="J99" s="52"/>
     </row>
     <row r="100" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B100" s="52"/>
-      <c r="C100" s="104"/>
+      <c r="C100" s="102"/>
       <c r="I100" s="52"/>
       <c r="J100" s="52"/>
     </row>
     <row r="101" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B101" s="52"/>
-      <c r="C101" s="104"/>
+      <c r="C101" s="102"/>
       <c r="I101" s="52"/>
       <c r="J101" s="52"/>
     </row>
     <row r="102" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B102" s="52"/>
-      <c r="C102" s="104"/>
+      <c r="C102" s="102"/>
       <c r="I102" s="52"/>
       <c r="J102" s="52"/>
     </row>
     <row r="103" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B103" s="52"/>
-      <c r="C103" s="104"/>
+      <c r="C103" s="102"/>
       <c r="I103" s="52"/>
       <c r="J103" s="52"/>
     </row>
     <row r="104" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B104" s="52"/>
-      <c r="C104" s="104"/>
+      <c r="C104" s="102"/>
       <c r="I104" s="52"/>
       <c r="J104" s="52"/>
     </row>
     <row r="105" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B105" s="52"/>
-      <c r="C105" s="104"/>
+      <c r="C105" s="102"/>
       <c r="I105" s="52"/>
       <c r="J105" s="52"/>
     </row>
     <row r="106" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B106" s="52"/>
-      <c r="C106" s="104"/>
+      <c r="C106" s="102"/>
       <c r="I106" s="52"/>
       <c r="J106" s="52"/>
     </row>
     <row r="107" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B107" s="52"/>
-      <c r="C107" s="104"/>
+      <c r="C107" s="102"/>
       <c r="I107" s="52"/>
       <c r="J107" s="52"/>
     </row>
     <row r="108" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B108" s="52"/>
-      <c r="C108" s="104"/>
+      <c r="C108" s="102"/>
       <c r="I108" s="52"/>
       <c r="J108" s="52"/>
     </row>
     <row r="109" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B109" s="52"/>
-      <c r="C109" s="104"/>
+      <c r="C109" s="102"/>
       <c r="I109" s="52"/>
       <c r="J109" s="52"/>
     </row>
     <row r="110" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B110" s="52"/>
-      <c r="C110" s="104"/>
+      <c r="C110" s="102"/>
       <c r="I110" s="52"/>
       <c r="J110" s="52"/>
     </row>
     <row r="111" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B111" s="52"/>
-      <c r="C111" s="104"/>
+      <c r="C111" s="102"/>
       <c r="I111" s="52"/>
       <c r="J111" s="52"/>
     </row>
     <row r="112" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B112" s="52"/>
-      <c r="C112" s="104"/>
+      <c r="C112" s="102"/>
       <c r="I112" s="52"/>
       <c r="J112" s="52"/>
     </row>
     <row r="113" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B113" s="52"/>
-      <c r="C113" s="104"/>
+      <c r="C113" s="102"/>
       <c r="I113" s="52"/>
       <c r="J113" s="52"/>
     </row>
     <row r="114" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B114" s="52"/>
-      <c r="C114" s="104"/>
+      <c r="C114" s="102"/>
       <c r="I114" s="52"/>
       <c r="J114" s="52"/>
     </row>
     <row r="115" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B115" s="52"/>
-      <c r="C115" s="104"/>
+      <c r="C115" s="102"/>
       <c r="I115" s="52"/>
       <c r="J115" s="52"/>
     </row>
     <row r="116" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B116" s="52"/>
-      <c r="C116" s="104"/>
+      <c r="C116" s="102"/>
       <c r="I116" s="52"/>
       <c r="J116" s="52"/>
     </row>
     <row r="117" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B117" s="52"/>
-      <c r="C117" s="104"/>
+      <c r="C117" s="102"/>
       <c r="I117" s="52"/>
       <c r="J117" s="52"/>
     </row>
     <row r="118" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B118" s="52"/>
-      <c r="C118" s="104"/>
+      <c r="C118" s="102"/>
       <c r="I118" s="52"/>
       <c r="J118" s="52"/>
     </row>
     <row r="119" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B119" s="52"/>
-      <c r="C119" s="104"/>
+      <c r="C119" s="102"/>
       <c r="I119" s="52"/>
       <c r="J119" s="52"/>
     </row>
     <row r="120" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B120" s="52"/>
-      <c r="C120" s="104"/>
+      <c r="C120" s="102"/>
       <c r="I120" s="52"/>
       <c r="J120" s="52"/>
     </row>
     <row r="121" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B121" s="52"/>
-      <c r="C121" s="104"/>
+      <c r="C121" s="102"/>
       <c r="I121" s="52"/>
       <c r="J121" s="52"/>
     </row>
     <row r="122" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B122" s="52"/>
-      <c r="C122" s="104"/>
+      <c r="C122" s="102"/>
       <c r="I122" s="52"/>
       <c r="J122" s="52"/>
     </row>
     <row r="123" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B123" s="52"/>
-      <c r="C123" s="104"/>
+      <c r="C123" s="102"/>
       <c r="I123" s="52"/>
       <c r="J123" s="52"/>
     </row>
     <row r="124" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B124" s="52"/>
-      <c r="C124" s="104"/>
+      <c r="C124" s="102"/>
       <c r="I124" s="52"/>
       <c r="J124" s="52"/>
     </row>
     <row r="125" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B125" s="52"/>
-      <c r="C125" s="104"/>
+      <c r="C125" s="102"/>
       <c r="I125" s="52"/>
       <c r="J125" s="52"/>
     </row>
     <row r="126" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B126" s="52"/>
-      <c r="C126" s="104"/>
+      <c r="C126" s="102"/>
       <c r="I126" s="52"/>
       <c r="J126" s="52"/>
     </row>
     <row r="127" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B127" s="52"/>
-      <c r="C127" s="104"/>
+      <c r="C127" s="102"/>
       <c r="I127" s="52"/>
       <c r="J127" s="52"/>
     </row>
     <row r="128" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B128" s="52"/>
-      <c r="C128" s="104"/>
+      <c r="C128" s="102"/>
       <c r="I128" s="52"/>
       <c r="J128" s="52"/>
     </row>
     <row r="129" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B129" s="52"/>
-      <c r="C129" s="104"/>
+      <c r="C129" s="102"/>
       <c r="I129" s="52"/>
       <c r="J129" s="52"/>
     </row>
     <row r="130" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B130" s="52"/>
-      <c r="C130" s="104"/>
+      <c r="C130" s="102"/>
       <c r="I130" s="52"/>
       <c r="J130" s="52"/>
     </row>
     <row r="131" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B131" s="52"/>
-      <c r="C131" s="104"/>
+      <c r="C131" s="102"/>
       <c r="I131" s="52"/>
       <c r="J131" s="52"/>
     </row>
     <row r="132" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B132" s="52"/>
-      <c r="C132" s="104"/>
+      <c r="C132" s="102"/>
       <c r="I132" s="52"/>
       <c r="J132" s="52"/>
     </row>
     <row r="133" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B133" s="52"/>
-      <c r="C133" s="104"/>
+      <c r="C133" s="102"/>
       <c r="I133" s="52"/>
       <c r="J133" s="52"/>
     </row>
     <row r="134" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B134" s="52"/>
-      <c r="C134" s="104"/>
+      <c r="C134" s="102"/>
       <c r="I134" s="52"/>
       <c r="J134" s="52"/>
     </row>
     <row r="135" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B135" s="52"/>
-      <c r="C135" s="104"/>
+      <c r="C135" s="102"/>
       <c r="I135" s="52"/>
       <c r="J135" s="52"/>
     </row>
     <row r="136" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B136" s="52"/>
-      <c r="C136" s="104"/>
+      <c r="C136" s="102"/>
       <c r="I136" s="52"/>
       <c r="J136" s="52"/>
     </row>
     <row r="137" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B137" s="52"/>
-      <c r="C137" s="104"/>
+      <c r="C137" s="102"/>
       <c r="I137" s="52"/>
       <c r="J137" s="52"/>
     </row>
     <row r="138" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B138" s="52"/>
-      <c r="C138" s="104"/>
+      <c r="C138" s="102"/>
       <c r="I138" s="52"/>
       <c r="J138" s="52"/>
     </row>
     <row r="139" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B139" s="52"/>
-      <c r="C139" s="104"/>
+      <c r="C139" s="102"/>
       <c r="I139" s="52"/>
       <c r="J139" s="52"/>
     </row>
     <row r="140" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B140" s="52"/>
-      <c r="C140" s="104"/>
+      <c r="C140" s="102"/>
       <c r="I140" s="52"/>
       <c r="J140" s="52"/>
     </row>
     <row r="141" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B141" s="52"/>
-      <c r="C141" s="104"/>
+      <c r="C141" s="102"/>
       <c r="I141" s="52"/>
       <c r="J141" s="52"/>
     </row>
     <row r="142" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B142" s="52"/>
-      <c r="C142" s="104"/>
+      <c r="C142" s="102"/>
       <c r="I142" s="52"/>
       <c r="J142" s="52"/>
     </row>
     <row r="143" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B143" s="52"/>
-      <c r="C143" s="104"/>
+      <c r="C143" s="102"/>
       <c r="I143" s="52"/>
       <c r="J143" s="52"/>
     </row>
     <row r="144" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B144" s="52"/>
-      <c r="C144" s="104"/>
+      <c r="C144" s="102"/>
       <c r="I144" s="52"/>
       <c r="J144" s="52"/>
     </row>
     <row r="145" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B145" s="52"/>
-      <c r="C145" s="104"/>
+      <c r="C145" s="102"/>
       <c r="I145" s="52"/>
       <c r="J145" s="52"/>
     </row>
     <row r="146" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B146" s="52"/>
-      <c r="C146" s="104"/>
+      <c r="C146" s="102"/>
       <c r="I146" s="52"/>
       <c r="J146" s="52"/>
     </row>
     <row r="147" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B147" s="52"/>
-      <c r="C147" s="104"/>
+      <c r="C147" s="102"/>
       <c r="I147" s="52"/>
       <c r="J147" s="52"/>
     </row>
     <row r="148" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B148" s="52"/>
-      <c r="C148" s="104"/>
+      <c r="C148" s="102"/>
       <c r="I148" s="52"/>
       <c r="J148" s="52"/>
     </row>
     <row r="149" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B149" s="52"/>
-      <c r="C149" s="104"/>
+      <c r="C149" s="102"/>
       <c r="I149" s="52"/>
       <c r="J149" s="52"/>
     </row>
     <row r="150" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B150" s="52"/>
-      <c r="C150" s="104"/>
+      <c r="C150" s="102"/>
       <c r="I150" s="52"/>
       <c r="J150" s="52"/>
     </row>
     <row r="151" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B151" s="52"/>
-      <c r="C151" s="104"/>
+      <c r="C151" s="102"/>
       <c r="I151" s="52"/>
       <c r="J151" s="52"/>
     </row>
     <row r="152" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B152" s="52"/>
-      <c r="C152" s="104"/>
+      <c r="C152" s="102"/>
       <c r="I152" s="52"/>
       <c r="J152" s="52"/>
     </row>
     <row r="153" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B153" s="52"/>
-      <c r="C153" s="104"/>
+      <c r="C153" s="102"/>
       <c r="I153" s="52"/>
       <c r="J153" s="52"/>
     </row>
     <row r="154" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B154" s="52"/>
-      <c r="C154" s="104"/>
+      <c r="C154" s="102"/>
       <c r="I154" s="52"/>
       <c r="J154" s="52"/>
     </row>
     <row r="155" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B155" s="52"/>
-      <c r="C155" s="104"/>
+      <c r="C155" s="102"/>
       <c r="I155" s="52"/>
       <c r="J155" s="52"/>
     </row>
     <row r="156" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B156" s="52"/>
-      <c r="C156" s="104"/>
+      <c r="C156" s="102"/>
       <c r="I156" s="52"/>
       <c r="J156" s="52"/>
     </row>
     <row r="157" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B157" s="52"/>
-      <c r="C157" s="104"/>
+      <c r="C157" s="102"/>
       <c r="I157" s="52"/>
       <c r="J157" s="52"/>
     </row>
     <row r="158" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B158" s="52"/>
-      <c r="C158" s="104"/>
+      <c r="C158" s="102"/>
       <c r="I158" s="52"/>
       <c r="J158" s="52"/>
     </row>
     <row r="159" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B159" s="52"/>
-      <c r="C159" s="104"/>
+      <c r="C159" s="102"/>
       <c r="I159" s="52"/>
       <c r="J159" s="52"/>
     </row>
     <row r="160" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B160" s="52"/>
-      <c r="C160" s="104"/>
+      <c r="C160" s="102"/>
       <c r="I160" s="52"/>
       <c r="J160" s="52"/>
     </row>
     <row r="161" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B161" s="52"/>
-      <c r="C161" s="104"/>
+      <c r="C161" s="102"/>
       <c r="I161" s="52"/>
       <c r="J161" s="52"/>
     </row>
     <row r="162" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B162" s="52"/>
-      <c r="C162" s="104"/>
+      <c r="C162" s="102"/>
       <c r="I162" s="52"/>
       <c r="J162" s="52"/>
     </row>
     <row r="163" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B163" s="52"/>
-      <c r="C163" s="104"/>
+      <c r="C163" s="102"/>
       <c r="I163" s="52"/>
       <c r="J163" s="52"/>
     </row>
     <row r="164" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B164" s="52"/>
-      <c r="C164" s="104"/>
+      <c r="C164" s="102"/>
       <c r="I164" s="52"/>
       <c r="J164" s="52"/>
     </row>
     <row r="165" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B165" s="52"/>
-      <c r="C165" s="104"/>
+      <c r="C165" s="102"/>
       <c r="I165" s="52"/>
       <c r="J165" s="52"/>
     </row>
     <row r="166" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B166" s="52"/>
-      <c r="C166" s="104"/>
+      <c r="C166" s="102"/>
       <c r="I166" s="52"/>
       <c r="J166" s="52"/>
     </row>
     <row r="167" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B167" s="52"/>
-      <c r="C167" s="104"/>
+      <c r="C167" s="102"/>
       <c r="I167" s="52"/>
       <c r="J167" s="52"/>
     </row>
     <row r="168" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B168" s="52"/>
-      <c r="C168" s="104"/>
+      <c r="C168" s="102"/>
       <c r="I168" s="52"/>
       <c r="J168" s="52"/>
     </row>
     <row r="169" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B169" s="52"/>
-      <c r="C169" s="104"/>
+      <c r="C169" s="102"/>
       <c r="I169" s="52"/>
       <c r="J169" s="52"/>
     </row>
     <row r="170" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B170" s="52"/>
-      <c r="C170" s="104"/>
+      <c r="C170" s="102"/>
       <c r="I170" s="52"/>
       <c r="J170" s="52"/>
     </row>
     <row r="171" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B171" s="52"/>
-      <c r="C171" s="104"/>
+      <c r="C171" s="102"/>
       <c r="I171" s="52"/>
       <c r="J171" s="52"/>
     </row>
     <row r="172" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B172" s="52"/>
-      <c r="C172" s="104"/>
+      <c r="C172" s="102"/>
       <c r="I172" s="52"/>
       <c r="J172" s="52"/>
     </row>
     <row r="173" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B173" s="52"/>
-      <c r="C173" s="104"/>
+      <c r="C173" s="102"/>
       <c r="I173" s="52"/>
       <c r="J173" s="52"/>
     </row>
     <row r="174" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B174" s="52"/>
-      <c r="C174" s="104"/>
+      <c r="C174" s="102"/>
       <c r="I174" s="52"/>
       <c r="J174" s="52"/>
     </row>
     <row r="175" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B175" s="52"/>
-      <c r="C175" s="104"/>
+      <c r="C175" s="102"/>
       <c r="I175" s="52"/>
       <c r="J175" s="52"/>
     </row>
     <row r="176" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B176" s="52"/>
-      <c r="C176" s="104"/>
+      <c r="C176" s="102"/>
       <c r="I176" s="52"/>
       <c r="J176" s="52"/>
     </row>
     <row r="177" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B177" s="52"/>
-      <c r="C177" s="104"/>
+      <c r="C177" s="102"/>
       <c r="I177" s="52"/>
       <c r="J177" s="52"/>
     </row>
     <row r="178" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B178" s="52"/>
-      <c r="C178" s="104"/>
+      <c r="C178" s="102"/>
       <c r="I178" s="52"/>
       <c r="J178" s="52"/>
     </row>
     <row r="179" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B179" s="52"/>
-      <c r="C179" s="104"/>
+      <c r="C179" s="102"/>
       <c r="I179" s="52"/>
       <c r="J179" s="52"/>
     </row>
     <row r="180" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B180" s="52"/>
-      <c r="C180" s="104"/>
+      <c r="C180" s="102"/>
       <c r="I180" s="52"/>
       <c r="J180" s="52"/>
     </row>
     <row r="181" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B181" s="52"/>
-      <c r="C181" s="104"/>
+      <c r="C181" s="102"/>
       <c r="I181" s="52"/>
       <c r="J181" s="52"/>
     </row>
     <row r="182" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B182" s="52"/>
-      <c r="C182" s="104"/>
+      <c r="C182" s="102"/>
       <c r="I182" s="52"/>
       <c r="J182" s="52"/>
     </row>
     <row r="183" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B183" s="52"/>
-      <c r="C183" s="104"/>
+      <c r="C183" s="102"/>
       <c r="I183" s="52"/>
       <c r="J183" s="52"/>
     </row>
     <row r="184" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B184" s="52"/>
-      <c r="C184" s="104"/>
+      <c r="C184" s="102"/>
       <c r="I184" s="52"/>
       <c r="J184" s="52"/>
     </row>
     <row r="185" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B185" s="52"/>
-      <c r="C185" s="104"/>
+      <c r="C185" s="102"/>
       <c r="I185" s="52"/>
       <c r="J185" s="52"/>
     </row>
     <row r="186" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B186" s="52"/>
-      <c r="C186" s="104"/>
+      <c r="C186" s="102"/>
       <c r="I186" s="52"/>
       <c r="J186" s="52"/>
     </row>
     <row r="187" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B187" s="52"/>
-      <c r="C187" s="104"/>
+      <c r="C187" s="102"/>
       <c r="I187" s="52"/>
       <c r="J187" s="52"/>
     </row>
     <row r="188" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B188" s="52"/>
-      <c r="C188" s="104"/>
+      <c r="C188" s="102"/>
       <c r="I188" s="52"/>
       <c r="J188" s="52"/>
     </row>
     <row r="189" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B189" s="52"/>
-      <c r="C189" s="104"/>
+      <c r="C189" s="102"/>
       <c r="I189" s="52"/>
       <c r="J189" s="52"/>
     </row>
     <row r="190" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B190" s="52"/>
-      <c r="C190" s="104"/>
+      <c r="C190" s="102"/>
       <c r="I190" s="52"/>
       <c r="J190" s="52"/>
     </row>
     <row r="191" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B191" s="52"/>
-      <c r="C191" s="104"/>
+      <c r="C191" s="102"/>
       <c r="I191" s="52"/>
       <c r="J191" s="52"/>
     </row>
@@ -12450,18 +12443,18 @@
       <c r="F1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="155" t="s">
         <v>423</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -12538,7 +12531,7 @@
       <c r="D6" s="79" t="s">
         <v>615</v>
       </c>
-      <c r="E6" s="102"/>
+      <c r="E6" s="100"/>
       <c r="F6" s="58"/>
       <c r="G6" s="79" t="s">
         <v>552</v>
@@ -12560,7 +12553,7 @@
       <c r="D7" s="79" t="s">
         <v>616</v>
       </c>
-      <c r="E7" s="102"/>
+      <c r="E7" s="100"/>
       <c r="F7" s="58"/>
       <c r="G7" s="79" t="s">
         <v>553</v>
@@ -12586,7 +12579,7 @@
       <c r="D8" s="89" t="s">
         <v>565</v>
       </c>
-      <c r="E8" s="125"/>
+      <c r="E8" s="123"/>
       <c r="F8" s="58"/>
       <c r="G8" s="79" t="s">
         <v>568</v>
@@ -12610,7 +12603,7 @@
       <c r="D9" s="79" t="s">
         <v>566</v>
       </c>
-      <c r="E9" s="123"/>
+      <c r="E9" s="121"/>
       <c r="F9" s="58"/>
       <c r="G9" s="79" t="s">
         <v>569</v>
@@ -12634,7 +12627,7 @@
       <c r="D10" s="89" t="s">
         <v>509</v>
       </c>
-      <c r="E10" s="123"/>
+      <c r="E10" s="121"/>
       <c r="F10" s="58"/>
       <c r="G10" s="79" t="s">
         <v>567</v>
@@ -12658,7 +12651,7 @@
       <c r="D11" s="86" t="s">
         <v>570</v>
       </c>
-      <c r="E11" s="123" t="s">
+      <c r="E11" s="121" t="s">
         <v>571</v>
       </c>
       <c r="F11" s="58"/>
@@ -12680,7 +12673,7 @@
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="89"/>
-      <c r="E12" s="123" t="s">
+      <c r="E12" s="121" t="s">
         <v>572</v>
       </c>
       <c r="F12" s="58"/>
@@ -12708,7 +12701,7 @@
       <c r="D13" s="86" t="s">
         <v>594</v>
       </c>
-      <c r="E13" s="123" t="s">
+      <c r="E13" s="121" t="s">
         <v>592</v>
       </c>
       <c r="F13" s="58"/>
@@ -12732,7 +12725,7 @@
       </c>
       <c r="C14" s="89"/>
       <c r="D14" s="89"/>
-      <c r="E14" s="123" t="s">
+      <c r="E14" s="121" t="s">
         <v>431</v>
       </c>
       <c r="F14" s="58"/>
@@ -12756,7 +12749,7 @@
       <c r="D15" s="86" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="123" t="s">
+      <c r="E15" s="121" t="s">
         <v>537</v>
       </c>
       <c r="F15" s="58"/>
@@ -12781,10 +12774,10 @@
       <c r="C16" s="92" t="s">
         <v>591</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="103" t="s">
         <v>433</v>
       </c>
-      <c r="E16" s="123" t="s">
+      <c r="E16" s="121" t="s">
         <v>595</v>
       </c>
       <c r="F16" s="58"/>
@@ -12805,10 +12798,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="93"/>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="103" t="s">
         <v>434</v>
       </c>
-      <c r="E17" s="123" t="s">
+      <c r="E17" s="121" t="s">
         <v>596</v>
       </c>
       <c r="F17" s="58"/>
@@ -12829,8 +12822,8 @@
         <v>14</v>
       </c>
       <c r="C18" s="93"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="123" t="s">
+      <c r="D18" s="104"/>
+      <c r="E18" s="121" t="s">
         <v>597</v>
       </c>
       <c r="F18" s="58"/>
@@ -12853,23 +12846,23 @@
         <v>15</v>
       </c>
       <c r="C19" s="93"/>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="108" t="s">
         <v>600</v>
       </c>
-      <c r="E19" s="111" t="s">
+      <c r="E19" s="109" t="s">
         <v>538</v>
       </c>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112" t="s">
+      <c r="F19" s="110"/>
+      <c r="G19" s="110" t="s">
         <v>547</v>
       </c>
-      <c r="H19" s="112"/>
-      <c r="I19" s="113" t="s">
+      <c r="H19" s="110"/>
+      <c r="I19" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="112"/>
-      <c r="K19" s="114"/>
-      <c r="L19" s="116" t="s">
+      <c r="J19" s="110"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -12878,21 +12871,21 @@
         <v>16</v>
       </c>
       <c r="C20" s="93"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="111" t="s">
+      <c r="D20" s="113"/>
+      <c r="E20" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="F20" s="112"/>
-      <c r="G20" s="112" t="s">
+      <c r="F20" s="110"/>
+      <c r="G20" s="110" t="s">
         <v>548</v>
       </c>
-      <c r="H20" s="112"/>
-      <c r="I20" s="113" t="s">
+      <c r="H20" s="110"/>
+      <c r="I20" s="111" t="s">
         <v>430</v>
       </c>
-      <c r="J20" s="112"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="116" t="s">
+      <c r="J20" s="110"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -12901,10 +12894,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="93"/>
-      <c r="D21" s="105" t="s">
+      <c r="D21" s="103" t="s">
         <v>603</v>
       </c>
-      <c r="E21" s="123" t="s">
+      <c r="E21" s="121" t="s">
         <v>601</v>
       </c>
       <c r="F21" s="58"/>
@@ -12925,8 +12918,8 @@
         <v>18</v>
       </c>
       <c r="C22" s="93"/>
-      <c r="D22" s="106"/>
-      <c r="E22" s="123" t="s">
+      <c r="D22" s="104"/>
+      <c r="E22" s="121" t="s">
         <v>602</v>
       </c>
       <c r="F22" s="58"/>
@@ -12950,7 +12943,7 @@
       <c r="D23" s="75" t="s">
         <v>436</v>
       </c>
-      <c r="E23" s="124" t="s">
+      <c r="E23" s="122" t="s">
         <v>608</v>
       </c>
       <c r="F23" s="58"/>
@@ -12972,7 +12965,7 @@
       </c>
       <c r="C24" s="93"/>
       <c r="D24" s="95"/>
-      <c r="E24" s="103" t="s">
+      <c r="E24" s="101" t="s">
         <v>609</v>
       </c>
       <c r="F24" s="58"/>
@@ -12994,7 +12987,7 @@
       </c>
       <c r="C25" s="93"/>
       <c r="D25" s="76"/>
-      <c r="E25" s="124" t="s">
+      <c r="E25" s="122" t="s">
         <v>610</v>
       </c>
       <c r="F25" s="58"/>
@@ -13019,10 +13012,10 @@
       <c r="C26" s="92" t="s">
         <v>437</v>
       </c>
-      <c r="D26" s="106" t="s">
+      <c r="D26" s="104" t="s">
         <v>510</v>
       </c>
-      <c r="E26" s="123" t="s">
+      <c r="E26" s="121" t="s">
         <v>511</v>
       </c>
       <c r="F26" s="58"/>
@@ -13045,8 +13038,8 @@
         <v>23</v>
       </c>
       <c r="C27" s="93"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="123" t="s">
+      <c r="D27" s="127"/>
+      <c r="E27" s="121" t="s">
         <v>514</v>
       </c>
       <c r="F27" s="58"/>
@@ -13067,23 +13060,23 @@
         <v>24</v>
       </c>
       <c r="C28" s="93"/>
-      <c r="D28" s="130" t="s">
+      <c r="D28" s="128" t="s">
         <v>502</v>
       </c>
-      <c r="E28" s="107" t="s">
+      <c r="E28" s="105" t="s">
         <v>503</v>
       </c>
-      <c r="F28" s="108"/>
-      <c r="G28" s="107" t="s">
+      <c r="F28" s="106"/>
+      <c r="G28" s="105" t="s">
         <v>505</v>
       </c>
-      <c r="H28" s="108"/>
-      <c r="I28" s="109" t="s">
+      <c r="H28" s="106"/>
+      <c r="I28" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="108"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="116" t="s">
+      <c r="J28" s="106"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13092,23 +13085,23 @@
         <v>25</v>
       </c>
       <c r="C29" s="94"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="107" t="s">
+      <c r="D29" s="129"/>
+      <c r="E29" s="105" t="s">
         <v>504</v>
       </c>
-      <c r="F29" s="108"/>
-      <c r="G29" s="107" t="s">
+      <c r="F29" s="106"/>
+      <c r="G29" s="105" t="s">
         <v>554</v>
       </c>
-      <c r="H29" s="108"/>
-      <c r="I29" s="109" t="s">
+      <c r="H29" s="106"/>
+      <c r="I29" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="106" t="s">
         <v>558</v>
       </c>
-      <c r="K29" s="118"/>
-      <c r="L29" s="116" t="s">
+      <c r="K29" s="116"/>
+      <c r="L29" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13119,23 +13112,23 @@
       <c r="C30" s="93" t="s">
         <v>490</v>
       </c>
-      <c r="D30" s="117" t="s">
+      <c r="D30" s="115" t="s">
         <v>491</v>
       </c>
-      <c r="E30" s="107" t="s">
+      <c r="E30" s="105" t="s">
         <v>493</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108" t="s">
+      <c r="F30" s="106"/>
+      <c r="G30" s="106" t="s">
         <v>494</v>
       </c>
-      <c r="H30" s="108"/>
-      <c r="I30" s="109" t="s">
+      <c r="H30" s="106"/>
+      <c r="I30" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="108"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="116" t="s">
+      <c r="J30" s="106"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13144,23 +13137,23 @@
         <v>27</v>
       </c>
       <c r="C31" s="93"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="107" t="s">
+      <c r="D31" s="117"/>
+      <c r="E31" s="105" t="s">
         <v>495</v>
       </c>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108" t="s">
+      <c r="F31" s="106"/>
+      <c r="G31" s="106" t="s">
         <v>496</v>
       </c>
-      <c r="H31" s="108"/>
-      <c r="I31" s="109" t="s">
+      <c r="H31" s="106"/>
+      <c r="I31" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="108" t="s">
+      <c r="J31" s="106" t="s">
         <v>559</v>
       </c>
-      <c r="K31" s="118"/>
-      <c r="L31" s="116" t="s">
+      <c r="K31" s="116"/>
+      <c r="L31" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13168,24 +13161,24 @@
       <c r="B32" s="84">
         <v>28</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="117" t="s">
+      <c r="C32" s="119"/>
+      <c r="D32" s="115" t="s">
         <v>438</v>
       </c>
-      <c r="E32" s="107" t="s">
+      <c r="E32" s="105" t="s">
         <v>619</v>
       </c>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108" t="s">
+      <c r="F32" s="106"/>
+      <c r="G32" s="106" t="s">
         <v>498</v>
       </c>
-      <c r="H32" s="108"/>
-      <c r="I32" s="109" t="s">
+      <c r="H32" s="106"/>
+      <c r="I32" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="108"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="116" t="s">
+      <c r="J32" s="106"/>
+      <c r="K32" s="116"/>
+      <c r="L32" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13193,24 +13186,24 @@
       <c r="B33" s="84">
         <v>29</v>
       </c>
-      <c r="C33" s="121"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="107" t="s">
+      <c r="C33" s="119"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="105" t="s">
         <v>620</v>
       </c>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108" t="s">
+      <c r="F33" s="106"/>
+      <c r="G33" s="106" t="s">
         <v>497</v>
       </c>
-      <c r="H33" s="108"/>
-      <c r="I33" s="109" t="s">
+      <c r="H33" s="106"/>
+      <c r="I33" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="108" t="s">
+      <c r="J33" s="106" t="s">
         <v>564</v>
       </c>
-      <c r="K33" s="118"/>
-      <c r="L33" s="116" t="s">
+      <c r="K33" s="116"/>
+      <c r="L33" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13218,24 +13211,24 @@
       <c r="B34" s="84">
         <v>30</v>
       </c>
-      <c r="C34" s="121"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="107" t="s">
+      <c r="C34" s="119"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="105" t="s">
         <v>499</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108" t="s">
+      <c r="F34" s="106"/>
+      <c r="G34" s="106" t="s">
         <v>500</v>
       </c>
-      <c r="H34" s="108"/>
-      <c r="I34" s="109" t="s">
+      <c r="H34" s="106"/>
+      <c r="I34" s="107" t="s">
         <v>430</v>
       </c>
-      <c r="J34" s="108" t="s">
+      <c r="J34" s="106" t="s">
         <v>560</v>
       </c>
-      <c r="K34" s="118"/>
-      <c r="L34" s="116" t="s">
+      <c r="K34" s="116"/>
+      <c r="L34" s="114" t="s">
         <v>632</v>
       </c>
     </row>
@@ -13247,7 +13240,7 @@
       <c r="D35" s="89" t="s">
         <v>439</v>
       </c>
-      <c r="E35" s="124"/>
+      <c r="E35" s="122"/>
       <c r="F35" s="58"/>
       <c r="G35" s="79" t="s">
         <v>501</v>
@@ -13273,7 +13266,7 @@
       <c r="D36" s="86" t="s">
         <v>486</v>
       </c>
-      <c r="E36" s="124" t="s">
+      <c r="E36" s="122" t="s">
         <v>621</v>
       </c>
       <c r="F36" s="58"/>
@@ -13295,7 +13288,7 @@
       </c>
       <c r="C37" s="94"/>
       <c r="D37" s="87"/>
-      <c r="E37" s="124" t="s">
+      <c r="E37" s="122" t="s">
         <v>623</v>
       </c>
       <c r="F37" s="58"/>
@@ -13317,13 +13310,13 @@
       <c r="B38" s="84">
         <v>34</v>
       </c>
-      <c r="C38" s="122" t="s">
+      <c r="C38" s="120" t="s">
         <v>440</v>
       </c>
       <c r="D38" s="86" t="s">
         <v>441</v>
       </c>
-      <c r="E38" s="124" t="s">
+      <c r="E38" s="122" t="s">
         <v>626</v>
       </c>
       <c r="F38" s="58"/>
@@ -13343,7 +13336,7 @@
       </c>
       <c r="C39" s="96"/>
       <c r="D39" s="89"/>
-      <c r="E39" s="124" t="s">
+      <c r="E39" s="122" t="s">
         <v>625</v>
       </c>
       <c r="F39" s="58"/>
@@ -13363,7 +13356,7 @@
       </c>
       <c r="C40" s="96"/>
       <c r="D40" s="87"/>
-      <c r="E40" s="124" t="s">
+      <c r="E40" s="122" t="s">
         <v>442</v>
       </c>
       <c r="F40" s="58"/>
@@ -13387,7 +13380,7 @@
       <c r="D41" s="89" t="s">
         <v>444</v>
       </c>
-      <c r="E41" s="124" t="s">
+      <c r="E41" s="122" t="s">
         <v>427</v>
       </c>
       <c r="F41" s="58"/>
@@ -13409,7 +13402,7 @@
       </c>
       <c r="C42" s="97"/>
       <c r="D42" s="89"/>
-      <c r="E42" s="124" t="s">
+      <c r="E42" s="122" t="s">
         <v>506</v>
       </c>
       <c r="F42" s="58"/>
@@ -13431,13 +13424,13 @@
       <c r="B43" s="84">
         <v>39</v>
       </c>
-      <c r="C43" s="126" t="s">
+      <c r="C43" s="124" t="s">
         <v>445</v>
       </c>
       <c r="D43" s="86" t="s">
         <v>446</v>
       </c>
-      <c r="E43" s="124" t="s">
+      <c r="E43" s="122" t="s">
         <v>540</v>
       </c>
       <c r="F43" s="58"/>
@@ -13457,9 +13450,9 @@
       <c r="B44" s="84">
         <v>40</v>
       </c>
-      <c r="C44" s="127"/>
+      <c r="C44" s="125"/>
       <c r="D44" s="87"/>
-      <c r="E44" s="124" t="s">
+      <c r="E44" s="122" t="s">
         <v>447</v>
       </c>
       <c r="F44" s="58"/>
@@ -13479,11 +13472,11 @@
       <c r="B45" s="84">
         <v>41</v>
       </c>
-      <c r="C45" s="127"/>
+      <c r="C45" s="125"/>
       <c r="D45" s="86" t="s">
         <v>448</v>
       </c>
-      <c r="E45" s="124" t="s">
+      <c r="E45" s="122" t="s">
         <v>541</v>
       </c>
       <c r="F45" s="58"/>
@@ -13503,9 +13496,9 @@
       <c r="B46" s="84">
         <v>42</v>
       </c>
-      <c r="C46" s="128"/>
+      <c r="C46" s="126"/>
       <c r="D46" s="87"/>
-      <c r="E46" s="124" t="s">
+      <c r="E46" s="122" t="s">
         <v>449</v>
       </c>
       <c r="F46" s="58"/>
@@ -13525,13 +13518,13 @@
       <c r="B47" s="84">
         <v>43</v>
       </c>
-      <c r="C47" s="102" t="s">
+      <c r="C47" s="100" t="s">
         <v>482</v>
       </c>
       <c r="D47" s="58" t="s">
         <v>483</v>
       </c>
-      <c r="E47" s="102"/>
+      <c r="E47" s="100"/>
       <c r="F47" s="58"/>
       <c r="G47" s="58" t="s">
         <v>484</v>

--- a/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
+++ b/docs/기획/RMHC Korea 홈페이지 개편 IA v0 (version 1).xlsb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rmhc\front_0624\docs\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E90D1B7-DC0E-4FDA-ABDC-CC2B352653D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E594D583-A046-4706-AC63-0BD97F40E0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="840" windowWidth="42210" windowHeight="26775" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3525" yWindow="2205" windowWidth="42210" windowHeight="26775" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="5" r:id="rId1"/>
@@ -3431,7 +3431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3638,9 +3638,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3725,7 +3722,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3991,6 +3988,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4420,42 +4423,42 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="156" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="156"/>
+      <c r="I5" s="156"/>
+      <c r="J5" s="156"/>
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="158"/>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="158"/>
+      <c r="A6" s="157"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="157"/>
+      <c r="J6" s="157"/>
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="159"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="5"/>
@@ -4806,32 +4809,32 @@
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
-      <c r="A37" s="160">
+      <c r="A37" s="159">
         <v>46118</v>
       </c>
-      <c r="B37" s="160"/>
-      <c r="C37" s="160"/>
-      <c r="D37" s="160"/>
-      <c r="E37" s="160"/>
-      <c r="F37" s="160"/>
-      <c r="G37" s="160"/>
-      <c r="H37" s="160"/>
-      <c r="I37" s="160"/>
-      <c r="J37" s="160"/>
+      <c r="B37" s="159"/>
+      <c r="C37" s="159"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="159"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="159"/>
+      <c r="H37" s="159"/>
+      <c r="I37" s="159"/>
+      <c r="J37" s="159"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="160" t="s">
+      <c r="A38" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="160"/>
-      <c r="C38" s="160"/>
-      <c r="D38" s="160"/>
-      <c r="E38" s="160"/>
-      <c r="F38" s="160"/>
-      <c r="G38" s="160"/>
-      <c r="H38" s="160"/>
-      <c r="I38" s="160"/>
-      <c r="J38" s="160"/>
+      <c r="B38" s="159"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="159"/>
+      <c r="E38" s="159"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="159"/>
+      <c r="H38" s="159"/>
+      <c r="I38" s="159"/>
+      <c r="J38" s="159"/>
     </row>
     <row r="39" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="5"/>
@@ -4858,52 +4861,52 @@
       <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="156"/>
-      <c r="B41" s="156"/>
-      <c r="C41" s="156"/>
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
-      <c r="F41" s="156"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="156"/>
-      <c r="J41" s="156"/>
+      <c r="A41" s="155"/>
+      <c r="B41" s="155"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
     </row>
     <row r="42" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="156"/>
-      <c r="B42" s="156"/>
-      <c r="C42" s="156"/>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="156"/>
+      <c r="A42" s="155"/>
+      <c r="B42" s="155"/>
+      <c r="C42" s="155"/>
+      <c r="D42" s="155"/>
+      <c r="E42" s="155"/>
+      <c r="F42" s="155"/>
+      <c r="G42" s="155"/>
+      <c r="H42" s="155"/>
+      <c r="I42" s="155"/>
+      <c r="J42" s="155"/>
     </row>
     <row r="43" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="156"/>
-      <c r="B43" s="156"/>
-      <c r="C43" s="156"/>
-      <c r="D43" s="156"/>
-      <c r="E43" s="156"/>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="156"/>
-      <c r="I43" s="156"/>
-      <c r="J43" s="156"/>
+      <c r="A43" s="155"/>
+      <c r="B43" s="155"/>
+      <c r="C43" s="155"/>
+      <c r="D43" s="155"/>
+      <c r="E43" s="155"/>
+      <c r="F43" s="155"/>
+      <c r="G43" s="155"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="155"/>
     </row>
     <row r="44" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="156"/>
-      <c r="B44" s="156"/>
-      <c r="C44" s="156"/>
-      <c r="D44" s="156"/>
-      <c r="E44" s="156"/>
-      <c r="F44" s="156"/>
-      <c r="G44" s="156"/>
-      <c r="H44" s="156"/>
-      <c r="I44" s="156"/>
-      <c r="J44" s="156"/>
+      <c r="A44" s="155"/>
+      <c r="B44" s="155"/>
+      <c r="C44" s="155"/>
+      <c r="D44" s="155"/>
+      <c r="E44" s="155"/>
+      <c r="F44" s="155"/>
+      <c r="G44" s="155"/>
+      <c r="H44" s="155"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="155"/>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
       <c r="A45" s="7"/>
@@ -4953,37 +4956,37 @@
   <sheetData>
     <row r="1" spans="2:10"/>
     <row r="2" spans="2:10">
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="173"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="172"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="174"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="175"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="177" t="s">
+      <c r="C4" s="176" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="177"/>
       <c r="E4" s="14" t="s">
         <v>3</v>
       </c>
@@ -4991,20 +4994,20 @@
       <c r="G4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="179" t="s">
+      <c r="H4" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="179"/>
-      <c r="J4" s="180"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="179"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="181" t="s">
+      <c r="C5" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="181"/>
+      <c r="D5" s="180"/>
       <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
@@ -5014,24 +5017,24 @@
       <c r="G5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="182" t="s">
+      <c r="H5" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="182"/>
-      <c r="J5" s="183"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="182"/>
     </row>
     <row r="6" spans="2:10" ht="56.1" customHeight="1">
-      <c r="B6" s="184" t="s">
+      <c r="B6" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="20" t="s">
@@ -5040,18 +5043,18 @@
       <c r="C7" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="185" t="s">
+      <c r="D7" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="185"/>
-      <c r="F7" s="186" t="s">
+      <c r="E7" s="184"/>
+      <c r="F7" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="187"/>
-      <c r="H7" s="185" t="s">
+      <c r="G7" s="186"/>
+      <c r="H7" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="185"/>
+      <c r="I7" s="184"/>
       <c r="J7" s="22" t="s">
         <v>17</v>
       </c>
@@ -5063,18 +5066,18 @@
       <c r="C8" s="43">
         <v>46118</v>
       </c>
-      <c r="D8" s="168" t="s">
+      <c r="D8" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="168"/>
-      <c r="F8" s="169" t="s">
+      <c r="E8" s="167"/>
+      <c r="F8" s="168" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="169"/>
-      <c r="H8" s="163" t="s">
+      <c r="G8" s="168"/>
+      <c r="H8" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="164"/>
+      <c r="I8" s="163"/>
       <c r="J8" s="25"/>
     </row>
     <row r="9" spans="2:10" ht="18.75" customHeight="1">
@@ -5082,23 +5085,23 @@
       <c r="C9" s="43">
         <v>46178</v>
       </c>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="169" t="s">
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="168" t="s">
         <v>633</v>
       </c>
-      <c r="G9" s="169"/>
-      <c r="H9" s="163"/>
-      <c r="I9" s="164"/>
+      <c r="G9" s="168"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="163"/>
       <c r="J9" s="26"/>
     </row>
     <row r="10" spans="2:10" ht="18.75" customHeight="1">
       <c r="B10" s="23"/>
       <c r="C10" s="43"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="170"/>
-      <c r="G10" s="169"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="168"/>
       <c r="H10" s="49"/>
       <c r="I10" s="50"/>
       <c r="J10" s="26"/>
@@ -5106,10 +5109,10 @@
     <row r="11" spans="2:10" ht="18.75" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="43"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="169"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="168"/>
+      <c r="G11" s="168"/>
       <c r="H11" s="49"/>
       <c r="I11" s="50"/>
       <c r="J11" s="26"/>
@@ -5117,10 +5120,10 @@
     <row r="12" spans="2:10" ht="18.75" customHeight="1">
       <c r="B12" s="23"/>
       <c r="C12" s="43"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="168"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="169"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="168"/>
       <c r="H12" s="49"/>
       <c r="I12" s="50"/>
       <c r="J12" s="26"/>
@@ -5128,63 +5131,63 @@
     <row r="13" spans="2:10" ht="18.75" customHeight="1">
       <c r="B13" s="23"/>
       <c r="C13" s="43"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="163"/>
-      <c r="I13" s="164"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="168"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="163"/>
       <c r="J13" s="26"/>
     </row>
     <row r="14" spans="2:10" ht="18.75" customHeight="1">
       <c r="B14" s="23"/>
       <c r="C14" s="43"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="169"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="164"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="168"/>
+      <c r="H14" s="162"/>
+      <c r="I14" s="163"/>
       <c r="J14" s="26"/>
     </row>
     <row r="15" spans="2:10" ht="18.75" customHeight="1">
       <c r="B15" s="23"/>
       <c r="C15" s="43"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
-      <c r="H15" s="163"/>
-      <c r="I15" s="164"/>
+      <c r="D15" s="167"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="163"/>
       <c r="J15" s="26"/>
     </row>
     <row r="16" spans="2:10" ht="18.75" customHeight="1">
       <c r="B16" s="23"/>
       <c r="C16" s="43"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="169"/>
-      <c r="G16" s="169"/>
-      <c r="H16" s="163"/>
-      <c r="I16" s="164"/>
+      <c r="D16" s="167"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="168"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="163"/>
       <c r="J16" s="26"/>
     </row>
     <row r="17" spans="2:10" ht="18.75" customHeight="1">
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="163"/>
-      <c r="I17" s="164"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="163"/>
       <c r="J17" s="26"/>
     </row>
     <row r="18" spans="2:10" ht="18.75" customHeight="1">
       <c r="B18" s="23"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169"/>
-      <c r="G18" s="169"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="168"/>
       <c r="H18" s="49"/>
       <c r="I18" s="50"/>
       <c r="J18" s="26"/>
@@ -5192,10 +5195,10 @@
     <row r="19" spans="2:10" ht="18.75" customHeight="1">
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="168"/>
       <c r="H19" s="49"/>
       <c r="I19" s="50"/>
       <c r="J19" s="26"/>
@@ -5203,10 +5206,10 @@
     <row r="20" spans="2:10" ht="18.75" customHeight="1">
       <c r="B20" s="23"/>
       <c r="C20" s="24"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="168"/>
       <c r="H20" s="49"/>
       <c r="I20" s="50"/>
       <c r="J20" s="26"/>
@@ -5214,8 +5217,8 @@
     <row r="21" spans="2:10" ht="18.75" customHeight="1">
       <c r="B21" s="23"/>
       <c r="C21" s="24"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="168"/>
       <c r="H21" s="49"/>
       <c r="I21" s="50"/>
       <c r="J21" s="26"/>
@@ -5223,10 +5226,10 @@
     <row r="22" spans="2:10" ht="18.75" customHeight="1">
       <c r="B22" s="23"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="169"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="168"/>
       <c r="H22" s="49"/>
       <c r="I22" s="50"/>
       <c r="J22" s="26"/>
@@ -5234,10 +5237,10 @@
     <row r="23" spans="2:10" ht="18.75" customHeight="1">
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
-      <c r="D23" s="168"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="168"/>
       <c r="H23" s="49"/>
       <c r="I23" s="50"/>
       <c r="J23" s="26"/>
@@ -5245,92 +5248,92 @@
     <row r="24" spans="2:10" ht="18.75" customHeight="1">
       <c r="B24" s="23"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="168"/>
-      <c r="E24" s="168"/>
-      <c r="F24" s="169"/>
-      <c r="G24" s="169"/>
-      <c r="H24" s="163"/>
-      <c r="I24" s="164"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="168"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="163"/>
       <c r="J24" s="26"/>
     </row>
     <row r="25" spans="2:10" ht="18.75" customHeight="1">
       <c r="B25" s="23"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="163"/>
-      <c r="I25" s="164"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="168"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="163"/>
       <c r="J25" s="26"/>
     </row>
     <row r="26" spans="2:10" ht="18.75" customHeight="1">
       <c r="B26" s="23"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="169"/>
-      <c r="H26" s="163"/>
-      <c r="I26" s="164"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="163"/>
       <c r="J26" s="26"/>
     </row>
     <row r="27" spans="2:10" ht="18.75" customHeight="1">
       <c r="B27" s="23"/>
       <c r="C27" s="24"/>
-      <c r="D27" s="168"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="163"/>
-      <c r="I27" s="164"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="168"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="163"/>
       <c r="J27" s="26"/>
     </row>
     <row r="28" spans="2:10" ht="18.75" customHeight="1">
       <c r="B28" s="23"/>
       <c r="C28" s="24"/>
-      <c r="D28" s="168"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="169"/>
-      <c r="G28" s="169"/>
-      <c r="H28" s="163"/>
-      <c r="I28" s="164"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="168"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="163"/>
       <c r="J28" s="26"/>
     </row>
     <row r="29" spans="2:10" ht="18.75" customHeight="1">
       <c r="B29" s="23"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="168"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="169"/>
-      <c r="G29" s="169"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="164"/>
+      <c r="D29" s="167"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="168"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="163"/>
       <c r="J29" s="26"/>
     </row>
     <row r="30" spans="2:10" ht="18.75" customHeight="1">
       <c r="B30" s="27"/>
       <c r="C30" s="28"/>
-      <c r="D30" s="161"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="162"/>
-      <c r="H30" s="163"/>
-      <c r="I30" s="164"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="163"/>
       <c r="J30" s="29"/>
     </row>
     <row r="31" spans="2:10" ht="76.5" customHeight="1">
-      <c r="B31" s="165" t="s">
+      <c r="B31" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="166"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="166"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="166"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="167"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="166"/>
     </row>
     <row r="32" spans="2:10">
       <c r="B32" s="30"/>
@@ -5593,17 +5596,17 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>256</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -7363,17 +7366,17 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -8785,15 +8788,15 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="2:9" ht="33.75" customHeight="1">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
     </row>
     <row r="3" spans="2:9" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -8896,7 +8899,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="56"/>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="71" t="s">
         <v>231</v>
       </c>
       <c r="E9" s="55"/>
@@ -8912,8 +8915,8 @@
         <v>6</v>
       </c>
       <c r="C10" s="56"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="71" t="s">
+      <c r="D10" s="71"/>
+      <c r="E10" s="70" t="s">
         <v>232</v>
       </c>
       <c r="F10" s="55"/>
@@ -8928,8 +8931,8 @@
         <v>7</v>
       </c>
       <c r="C11" s="56"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="71" t="s">
+      <c r="D11" s="72"/>
+      <c r="E11" s="70" t="s">
         <v>233</v>
       </c>
       <c r="F11" s="55"/>
@@ -8946,7 +8949,7 @@
       <c r="C12" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="73" t="s">
         <v>179</v>
       </c>
       <c r="E12" s="57"/>
@@ -9559,18 +9562,18 @@
       <c r="F1" s="44"/>
     </row>
     <row r="2" spans="2:14" ht="33.75" customHeight="1">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
     </row>
     <row r="3" spans="2:14" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -9615,292 +9618,292 @@
       </c>
     </row>
     <row r="5" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B5" s="130">
+      <c r="B5" s="129">
         <v>1</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="131"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134" t="s">
+      <c r="D5" s="130"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133" t="s">
         <v>280</v>
       </c>
-      <c r="H5" s="134" t="s">
+      <c r="H5" s="133" t="s">
         <v>281</v>
       </c>
-      <c r="I5" s="135" t="s">
+      <c r="I5" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="135" t="s">
+      <c r="J5" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134" t="s">
+      <c r="K5" s="133"/>
+      <c r="L5" s="133" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B6" s="130">
+      <c r="B6" s="129">
         <v>2</v>
       </c>
-      <c r="C6" s="136"/>
-      <c r="D6" s="131" t="s">
+      <c r="C6" s="135"/>
+      <c r="D6" s="130" t="s">
         <v>376</v>
       </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="134" t="s">
+      <c r="E6" s="131"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="133" t="s">
         <v>377</v>
       </c>
-      <c r="H6" s="134" t="s">
+      <c r="H6" s="133" t="s">
         <v>378</v>
       </c>
-      <c r="I6" s="135" t="s">
+      <c r="I6" s="134" t="s">
         <v>372</v>
       </c>
-      <c r="J6" s="135" t="s">
+      <c r="J6" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="134" t="s">
+      <c r="K6" s="133" t="s">
         <v>379</v>
       </c>
-      <c r="L6" s="134"/>
+      <c r="L6" s="133"/>
     </row>
     <row r="7" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B7" s="130">
+      <c r="B7" s="129">
         <v>3</v>
       </c>
-      <c r="C7" s="131" t="s">
+      <c r="C7" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="132"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="134" t="s">
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="134" t="s">
+      <c r="H7" s="133" t="s">
         <v>282</v>
       </c>
-      <c r="I7" s="135" t="s">
+      <c r="I7" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="135" t="s">
+      <c r="J7" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="134" t="s">
+      <c r="K7" s="133" t="s">
         <v>259</v>
       </c>
-      <c r="L7" s="134" t="s">
+      <c r="L7" s="133" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B8" s="130">
+      <c r="B8" s="129">
         <v>4</v>
       </c>
-      <c r="C8" s="136"/>
-      <c r="D8" s="131" t="s">
+      <c r="C8" s="135"/>
+      <c r="D8" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="133" t="s">
+      <c r="E8" s="132" t="s">
         <v>267</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="134" t="s">
+      <c r="F8" s="132"/>
+      <c r="G8" s="133" t="s">
         <v>283</v>
       </c>
-      <c r="H8" s="134" t="s">
+      <c r="H8" s="133" t="s">
         <v>285</v>
       </c>
-      <c r="I8" s="135" t="s">
+      <c r="I8" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="135" t="s">
+      <c r="J8" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K8" s="134" t="s">
+      <c r="K8" s="133" t="s">
         <v>264</v>
       </c>
-      <c r="L8" s="134" t="s">
+      <c r="L8" s="133" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B9" s="130">
+      <c r="B9" s="129">
         <v>5</v>
       </c>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="133" t="s">
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="132" t="s">
         <v>263</v>
       </c>
-      <c r="F9" s="133"/>
-      <c r="G9" s="134" t="s">
+      <c r="F9" s="132"/>
+      <c r="G9" s="133" t="s">
         <v>284</v>
       </c>
-      <c r="H9" s="134" t="s">
+      <c r="H9" s="133" t="s">
         <v>286</v>
       </c>
-      <c r="I9" s="135" t="s">
+      <c r="I9" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="135" t="s">
+      <c r="J9" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="134" t="s">
+      <c r="K9" s="133" t="s">
         <v>265</v>
       </c>
-      <c r="L9" s="134" t="s">
+      <c r="L9" s="133" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="10" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B10" s="130">
+      <c r="B10" s="129">
         <v>6</v>
       </c>
-      <c r="C10" s="136"/>
-      <c r="D10" s="131" t="s">
+      <c r="C10" s="135"/>
+      <c r="D10" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="133" t="s">
+      <c r="E10" s="132" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="133"/>
-      <c r="G10" s="134" t="s">
+      <c r="F10" s="132"/>
+      <c r="G10" s="133" t="s">
         <v>287</v>
       </c>
-      <c r="H10" s="134" t="s">
+      <c r="H10" s="133" t="s">
         <v>288</v>
       </c>
-      <c r="I10" s="135" t="s">
+      <c r="I10" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="135" t="s">
+      <c r="J10" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="134" t="s">
+      <c r="K10" s="133" t="s">
         <v>277</v>
       </c>
-      <c r="L10" s="134" t="s">
+      <c r="L10" s="133" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B11" s="130">
+      <c r="B11" s="129">
         <v>7</v>
       </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="133" t="s">
+      <c r="C11" s="135"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="132" t="s">
         <v>269</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="134" t="s">
+      <c r="F11" s="132"/>
+      <c r="G11" s="133" t="s">
         <v>289</v>
       </c>
-      <c r="H11" s="134" t="s">
+      <c r="H11" s="133" t="s">
         <v>292</v>
       </c>
-      <c r="I11" s="135" t="s">
+      <c r="I11" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="135" t="s">
+      <c r="J11" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134" t="s">
+      <c r="K11" s="133"/>
+      <c r="L11" s="133" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="12" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B12" s="130">
+      <c r="B12" s="129">
         <v>8</v>
       </c>
-      <c r="C12" s="136"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="133" t="s">
+      <c r="C12" s="135"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="132" t="s">
         <v>270</v>
       </c>
-      <c r="F12" s="133"/>
-      <c r="G12" s="134" t="s">
+      <c r="F12" s="132"/>
+      <c r="G12" s="133" t="s">
         <v>290</v>
       </c>
-      <c r="H12" s="134" t="s">
+      <c r="H12" s="133" t="s">
         <v>291</v>
       </c>
-      <c r="I12" s="135" t="s">
+      <c r="I12" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="135" t="s">
+      <c r="J12" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="134"/>
-      <c r="L12" s="134" t="s">
+      <c r="K12" s="133"/>
+      <c r="L12" s="133" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="13" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B13" s="130">
+      <c r="B13" s="129">
         <v>9</v>
       </c>
-      <c r="C13" s="136"/>
-      <c r="D13" s="134" t="s">
+      <c r="C13" s="135"/>
+      <c r="D13" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="134" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="133" t="s">
         <v>371</v>
       </c>
-      <c r="H13" s="134" t="s">
+      <c r="H13" s="133" t="s">
         <v>375</v>
       </c>
-      <c r="I13" s="135" t="s">
+      <c r="I13" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="135" t="s">
+      <c r="J13" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="134" t="s">
+      <c r="K13" s="133" t="s">
         <v>373</v>
       </c>
-      <c r="L13" s="134" t="s">
+      <c r="L13" s="133" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="14" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B14" s="130">
+      <c r="B14" s="129">
         <v>10</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="C14" s="130" t="s">
         <v>580</v>
       </c>
-      <c r="D14" s="133" t="s">
+      <c r="D14" s="132" t="s">
         <v>599</v>
       </c>
-      <c r="E14" s="131" t="s">
+      <c r="E14" s="130" t="s">
         <v>589</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="134" t="s">
+      <c r="F14" s="132"/>
+      <c r="G14" s="133" t="s">
         <v>588</v>
       </c>
-      <c r="H14" s="134" t="s">
+      <c r="H14" s="133" t="s">
         <v>581</v>
       </c>
-      <c r="I14" s="135" t="s">
+      <c r="I14" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="135" t="s">
+      <c r="J14" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="134" t="s">
+      <c r="K14" s="133" t="s">
         <v>583</v>
       </c>
-      <c r="L14" s="134" t="s">
+      <c r="L14" s="133" t="s">
         <v>582</v>
       </c>
       <c r="N14" s="60" t="s">
@@ -9908,1596 +9911,1596 @@
       </c>
     </row>
     <row r="15" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B15" s="130">
+      <c r="B15" s="129">
         <v>11</v>
       </c>
-      <c r="C15" s="137"/>
-      <c r="D15" s="132" t="s">
+      <c r="C15" s="136"/>
+      <c r="D15" s="131" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133" t="s">
         <v>344</v>
       </c>
-      <c r="I15" s="135" t="s">
+      <c r="I15" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="135" t="s">
+      <c r="J15" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="134" t="s">
+      <c r="K15" s="133" t="s">
         <v>584</v>
       </c>
-      <c r="L15" s="134"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B16" s="130">
+      <c r="B16" s="129">
         <v>12</v>
       </c>
-      <c r="C16" s="137"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="133" t="s">
+      <c r="C16" s="136"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="132" t="s">
         <v>420</v>
       </c>
-      <c r="F16" s="133"/>
-      <c r="G16" s="134" t="s">
+      <c r="F16" s="132"/>
+      <c r="G16" s="133" t="s">
         <v>389</v>
       </c>
-      <c r="H16" s="134" t="s">
+      <c r="H16" s="133" t="s">
         <v>459</v>
       </c>
-      <c r="I16" s="135" t="s">
+      <c r="I16" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="135" t="s">
+      <c r="J16" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K16" s="134" t="s">
+      <c r="K16" s="133" t="s">
         <v>585</v>
       </c>
-      <c r="L16" s="134"/>
+      <c r="L16" s="133"/>
     </row>
     <row r="17" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B17" s="130">
+      <c r="B17" s="129">
         <v>13</v>
       </c>
-      <c r="C17" s="141"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="133" t="s">
+      <c r="C17" s="140"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="132" t="s">
         <v>421</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="134" t="s">
+      <c r="F17" s="132"/>
+      <c r="G17" s="133" t="s">
         <v>388</v>
       </c>
-      <c r="H17" s="134" t="s">
+      <c r="H17" s="133" t="s">
         <v>460</v>
       </c>
-      <c r="I17" s="135" t="s">
+      <c r="I17" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="135" t="s">
+      <c r="J17" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="134" t="s">
+      <c r="K17" s="133" t="s">
         <v>586</v>
       </c>
-      <c r="L17" s="134"/>
+      <c r="L17" s="133"/>
       <c r="N17" s="60" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="18" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B18" s="130">
+      <c r="B18" s="129">
         <v>14</v>
       </c>
-      <c r="C18" s="137" t="s">
+      <c r="C18" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="137"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134" t="s">
+      <c r="D18" s="136"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="134" t="s">
+      <c r="H18" s="133" t="s">
         <v>293</v>
       </c>
-      <c r="I18" s="135" t="s">
+      <c r="I18" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="135" t="s">
+      <c r="J18" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="134" t="s">
+      <c r="K18" s="133" t="s">
         <v>276</v>
       </c>
-      <c r="L18" s="134" t="s">
+      <c r="L18" s="133" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B19" s="130">
+      <c r="B19" s="129">
         <v>15</v>
       </c>
-      <c r="C19" s="136"/>
-      <c r="D19" s="131" t="s">
+      <c r="C19" s="135"/>
+      <c r="D19" s="130" t="s">
         <v>278</v>
       </c>
-      <c r="E19" s="133" t="s">
+      <c r="E19" s="132" t="s">
         <v>273</v>
       </c>
-      <c r="F19" s="133"/>
-      <c r="G19" s="134" t="s">
+      <c r="F19" s="132"/>
+      <c r="G19" s="133" t="s">
         <v>295</v>
       </c>
-      <c r="H19" s="134" t="s">
+      <c r="H19" s="133" t="s">
         <v>296</v>
       </c>
-      <c r="I19" s="135" t="s">
+      <c r="I19" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="135" t="s">
+      <c r="J19" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="134" t="s">
+      <c r="K19" s="133" t="s">
         <v>277</v>
       </c>
-      <c r="L19" s="134" t="s">
+      <c r="L19" s="133" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="20" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B20" s="130">
+      <c r="B20" s="129">
         <v>16</v>
       </c>
-      <c r="C20" s="136"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="144" t="s">
+      <c r="C20" s="135"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="143" t="s">
         <v>274</v>
       </c>
-      <c r="F20" s="144"/>
-      <c r="G20" s="145" t="s">
+      <c r="F20" s="143"/>
+      <c r="G20" s="144" t="s">
         <v>297</v>
       </c>
-      <c r="H20" s="134" t="s">
+      <c r="H20" s="133" t="s">
         <v>298</v>
       </c>
-      <c r="I20" s="135" t="s">
+      <c r="I20" s="134" t="s">
         <v>382</v>
       </c>
-      <c r="J20" s="135" t="s">
+      <c r="J20" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="134" t="s">
+      <c r="K20" s="133" t="s">
         <v>380</v>
       </c>
-      <c r="L20" s="134" t="s">
+      <c r="L20" s="133" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="21" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B21" s="130">
+      <c r="B21" s="129">
         <v>17</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="144" t="s">
+      <c r="C21" s="135"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="143" t="s">
         <v>381</v>
       </c>
-      <c r="F21" s="144"/>
-      <c r="G21" s="146" t="s">
+      <c r="F21" s="143"/>
+      <c r="G21" s="145" t="s">
         <v>294</v>
       </c>
-      <c r="H21" s="147" t="s">
+      <c r="H21" s="146" t="s">
         <v>300</v>
       </c>
-      <c r="I21" s="135" t="s">
+      <c r="I21" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="135" t="s">
+      <c r="J21" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="134" t="s">
+      <c r="K21" s="133" t="s">
         <v>461</v>
       </c>
-      <c r="L21" s="134" t="s">
+      <c r="L21" s="133" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="22" spans="2:14" s="60" customFormat="1" ht="43.5" customHeight="1">
-      <c r="B22" s="130">
+      <c r="B22" s="129">
         <v>18</v>
       </c>
-      <c r="C22" s="131" t="s">
+      <c r="C22" s="130" t="s">
         <v>279</v>
       </c>
-      <c r="D22" s="143"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="146" t="s">
+      <c r="D22" s="142"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="145" t="s">
         <v>279</v>
       </c>
-      <c r="H22" s="134" t="s">
+      <c r="H22" s="133" t="s">
         <v>299</v>
       </c>
-      <c r="I22" s="135" t="s">
+      <c r="I22" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="135" t="s">
+      <c r="J22" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="134" t="s">
+      <c r="K22" s="133" t="s">
         <v>575</v>
       </c>
-      <c r="L22" s="134" t="s">
+      <c r="L22" s="133" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="23" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="130">
+      <c r="B23" s="129">
         <v>19</v>
       </c>
-      <c r="C23" s="136"/>
-      <c r="D23" s="131" t="s">
+      <c r="C23" s="135"/>
+      <c r="D23" s="130" t="s">
         <v>220</v>
       </c>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="134" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133" t="s">
         <v>362</v>
       </c>
-      <c r="H23" s="134" t="s">
+      <c r="H23" s="133" t="s">
         <v>455</v>
       </c>
-      <c r="I23" s="135" t="s">
+      <c r="I23" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="135" t="s">
+      <c r="J23" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="134" t="s">
+      <c r="K23" s="133" t="s">
         <v>576</v>
       </c>
-      <c r="L23" s="134" t="s">
+      <c r="L23" s="133" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="24" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B24" s="130">
+      <c r="B24" s="129">
         <v>20</v>
       </c>
-      <c r="C24" s="136"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="133" t="s">
+      <c r="C24" s="135"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="132" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="133"/>
-      <c r="G24" s="134" t="s">
+      <c r="F24" s="132"/>
+      <c r="G24" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="H24" s="134" t="s">
+      <c r="H24" s="133" t="s">
         <v>457</v>
       </c>
-      <c r="I24" s="135" t="s">
+      <c r="I24" s="134" t="s">
         <v>454</v>
       </c>
-      <c r="J24" s="135" t="s">
+      <c r="J24" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="134"/>
-      <c r="L24" s="134" t="s">
+      <c r="K24" s="133"/>
+      <c r="L24" s="133" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="25" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B25" s="130">
+      <c r="B25" s="129">
         <v>21</v>
       </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="137" t="s">
+      <c r="C25" s="135"/>
+      <c r="D25" s="136" t="s">
         <v>453</v>
       </c>
-      <c r="E25" s="133" t="s">
+      <c r="E25" s="132" t="s">
         <v>346</v>
       </c>
-      <c r="F25" s="133"/>
-      <c r="G25" s="134" t="s">
+      <c r="F25" s="132"/>
+      <c r="G25" s="133" t="s">
         <v>363</v>
       </c>
-      <c r="H25" s="134" t="s">
+      <c r="H25" s="133" t="s">
         <v>456</v>
       </c>
-      <c r="I25" s="135" t="s">
+      <c r="I25" s="134" t="s">
         <v>454</v>
       </c>
-      <c r="J25" s="135" t="s">
+      <c r="J25" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K25" s="134"/>
-      <c r="L25" s="134" t="s">
+      <c r="K25" s="133"/>
+      <c r="L25" s="133" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="26" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B26" s="130">
+      <c r="B26" s="129">
         <v>22</v>
       </c>
-      <c r="C26" s="136"/>
-      <c r="D26" s="141"/>
-      <c r="E26" s="133" t="s">
+      <c r="C26" s="135"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="132" t="s">
         <v>347</v>
       </c>
-      <c r="F26" s="133"/>
-      <c r="G26" s="134" t="s">
+      <c r="F26" s="132"/>
+      <c r="G26" s="133" t="s">
         <v>364</v>
       </c>
-      <c r="H26" s="134" t="s">
+      <c r="H26" s="133" t="s">
         <v>458</v>
       </c>
-      <c r="I26" s="135" t="s">
+      <c r="I26" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="135" t="s">
+      <c r="J26" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K26" s="134" t="s">
+      <c r="K26" s="133" t="s">
         <v>577</v>
       </c>
-      <c r="L26" s="134" t="s">
+      <c r="L26" s="133" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="27" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B27" s="130">
+      <c r="B27" s="129">
         <v>23</v>
       </c>
-      <c r="C27" s="136"/>
-      <c r="D27" s="137" t="s">
+      <c r="C27" s="135"/>
+      <c r="D27" s="136" t="s">
         <v>462</v>
       </c>
-      <c r="E27" s="133" t="s">
+      <c r="E27" s="132" t="s">
         <v>463</v>
       </c>
-      <c r="F27" s="133"/>
-      <c r="G27" s="134" t="s">
+      <c r="F27" s="132"/>
+      <c r="G27" s="133" t="s">
         <v>465</v>
       </c>
-      <c r="H27" s="134" t="s">
+      <c r="H27" s="133" t="s">
         <v>468</v>
       </c>
-      <c r="I27" s="135" t="s">
+      <c r="I27" s="134" t="s">
         <v>372</v>
       </c>
-      <c r="J27" s="135" t="s">
+      <c r="J27" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K27" s="134" t="s">
+      <c r="K27" s="133" t="s">
         <v>467</v>
       </c>
-      <c r="L27" s="134"/>
+      <c r="L27" s="133"/>
     </row>
     <row r="28" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B28" s="130">
+      <c r="B28" s="187">
         <v>24</v>
       </c>
-      <c r="C28" s="136"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="133" t="s">
+      <c r="C28" s="97"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="121" t="s">
         <v>464</v>
       </c>
-      <c r="F28" s="133"/>
-      <c r="G28" s="134" t="s">
+      <c r="F28" s="121"/>
+      <c r="G28" s="99" t="s">
         <v>466</v>
       </c>
-      <c r="H28" s="134" t="s">
+      <c r="H28" s="99" t="s">
         <v>469</v>
       </c>
-      <c r="I28" s="135" t="s">
+      <c r="I28" s="188" t="s">
         <v>372</v>
       </c>
-      <c r="J28" s="135" t="s">
+      <c r="J28" s="188" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="134" t="s">
+      <c r="K28" s="99" t="s">
         <v>467</v>
       </c>
-      <c r="L28" s="134"/>
+      <c r="L28" s="99"/>
     </row>
     <row r="29" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B29" s="130">
+      <c r="B29" s="129">
         <v>25</v>
       </c>
-      <c r="C29" s="137"/>
-      <c r="D29" s="144" t="s">
+      <c r="C29" s="136"/>
+      <c r="D29" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="134" t="s">
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="133" t="s">
         <v>360</v>
       </c>
-      <c r="H29" s="134" t="s">
+      <c r="H29" s="133" t="s">
         <v>342</v>
       </c>
-      <c r="I29" s="135" t="s">
+      <c r="I29" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="135" t="s">
+      <c r="J29" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K29" s="134" t="s">
+      <c r="K29" s="133" t="s">
         <v>222</v>
       </c>
-      <c r="L29" s="134" t="s">
+      <c r="L29" s="133" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="30" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B30" s="130">
+      <c r="B30" s="129">
         <v>26</v>
       </c>
-      <c r="C30" s="137"/>
-      <c r="D30" s="133" t="s">
+      <c r="C30" s="136"/>
+      <c r="D30" s="132" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="134" t="s">
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="133" t="s">
         <v>361</v>
       </c>
-      <c r="H30" s="134" t="s">
+      <c r="H30" s="133" t="s">
         <v>343</v>
       </c>
-      <c r="I30" s="135" t="s">
+      <c r="I30" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="135" t="s">
+      <c r="J30" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K30" s="148" t="s">
+      <c r="K30" s="147" t="s">
         <v>578</v>
       </c>
-      <c r="L30" s="134" t="s">
+      <c r="L30" s="133" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="0" hidden="1" customHeight="1">
-      <c r="B31" s="130">
+      <c r="B31" s="129">
         <v>27</v>
       </c>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="150"/>
-      <c r="J31" s="150"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="149"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="148"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="148"/>
+      <c r="L31" s="148"/>
     </row>
     <row r="32" spans="2:14" ht="0" hidden="1" customHeight="1">
-      <c r="B32" s="130">
+      <c r="B32" s="129">
         <v>28</v>
       </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="149"/>
-      <c r="H32" s="149"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="149"/>
-      <c r="L32" s="149"/>
+      <c r="C32" s="148"/>
+      <c r="D32" s="148"/>
+      <c r="E32" s="148"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="149"/>
+      <c r="K32" s="148"/>
+      <c r="L32" s="148"/>
     </row>
     <row r="33" spans="2:13" ht="0" hidden="1" customHeight="1">
-      <c r="B33" s="130">
+      <c r="B33" s="129">
         <v>29</v>
       </c>
-      <c r="C33" s="149"/>
-      <c r="D33" s="149"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="149"/>
-      <c r="G33" s="149"/>
-      <c r="H33" s="149"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="149"/>
-      <c r="L33" s="149"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="148"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="149"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="148"/>
+      <c r="L33" s="148"/>
     </row>
     <row r="34" spans="2:13" ht="0" hidden="1" customHeight="1">
-      <c r="B34" s="130">
+      <c r="B34" s="129">
         <v>30</v>
       </c>
-      <c r="C34" s="149"/>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="149"/>
-      <c r="I34" s="150"/>
-      <c r="J34" s="150"/>
-      <c r="K34" s="149"/>
-      <c r="L34" s="149"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="148"/>
+      <c r="E34" s="148"/>
+      <c r="F34" s="148"/>
+      <c r="G34" s="148"/>
+      <c r="H34" s="148"/>
+      <c r="I34" s="149"/>
+      <c r="J34" s="149"/>
+      <c r="K34" s="148"/>
+      <c r="L34" s="148"/>
     </row>
     <row r="35" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="130">
+      <c r="B35" s="129">
         <v>31</v>
       </c>
-      <c r="C35" s="136"/>
-      <c r="D35" s="131" t="s">
+      <c r="C35" s="135"/>
+      <c r="D35" s="130" t="s">
         <v>219</v>
       </c>
-      <c r="E35" s="151" t="s">
+      <c r="E35" s="150" t="s">
         <v>630</v>
       </c>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152" t="s">
+      <c r="F35" s="150"/>
+      <c r="G35" s="151" t="s">
         <v>629</v>
       </c>
-      <c r="H35" s="152" t="s">
+      <c r="H35" s="151" t="s">
         <v>344</v>
       </c>
-      <c r="I35" s="153" t="s">
+      <c r="I35" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="153" t="s">
+      <c r="J35" s="152" t="s">
         <v>86</v>
       </c>
-      <c r="K35" s="152" t="s">
+      <c r="K35" s="151" t="s">
         <v>579</v>
       </c>
-      <c r="L35" s="152" t="s">
+      <c r="L35" s="151" t="s">
         <v>353</v>
       </c>
-      <c r="M35" s="114" t="s">
+      <c r="M35" s="113" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B36" s="130">
+      <c r="B36" s="129">
         <v>32</v>
       </c>
-      <c r="C36" s="136"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="133" t="s">
+      <c r="C36" s="135"/>
+      <c r="D36" s="136"/>
+      <c r="E36" s="132" t="s">
         <v>420</v>
       </c>
-      <c r="F36" s="133"/>
-      <c r="G36" s="134" t="s">
+      <c r="F36" s="132"/>
+      <c r="G36" s="133" t="s">
         <v>389</v>
       </c>
-      <c r="H36" s="134" t="s">
+      <c r="H36" s="133" t="s">
         <v>459</v>
       </c>
-      <c r="I36" s="135" t="s">
+      <c r="I36" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="135" t="s">
+      <c r="J36" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K36" s="134"/>
-      <c r="L36" s="134" t="s">
+      <c r="K36" s="133"/>
+      <c r="L36" s="133" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="37" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B37" s="130">
+      <c r="B37" s="129">
         <v>33</v>
       </c>
-      <c r="C37" s="136"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="133" t="s">
+      <c r="C37" s="135"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="132" t="s">
         <v>421</v>
       </c>
-      <c r="F37" s="133"/>
-      <c r="G37" s="134" t="s">
+      <c r="F37" s="132"/>
+      <c r="G37" s="133" t="s">
         <v>388</v>
       </c>
-      <c r="H37" s="134" t="s">
+      <c r="H37" s="133" t="s">
         <v>460</v>
       </c>
-      <c r="I37" s="135" t="s">
+      <c r="I37" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="135" t="s">
+      <c r="J37" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K37" s="134"/>
-      <c r="L37" s="134" t="s">
+      <c r="K37" s="133"/>
+      <c r="L37" s="133" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="38" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B38" s="130">
+      <c r="B38" s="129">
         <v>34</v>
       </c>
-      <c r="C38" s="141"/>
-      <c r="D38" s="144" t="s">
+      <c r="C38" s="140"/>
+      <c r="D38" s="143" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="133"/>
-      <c r="F38" s="133"/>
-      <c r="G38" s="134" t="s">
+      <c r="E38" s="132"/>
+      <c r="F38" s="132"/>
+      <c r="G38" s="133" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="134" t="s">
+      <c r="H38" s="133" t="s">
         <v>345</v>
       </c>
-      <c r="I38" s="135" t="s">
+      <c r="I38" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J38" s="135" t="s">
+      <c r="J38" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K38" s="134" t="s">
+      <c r="K38" s="133" t="s">
         <v>587</v>
       </c>
-      <c r="L38" s="134" t="s">
+      <c r="L38" s="133" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B39" s="130">
+      <c r="B39" s="129">
         <v>35</v>
       </c>
-      <c r="C39" s="142" t="s">
+      <c r="C39" s="141" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="141" t="s">
+      <c r="D39" s="140" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="134"/>
-      <c r="F39" s="134"/>
-      <c r="G39" s="134" t="s">
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133" t="s">
         <v>301</v>
       </c>
-      <c r="H39" s="134" t="s">
+      <c r="H39" s="133" t="s">
         <v>302</v>
       </c>
-      <c r="I39" s="135" t="s">
+      <c r="I39" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="135"/>
-      <c r="K39" s="134"/>
-      <c r="L39" s="134" t="s">
+      <c r="J39" s="134"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B40" s="130">
+      <c r="B40" s="129">
         <v>36</v>
       </c>
-      <c r="C40" s="136"/>
-      <c r="D40" s="134" t="s">
+      <c r="C40" s="135"/>
+      <c r="D40" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="E40" s="134"/>
-      <c r="F40" s="134"/>
-      <c r="G40" s="134" t="s">
+      <c r="E40" s="133"/>
+      <c r="F40" s="133"/>
+      <c r="G40" s="133" t="s">
         <v>303</v>
       </c>
-      <c r="H40" s="134" t="s">
+      <c r="H40" s="133" t="s">
         <v>304</v>
       </c>
-      <c r="I40" s="135" t="s">
+      <c r="I40" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J40" s="135"/>
-      <c r="K40" s="134"/>
-      <c r="L40" s="134" t="s">
+      <c r="J40" s="134"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="133" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B41" s="130">
+      <c r="B41" s="129">
         <v>37</v>
       </c>
-      <c r="C41" s="136"/>
-      <c r="D41" s="134" t="s">
+      <c r="C41" s="135"/>
+      <c r="D41" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="134"/>
-      <c r="F41" s="134"/>
-      <c r="G41" s="134" t="s">
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="134" t="s">
+      <c r="H41" s="133" t="s">
         <v>305</v>
       </c>
-      <c r="I41" s="135" t="s">
+      <c r="I41" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J41" s="135"/>
-      <c r="K41" s="134"/>
-      <c r="L41" s="134" t="s">
+      <c r="J41" s="134"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="42" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B42" s="130">
+      <c r="B42" s="129">
         <v>38</v>
       </c>
-      <c r="C42" s="136"/>
-      <c r="D42" s="134" t="s">
+      <c r="C42" s="135"/>
+      <c r="D42" s="133" t="s">
         <v>367</v>
       </c>
-      <c r="E42" s="134"/>
-      <c r="F42" s="134"/>
-      <c r="G42" s="134" t="s">
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="133" t="s">
         <v>368</v>
       </c>
-      <c r="H42" s="134" t="s">
+      <c r="H42" s="133" t="s">
         <v>306</v>
       </c>
-      <c r="I42" s="135" t="s">
+      <c r="I42" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="135"/>
-      <c r="K42" s="134" t="s">
+      <c r="J42" s="134"/>
+      <c r="K42" s="133" t="s">
         <v>369</v>
       </c>
-      <c r="L42" s="134" t="s">
+      <c r="L42" s="133" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="43" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B43" s="130">
+      <c r="B43" s="129">
         <v>39</v>
       </c>
-      <c r="C43" s="136"/>
-      <c r="D43" s="134" t="s">
+      <c r="C43" s="135"/>
+      <c r="D43" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="134"/>
-      <c r="F43" s="134"/>
-      <c r="G43" s="134" t="s">
+      <c r="E43" s="133"/>
+      <c r="F43" s="133"/>
+      <c r="G43" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="H43" s="134" t="s">
+      <c r="H43" s="133" t="s">
         <v>307</v>
       </c>
-      <c r="I43" s="135" t="s">
+      <c r="I43" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J43" s="135"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134" t="s">
+      <c r="J43" s="134"/>
+      <c r="K43" s="133"/>
+      <c r="L43" s="133" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="44" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B44" s="130">
+      <c r="B44" s="129">
         <v>40</v>
       </c>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="141" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="134" t="s">
+      <c r="D44" s="133" t="s">
         <v>470</v>
       </c>
-      <c r="E44" s="134"/>
-      <c r="F44" s="134"/>
-      <c r="G44" s="134" t="s">
+      <c r="E44" s="133"/>
+      <c r="F44" s="133"/>
+      <c r="G44" s="133" t="s">
         <v>474</v>
       </c>
-      <c r="H44" s="134" t="s">
+      <c r="H44" s="133" t="s">
         <v>314</v>
       </c>
-      <c r="I44" s="135" t="s">
+      <c r="I44" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J44" s="135" t="s">
+      <c r="J44" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K44" s="134"/>
-      <c r="L44" s="134" t="s">
+      <c r="K44" s="133"/>
+      <c r="L44" s="133" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="45" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B45" s="130">
+      <c r="B45" s="129">
         <v>41</v>
       </c>
-      <c r="C45" s="136"/>
-      <c r="D45" s="134" t="s">
+      <c r="C45" s="135"/>
+      <c r="D45" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="E45" s="134"/>
-      <c r="F45" s="134"/>
-      <c r="G45" s="134" t="s">
+      <c r="E45" s="133"/>
+      <c r="F45" s="133"/>
+      <c r="G45" s="133" t="s">
         <v>475</v>
       </c>
-      <c r="H45" s="134" t="s">
+      <c r="H45" s="133" t="s">
         <v>315</v>
       </c>
-      <c r="I45" s="135" t="s">
+      <c r="I45" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="135" t="s">
+      <c r="J45" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K45" s="134" t="s">
+      <c r="K45" s="133" t="s">
         <v>419</v>
       </c>
-      <c r="L45" s="134" t="s">
+      <c r="L45" s="133" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="46" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B46" s="130">
+      <c r="B46" s="129">
         <v>42</v>
       </c>
-      <c r="C46" s="136"/>
-      <c r="D46" s="134" t="s">
+      <c r="C46" s="135"/>
+      <c r="D46" s="133" t="s">
         <v>471</v>
       </c>
-      <c r="E46" s="134"/>
-      <c r="F46" s="134"/>
-      <c r="G46" s="134" t="s">
+      <c r="E46" s="133"/>
+      <c r="F46" s="133"/>
+      <c r="G46" s="133" t="s">
         <v>476</v>
       </c>
-      <c r="H46" s="134" t="s">
+      <c r="H46" s="133" t="s">
         <v>316</v>
       </c>
-      <c r="I46" s="135" t="s">
+      <c r="I46" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J46" s="135" t="s">
+      <c r="J46" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K46" s="134" t="s">
+      <c r="K46" s="133" t="s">
         <v>419</v>
       </c>
-      <c r="L46" s="134" t="s">
+      <c r="L46" s="133" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="47" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B47" s="130">
+      <c r="B47" s="129">
         <v>43</v>
       </c>
-      <c r="C47" s="136"/>
-      <c r="D47" s="131" t="s">
+      <c r="C47" s="135"/>
+      <c r="D47" s="130" t="s">
         <v>472</v>
       </c>
-      <c r="E47" s="134"/>
-      <c r="F47" s="134"/>
-      <c r="G47" s="134" t="s">
+      <c r="E47" s="133"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="133" t="s">
         <v>477</v>
       </c>
-      <c r="H47" s="134" t="s">
+      <c r="H47" s="133" t="s">
         <v>317</v>
       </c>
-      <c r="I47" s="135" t="s">
+      <c r="I47" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J47" s="135" t="s">
+      <c r="J47" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="134" t="s">
+      <c r="K47" s="133" t="s">
         <v>419</v>
       </c>
-      <c r="L47" s="134" t="s">
+      <c r="L47" s="133" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="48" spans="2:13" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B48" s="130">
+      <c r="B48" s="129">
         <v>44</v>
       </c>
-      <c r="C48" s="136"/>
-      <c r="D48" s="131" t="s">
+      <c r="C48" s="135"/>
+      <c r="D48" s="130" t="s">
         <v>473</v>
       </c>
-      <c r="E48" s="134"/>
-      <c r="F48" s="134"/>
-      <c r="G48" s="134" t="s">
+      <c r="E48" s="133"/>
+      <c r="F48" s="133"/>
+      <c r="G48" s="133" t="s">
         <v>478</v>
       </c>
-      <c r="H48" s="134" t="s">
+      <c r="H48" s="133" t="s">
         <v>354</v>
       </c>
-      <c r="I48" s="135" t="s">
+      <c r="I48" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="135" t="s">
+      <c r="J48" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="134" t="s">
+      <c r="K48" s="133" t="s">
         <v>419</v>
       </c>
-      <c r="L48" s="134" t="s">
+      <c r="L48" s="133" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="49" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B49" s="130">
+      <c r="B49" s="129">
         <v>45</v>
       </c>
-      <c r="C49" s="142" t="s">
+      <c r="C49" s="141" t="s">
         <v>215</v>
       </c>
-      <c r="D49" s="134" t="s">
+      <c r="D49" s="133" t="s">
         <v>179</v>
       </c>
-      <c r="E49" s="133"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="134" t="s">
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="133" t="s">
         <v>179</v>
       </c>
-      <c r="H49" s="134" t="s">
+      <c r="H49" s="133" t="s">
         <v>308</v>
       </c>
-      <c r="I49" s="135" t="s">
+      <c r="I49" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="135" t="s">
+      <c r="J49" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K49" s="134" t="s">
+      <c r="K49" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="L49" s="134" t="s">
+      <c r="L49" s="133" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="50" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B50" s="130">
+      <c r="B50" s="129">
         <v>46</v>
       </c>
-      <c r="C50" s="136"/>
-      <c r="D50" s="134" t="s">
+      <c r="C50" s="135"/>
+      <c r="D50" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="E50" s="133"/>
-      <c r="F50" s="133"/>
-      <c r="G50" s="134" t="s">
+      <c r="E50" s="132"/>
+      <c r="F50" s="132"/>
+      <c r="G50" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="134" t="s">
+      <c r="H50" s="133" t="s">
         <v>309</v>
       </c>
-      <c r="I50" s="135" t="s">
+      <c r="I50" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J50" s="135" t="s">
+      <c r="J50" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K50" s="134" t="s">
+      <c r="K50" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="L50" s="134"/>
+      <c r="L50" s="133"/>
     </row>
     <row r="51" spans="2:12" s="60" customFormat="1" ht="31.5" customHeight="1">
-      <c r="B51" s="130">
+      <c r="B51" s="129">
         <v>47</v>
       </c>
-      <c r="C51" s="136"/>
-      <c r="D51" s="131" t="s">
+      <c r="C51" s="135"/>
+      <c r="D51" s="130" t="s">
         <v>181</v>
       </c>
-      <c r="E51" s="133"/>
-      <c r="F51" s="133"/>
-      <c r="G51" s="134" t="s">
+      <c r="E51" s="132"/>
+      <c r="F51" s="132"/>
+      <c r="G51" s="133" t="s">
         <v>312</v>
       </c>
-      <c r="H51" s="134" t="s">
+      <c r="H51" s="133" t="s">
         <v>310</v>
       </c>
-      <c r="I51" s="135" t="s">
+      <c r="I51" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J51" s="135" t="s">
+      <c r="J51" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K51" s="134" t="s">
+      <c r="K51" s="133" t="s">
         <v>399</v>
       </c>
-      <c r="L51" s="134" t="s">
+      <c r="L51" s="133" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="52" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B52" s="130">
+      <c r="B52" s="129">
         <v>48</v>
       </c>
-      <c r="C52" s="136"/>
-      <c r="D52" s="131" t="s">
+      <c r="C52" s="135"/>
+      <c r="D52" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="E52" s="132"/>
-      <c r="F52" s="131"/>
-      <c r="G52" s="131" t="s">
+      <c r="E52" s="131"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="130" t="s">
         <v>313</v>
       </c>
-      <c r="H52" s="134" t="s">
+      <c r="H52" s="133" t="s">
         <v>311</v>
       </c>
-      <c r="I52" s="154" t="s">
+      <c r="I52" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J52" s="135" t="s">
+      <c r="J52" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K52" s="131" t="s">
+      <c r="K52" s="130" t="s">
         <v>405</v>
       </c>
-      <c r="L52" s="131" t="s">
+      <c r="L52" s="130" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="53" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B53" s="130">
+      <c r="B53" s="129">
         <v>49</v>
       </c>
-      <c r="C53" s="136"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="132" t="s">
+      <c r="C53" s="135"/>
+      <c r="D53" s="140"/>
+      <c r="E53" s="131" t="s">
         <v>400</v>
       </c>
-      <c r="F53" s="131"/>
-      <c r="G53" s="131" t="s">
+      <c r="F53" s="130"/>
+      <c r="G53" s="130" t="s">
         <v>401</v>
       </c>
-      <c r="H53" s="134" t="s">
+      <c r="H53" s="133" t="s">
         <v>402</v>
       </c>
-      <c r="I53" s="154" t="s">
+      <c r="I53" s="153" t="s">
         <v>403</v>
       </c>
-      <c r="J53" s="135" t="s">
+      <c r="J53" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K53" s="131" t="s">
+      <c r="K53" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="L53" s="131"/>
+      <c r="L53" s="130"/>
     </row>
     <row r="54" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B54" s="130">
+      <c r="B54" s="129">
         <v>50</v>
       </c>
-      <c r="C54" s="136"/>
-      <c r="D54" s="137" t="s">
+      <c r="C54" s="135"/>
+      <c r="D54" s="136" t="s">
         <v>395</v>
       </c>
-      <c r="E54" s="131"/>
-      <c r="F54" s="131"/>
-      <c r="G54" s="131" t="s">
+      <c r="E54" s="130"/>
+      <c r="F54" s="130"/>
+      <c r="G54" s="130" t="s">
         <v>395</v>
       </c>
-      <c r="H54" s="134" t="s">
+      <c r="H54" s="133" t="s">
         <v>393</v>
       </c>
-      <c r="I54" s="154" t="s">
+      <c r="I54" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J54" s="135" t="s">
+      <c r="J54" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="131" t="s">
+      <c r="K54" s="130" t="s">
         <v>394</v>
       </c>
-      <c r="L54" s="131" t="s">
+      <c r="L54" s="130" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="55" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B55" s="130">
+      <c r="B55" s="129">
         <v>51</v>
       </c>
-      <c r="C55" s="142" t="s">
+      <c r="C55" s="141" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="131" t="s">
+      <c r="D55" s="130" t="s">
         <v>185</v>
       </c>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="131" t="s">
+      <c r="E55" s="130"/>
+      <c r="F55" s="130"/>
+      <c r="G55" s="130" t="s">
         <v>318</v>
       </c>
-      <c r="H55" s="131" t="s">
+      <c r="H55" s="130" t="s">
         <v>321</v>
       </c>
-      <c r="I55" s="154" t="s">
+      <c r="I55" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J55" s="154"/>
-      <c r="K55" s="131"/>
-      <c r="L55" s="131" t="s">
+      <c r="J55" s="153"/>
+      <c r="K55" s="130"/>
+      <c r="L55" s="130" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="56" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B56" s="130">
+      <c r="B56" s="129">
         <v>52</v>
       </c>
-      <c r="C56" s="136"/>
-      <c r="D56" s="131" t="s">
+      <c r="C56" s="135"/>
+      <c r="D56" s="130" t="s">
         <v>187</v>
       </c>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="131" t="s">
+      <c r="E56" s="130"/>
+      <c r="F56" s="130"/>
+      <c r="G56" s="130" t="s">
         <v>319</v>
       </c>
-      <c r="H56" s="131" t="s">
+      <c r="H56" s="130" t="s">
         <v>322</v>
       </c>
-      <c r="I56" s="154" t="s">
+      <c r="I56" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J56" s="135" t="s">
+      <c r="J56" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K56" s="131" t="s">
+      <c r="K56" s="130" t="s">
         <v>366</v>
       </c>
-      <c r="L56" s="131" t="s">
+      <c r="L56" s="130" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="57" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B57" s="130">
+      <c r="B57" s="129">
         <v>53</v>
       </c>
-      <c r="C57" s="136"/>
-      <c r="D57" s="131" t="s">
+      <c r="C57" s="135"/>
+      <c r="D57" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="E57" s="131"/>
-      <c r="F57" s="131"/>
-      <c r="G57" s="131" t="s">
+      <c r="E57" s="130"/>
+      <c r="F57" s="130"/>
+      <c r="G57" s="130" t="s">
         <v>320</v>
       </c>
-      <c r="H57" s="131" t="s">
+      <c r="H57" s="130" t="s">
         <v>323</v>
       </c>
-      <c r="I57" s="154" t="s">
+      <c r="I57" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J57" s="154"/>
-      <c r="K57" s="131"/>
-      <c r="L57" s="131" t="s">
+      <c r="J57" s="153"/>
+      <c r="K57" s="130"/>
+      <c r="L57" s="130" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="58" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B58" s="130">
+      <c r="B58" s="129">
         <v>54</v>
       </c>
-      <c r="C58" s="136"/>
-      <c r="D58" s="134" t="s">
+      <c r="C58" s="135"/>
+      <c r="D58" s="133" t="s">
         <v>216</v>
       </c>
-      <c r="E58" s="131"/>
-      <c r="F58" s="131"/>
-      <c r="G58" s="131" t="s">
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="130" t="s">
         <v>216</v>
       </c>
-      <c r="H58" s="131" t="s">
+      <c r="H58" s="130" t="s">
         <v>324</v>
       </c>
-      <c r="I58" s="154" t="s">
+      <c r="I58" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J58" s="154"/>
-      <c r="K58" s="131"/>
-      <c r="L58" s="131" t="s">
+      <c r="J58" s="153"/>
+      <c r="K58" s="130"/>
+      <c r="L58" s="130" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B59" s="53">
+      <c r="B59" s="129">
         <v>55</v>
       </c>
-      <c r="C59" s="98"/>
-      <c r="D59" s="61" t="s">
+      <c r="C59" s="135"/>
+      <c r="D59" s="130" t="s">
         <v>416</v>
       </c>
-      <c r="E59" s="75"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61" t="s">
+      <c r="E59" s="131"/>
+      <c r="F59" s="131"/>
+      <c r="G59" s="130"/>
+      <c r="H59" s="130" t="s">
         <v>417</v>
       </c>
-      <c r="I59" s="70" t="s">
+      <c r="I59" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="J59" s="68" t="s">
+      <c r="J59" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="61" t="s">
+      <c r="K59" s="130" t="s">
         <v>418</v>
       </c>
-      <c r="L59" s="61"/>
+      <c r="L59" s="130"/>
     </row>
     <row r="60" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B60" s="130">
+      <c r="B60" s="129">
         <v>56</v>
       </c>
-      <c r="C60" s="142" t="s">
+      <c r="C60" s="141" t="s">
         <v>218</v>
       </c>
-      <c r="D60" s="131" t="s">
+      <c r="D60" s="130" t="s">
         <v>325</v>
       </c>
-      <c r="E60" s="133"/>
-      <c r="F60" s="133"/>
-      <c r="G60" s="134" t="s">
+      <c r="E60" s="132"/>
+      <c r="F60" s="132"/>
+      <c r="G60" s="133" t="s">
         <v>325</v>
       </c>
-      <c r="H60" s="134" t="s">
+      <c r="H60" s="133" t="s">
         <v>327</v>
       </c>
-      <c r="I60" s="135" t="s">
+      <c r="I60" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J60" s="135" t="s">
+      <c r="J60" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K60" s="134"/>
-      <c r="L60" s="134" t="s">
+      <c r="K60" s="133"/>
+      <c r="L60" s="133" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B61" s="130">
+      <c r="B61" s="129">
         <v>57</v>
       </c>
-      <c r="C61" s="136"/>
-      <c r="D61" s="137"/>
-      <c r="E61" s="133" t="s">
+      <c r="C61" s="135"/>
+      <c r="D61" s="136"/>
+      <c r="E61" s="132" t="s">
         <v>326</v>
       </c>
-      <c r="F61" s="133"/>
-      <c r="G61" s="134" t="s">
+      <c r="F61" s="132"/>
+      <c r="G61" s="133" t="s">
         <v>329</v>
       </c>
-      <c r="H61" s="134" t="s">
+      <c r="H61" s="133" t="s">
         <v>328</v>
       </c>
-      <c r="I61" s="135" t="s">
+      <c r="I61" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J61" s="135" t="s">
+      <c r="J61" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K61" s="134"/>
-      <c r="L61" s="134" t="s">
+      <c r="K61" s="133"/>
+      <c r="L61" s="133" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="62" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B62" s="130">
+      <c r="B62" s="129">
         <v>58</v>
       </c>
-      <c r="C62" s="136"/>
-      <c r="D62" s="131" t="s">
+      <c r="C62" s="135"/>
+      <c r="D62" s="130" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="133"/>
-      <c r="F62" s="133"/>
-      <c r="G62" s="134" t="s">
+      <c r="E62" s="132"/>
+      <c r="F62" s="132"/>
+      <c r="G62" s="133" t="s">
         <v>330</v>
       </c>
-      <c r="H62" s="134" t="s">
+      <c r="H62" s="133" t="s">
         <v>332</v>
       </c>
-      <c r="I62" s="135" t="s">
+      <c r="I62" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J62" s="135" t="s">
+      <c r="J62" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K62" s="134"/>
-      <c r="L62" s="134" t="s">
+      <c r="K62" s="133"/>
+      <c r="L62" s="133" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="63" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B63" s="130">
+      <c r="B63" s="129">
         <v>59</v>
       </c>
-      <c r="C63" s="136"/>
-      <c r="D63" s="137"/>
-      <c r="E63" s="133" t="s">
+      <c r="C63" s="135"/>
+      <c r="D63" s="136"/>
+      <c r="E63" s="132" t="s">
         <v>189</v>
       </c>
-      <c r="F63" s="133"/>
-      <c r="G63" s="134" t="s">
+      <c r="F63" s="132"/>
+      <c r="G63" s="133" t="s">
         <v>331</v>
       </c>
-      <c r="H63" s="134" t="s">
+      <c r="H63" s="133" t="s">
         <v>333</v>
       </c>
-      <c r="I63" s="135" t="s">
+      <c r="I63" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J63" s="135" t="s">
+      <c r="J63" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K63" s="134"/>
-      <c r="L63" s="134" t="s">
+      <c r="K63" s="133"/>
+      <c r="L63" s="133" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="64" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B64" s="130">
+      <c r="B64" s="129">
         <v>60</v>
       </c>
-      <c r="C64" s="131" t="s">
+      <c r="C64" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="133" t="s">
+      <c r="D64" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="E64" s="134"/>
-      <c r="F64" s="134"/>
-      <c r="G64" s="134" t="s">
+      <c r="E64" s="133"/>
+      <c r="F64" s="133"/>
+      <c r="G64" s="133" t="s">
         <v>335</v>
       </c>
-      <c r="H64" s="134" t="s">
+      <c r="H64" s="133" t="s">
         <v>334</v>
       </c>
-      <c r="I64" s="135" t="s">
+      <c r="I64" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="135"/>
-      <c r="K64" s="134"/>
-      <c r="L64" s="134" t="s">
+      <c r="J64" s="134"/>
+      <c r="K64" s="133"/>
+      <c r="L64" s="133" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="65" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B65" s="130">
+      <c r="B65" s="129">
         <v>61</v>
       </c>
-      <c r="C65" s="137"/>
-      <c r="D65" s="133" t="s">
+      <c r="C65" s="136"/>
+      <c r="D65" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="134"/>
-      <c r="F65" s="134"/>
-      <c r="G65" s="134" t="s">
+      <c r="E65" s="133"/>
+      <c r="F65" s="133"/>
+      <c r="G65" s="133" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="134" t="s">
+      <c r="H65" s="133" t="s">
         <v>406</v>
       </c>
-      <c r="I65" s="135" t="s">
+      <c r="I65" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J65" s="135"/>
-      <c r="K65" s="134"/>
-      <c r="L65" s="134" t="s">
+      <c r="J65" s="134"/>
+      <c r="K65" s="133"/>
+      <c r="L65" s="133" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="66" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B66" s="130">
+      <c r="B66" s="129">
         <v>62</v>
       </c>
-      <c r="C66" s="137"/>
-      <c r="D66" s="133" t="s">
+      <c r="C66" s="136"/>
+      <c r="D66" s="132" t="s">
         <v>226</v>
       </c>
-      <c r="E66" s="134"/>
-      <c r="F66" s="134"/>
-      <c r="G66" s="134" t="s">
+      <c r="E66" s="133"/>
+      <c r="F66" s="133"/>
+      <c r="G66" s="133" t="s">
         <v>336</v>
       </c>
-      <c r="H66" s="134" t="s">
+      <c r="H66" s="133" t="s">
         <v>409</v>
       </c>
-      <c r="I66" s="135" t="s">
+      <c r="I66" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J66" s="135"/>
-      <c r="K66" s="134"/>
-      <c r="L66" s="134" t="s">
+      <c r="J66" s="134"/>
+      <c r="K66" s="133"/>
+      <c r="L66" s="133" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="67" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B67" s="53">
+      <c r="B67" s="129">
         <v>63</v>
       </c>
-      <c r="C67" s="99"/>
-      <c r="D67" s="62" t="s">
+      <c r="C67" s="136"/>
+      <c r="D67" s="132" t="s">
         <v>407</v>
       </c>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58" t="s">
+      <c r="E67" s="133"/>
+      <c r="F67" s="133"/>
+      <c r="G67" s="133" t="s">
         <v>408</v>
       </c>
-      <c r="H67" s="58" t="s">
+      <c r="H67" s="133" t="s">
         <v>410</v>
       </c>
-      <c r="I67" s="68" t="s">
+      <c r="I67" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J67" s="68" t="s">
+      <c r="J67" s="134" t="s">
         <v>412</v>
       </c>
-      <c r="K67" s="58" t="s">
+      <c r="K67" s="133" t="s">
         <v>413</v>
       </c>
-      <c r="L67" s="58" t="s">
+      <c r="L67" s="133" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="68" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B68" s="130">
+      <c r="B68" s="129">
         <v>64</v>
       </c>
-      <c r="C68" s="137"/>
-      <c r="D68" s="133" t="s">
+      <c r="C68" s="136"/>
+      <c r="D68" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="E68" s="134"/>
-      <c r="F68" s="134"/>
-      <c r="G68" s="134"/>
-      <c r="H68" s="134"/>
-      <c r="I68" s="138" t="s">
+      <c r="E68" s="133"/>
+      <c r="F68" s="133"/>
+      <c r="G68" s="133"/>
+      <c r="H68" s="133"/>
+      <c r="I68" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="J68" s="138"/>
-      <c r="K68" s="139" t="s">
+      <c r="J68" s="137"/>
+      <c r="K68" s="138" t="s">
         <v>76</v>
       </c>
-      <c r="L68" s="134"/>
+      <c r="L68" s="133"/>
     </row>
     <row r="69" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B69" s="130">
+      <c r="B69" s="129">
         <v>65</v>
       </c>
-      <c r="C69" s="137"/>
-      <c r="D69" s="133" t="s">
+      <c r="C69" s="136"/>
+      <c r="D69" s="132" t="s">
         <v>205</v>
       </c>
-      <c r="E69" s="134"/>
-      <c r="F69" s="134"/>
-      <c r="G69" s="134"/>
-      <c r="H69" s="134"/>
-      <c r="I69" s="138" t="s">
+      <c r="E69" s="133"/>
+      <c r="F69" s="133"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="133"/>
+      <c r="I69" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="J69" s="138"/>
-      <c r="K69" s="134" t="s">
+      <c r="J69" s="137"/>
+      <c r="K69" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="L69" s="134"/>
+      <c r="L69" s="133"/>
     </row>
     <row r="70" spans="2:12" s="60" customFormat="1" ht="34.5" customHeight="1">
-      <c r="B70" s="130">
+      <c r="B70" s="129">
         <v>66</v>
       </c>
-      <c r="C70" s="137"/>
-      <c r="D70" s="133" t="s">
+      <c r="C70" s="136"/>
+      <c r="D70" s="132" t="s">
         <v>207</v>
       </c>
-      <c r="E70" s="134"/>
-      <c r="F70" s="134"/>
-      <c r="G70" s="134" t="s">
+      <c r="E70" s="133"/>
+      <c r="F70" s="133"/>
+      <c r="G70" s="133" t="s">
         <v>340</v>
       </c>
-      <c r="H70" s="134" t="s">
+      <c r="H70" s="133" t="s">
         <v>411</v>
       </c>
-      <c r="I70" s="140" t="s">
+      <c r="I70" s="139" t="s">
         <v>339</v>
       </c>
-      <c r="J70" s="135" t="s">
+      <c r="J70" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="K70" s="134" t="s">
+      <c r="K70" s="133" t="s">
         <v>341</v>
       </c>
-      <c r="L70" s="134"/>
+      <c r="L70" s="133"/>
     </row>
     <row r="71" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B71" s="130">
+      <c r="B71" s="129">
         <v>67</v>
       </c>
-      <c r="C71" s="137"/>
-      <c r="D71" s="133" t="s">
+      <c r="C71" s="136"/>
+      <c r="D71" s="132" t="s">
         <v>79</v>
       </c>
-      <c r="E71" s="134"/>
-      <c r="F71" s="134"/>
-      <c r="G71" s="134"/>
-      <c r="H71" s="134"/>
-      <c r="I71" s="138" t="s">
+      <c r="E71" s="133"/>
+      <c r="F71" s="133"/>
+      <c r="G71" s="133"/>
+      <c r="H71" s="133"/>
+      <c r="I71" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="J71" s="138"/>
-      <c r="K71" s="139" t="s">
+      <c r="J71" s="137"/>
+      <c r="K71" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="L71" s="134"/>
+      <c r="L71" s="133"/>
     </row>
     <row r="72" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B72" s="130">
+      <c r="B72" s="129">
         <v>68</v>
       </c>
-      <c r="C72" s="137"/>
-      <c r="D72" s="133" t="s">
+      <c r="C72" s="136"/>
+      <c r="D72" s="132" t="s">
         <v>606</v>
       </c>
-      <c r="E72" s="134"/>
-      <c r="F72" s="134"/>
-      <c r="G72" s="134"/>
-      <c r="H72" s="134"/>
-      <c r="I72" s="138" t="s">
+      <c r="E72" s="133"/>
+      <c r="F72" s="133"/>
+      <c r="G72" s="133"/>
+      <c r="H72" s="133"/>
+      <c r="I72" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="J72" s="138"/>
-      <c r="K72" s="139" t="s">
+      <c r="J72" s="137"/>
+      <c r="K72" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="L72" s="134"/>
+      <c r="L72" s="133"/>
     </row>
     <row r="73" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B73" s="130">
+      <c r="B73" s="129">
         <v>69</v>
       </c>
-      <c r="C73" s="141"/>
-      <c r="D73" s="133" t="s">
+      <c r="C73" s="140"/>
+      <c r="D73" s="132" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="134"/>
-      <c r="F73" s="134"/>
-      <c r="G73" s="134"/>
-      <c r="H73" s="134"/>
-      <c r="I73" s="138" t="s">
+      <c r="E73" s="133"/>
+      <c r="F73" s="133"/>
+      <c r="G73" s="133"/>
+      <c r="H73" s="133"/>
+      <c r="I73" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="J73" s="138"/>
-      <c r="K73" s="139" t="s">
+      <c r="J73" s="137"/>
+      <c r="K73" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="L73" s="134"/>
+      <c r="L73" s="133"/>
     </row>
     <row r="74" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B74" s="130">
+      <c r="B74" s="129">
         <v>70</v>
       </c>
-      <c r="C74" s="141" t="s">
+      <c r="C74" s="140" t="s">
         <v>223</v>
       </c>
-      <c r="D74" s="133" t="s">
+      <c r="D74" s="132" t="s">
         <v>224</v>
       </c>
-      <c r="E74" s="134"/>
-      <c r="F74" s="134"/>
-      <c r="G74" s="134" t="s">
+      <c r="E74" s="133"/>
+      <c r="F74" s="133"/>
+      <c r="G74" s="133" t="s">
         <v>415</v>
       </c>
-      <c r="H74" s="134" t="s">
+      <c r="H74" s="133" t="s">
         <v>337</v>
       </c>
-      <c r="I74" s="135" t="s">
+      <c r="I74" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J74" s="138"/>
-      <c r="K74" s="134" t="s">
+      <c r="J74" s="137"/>
+      <c r="K74" s="133" t="s">
         <v>225</v>
       </c>
-      <c r="L74" s="134"/>
+      <c r="L74" s="133"/>
     </row>
     <row r="75" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B75" s="53">
         <v>71</v>
       </c>
-      <c r="C75" s="100" t="s">
+      <c r="C75" s="99" t="s">
         <v>384</v>
       </c>
       <c r="D75" s="58" t="s">
@@ -11522,7 +11525,7 @@
       <c r="B76" s="53">
         <v>72</v>
       </c>
-      <c r="C76" s="100" t="s">
+      <c r="C76" s="99" t="s">
         <v>384</v>
       </c>
       <c r="D76" s="58" t="s">
@@ -11544,692 +11547,692 @@
       <c r="L76" s="58"/>
     </row>
     <row r="77" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B77" s="77"/>
-      <c r="C77" s="101"/>
-      <c r="I77" s="77"/>
-      <c r="J77" s="77"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="100"/>
+      <c r="I77" s="76"/>
+      <c r="J77" s="76"/>
     </row>
     <row r="78" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B78" s="77"/>
-      <c r="C78" s="101"/>
-      <c r="I78" s="77"/>
-      <c r="J78" s="77"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="100"/>
+      <c r="I78" s="76"/>
+      <c r="J78" s="76"/>
     </row>
     <row r="79" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B79" s="77"/>
-      <c r="C79" s="101"/>
-      <c r="I79" s="77"/>
-      <c r="J79" s="77"/>
+      <c r="B79" s="76"/>
+      <c r="C79" s="100"/>
+      <c r="I79" s="76"/>
+      <c r="J79" s="76"/>
     </row>
     <row r="80" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B80" s="77"/>
-      <c r="C80" s="101"/>
-      <c r="I80" s="77"/>
-      <c r="J80" s="77"/>
+      <c r="B80" s="76"/>
+      <c r="C80" s="100"/>
+      <c r="I80" s="76"/>
+      <c r="J80" s="76"/>
     </row>
     <row r="81" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B81" s="77"/>
-      <c r="C81" s="101"/>
-      <c r="I81" s="77"/>
-      <c r="J81" s="77"/>
+      <c r="B81" s="76"/>
+      <c r="C81" s="100"/>
+      <c r="I81" s="76"/>
+      <c r="J81" s="76"/>
     </row>
     <row r="82" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B82" s="77"/>
-      <c r="C82" s="101"/>
-      <c r="I82" s="77"/>
-      <c r="J82" s="77"/>
+      <c r="B82" s="76"/>
+      <c r="C82" s="100"/>
+      <c r="I82" s="76"/>
+      <c r="J82" s="76"/>
     </row>
     <row r="83" spans="2:10" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B83" s="77"/>
-      <c r="C83" s="101"/>
-      <c r="I83" s="77"/>
-      <c r="J83" s="77"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="100"/>
+      <c r="I83" s="76"/>
+      <c r="J83" s="76"/>
     </row>
     <row r="84" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
-      <c r="B84" s="77"/>
-      <c r="C84" s="102"/>
+      <c r="B84" s="76"/>
+      <c r="C84" s="101"/>
       <c r="I84" s="52"/>
       <c r="J84" s="52"/>
     </row>
     <row r="85" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B85" s="52"/>
-      <c r="C85" s="102"/>
+      <c r="C85" s="101"/>
       <c r="I85" s="52"/>
       <c r="J85" s="52"/>
     </row>
     <row r="86" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B86" s="52"/>
-      <c r="C86" s="102"/>
+      <c r="C86" s="101"/>
       <c r="I86" s="52"/>
       <c r="J86" s="52"/>
     </row>
     <row r="87" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B87" s="52"/>
-      <c r="C87" s="102"/>
+      <c r="C87" s="101"/>
       <c r="I87" s="52"/>
       <c r="J87" s="52"/>
     </row>
     <row r="88" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B88" s="52"/>
-      <c r="C88" s="102"/>
+      <c r="C88" s="101"/>
       <c r="I88" s="52"/>
       <c r="J88" s="52"/>
     </row>
     <row r="89" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B89" s="52"/>
-      <c r="C89" s="102"/>
+      <c r="C89" s="101"/>
       <c r="I89" s="52"/>
       <c r="J89" s="52"/>
     </row>
     <row r="90" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B90" s="52"/>
-      <c r="C90" s="102"/>
+      <c r="C90" s="101"/>
       <c r="I90" s="52"/>
       <c r="J90" s="52"/>
     </row>
     <row r="91" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B91" s="52"/>
-      <c r="C91" s="102"/>
+      <c r="C91" s="101"/>
       <c r="I91" s="52"/>
       <c r="J91" s="52"/>
     </row>
     <row r="92" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B92" s="52"/>
-      <c r="C92" s="102"/>
+      <c r="C92" s="101"/>
       <c r="I92" s="52"/>
       <c r="J92" s="52"/>
     </row>
     <row r="93" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B93" s="52"/>
-      <c r="C93" s="102"/>
+      <c r="C93" s="101"/>
       <c r="I93" s="52"/>
       <c r="J93" s="52"/>
     </row>
     <row r="94" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B94" s="52"/>
-      <c r="C94" s="102"/>
+      <c r="C94" s="101"/>
       <c r="I94" s="52"/>
       <c r="J94" s="52"/>
     </row>
     <row r="95" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B95" s="52"/>
-      <c r="C95" s="102"/>
+      <c r="C95" s="101"/>
       <c r="I95" s="52"/>
       <c r="J95" s="52"/>
     </row>
     <row r="96" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B96" s="52"/>
-      <c r="C96" s="102"/>
+      <c r="C96" s="101"/>
       <c r="I96" s="52"/>
       <c r="J96" s="52"/>
     </row>
     <row r="97" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B97" s="52"/>
-      <c r="C97" s="102"/>
+      <c r="C97" s="101"/>
       <c r="I97" s="52"/>
       <c r="J97" s="52"/>
     </row>
     <row r="98" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B98" s="52"/>
-      <c r="C98" s="102"/>
+      <c r="C98" s="101"/>
       <c r="I98" s="52"/>
       <c r="J98" s="52"/>
     </row>
     <row r="99" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B99" s="52"/>
-      <c r="C99" s="102"/>
+      <c r="C99" s="101"/>
       <c r="I99" s="52"/>
       <c r="J99" s="52"/>
     </row>
     <row r="100" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B100" s="52"/>
-      <c r="C100" s="102"/>
+      <c r="C100" s="101"/>
       <c r="I100" s="52"/>
       <c r="J100" s="52"/>
     </row>
     <row r="101" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B101" s="52"/>
-      <c r="C101" s="102"/>
+      <c r="C101" s="101"/>
       <c r="I101" s="52"/>
       <c r="J101" s="52"/>
     </row>
     <row r="102" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B102" s="52"/>
-      <c r="C102" s="102"/>
+      <c r="C102" s="101"/>
       <c r="I102" s="52"/>
       <c r="J102" s="52"/>
     </row>
     <row r="103" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B103" s="52"/>
-      <c r="C103" s="102"/>
+      <c r="C103" s="101"/>
       <c r="I103" s="52"/>
       <c r="J103" s="52"/>
     </row>
     <row r="104" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B104" s="52"/>
-      <c r="C104" s="102"/>
+      <c r="C104" s="101"/>
       <c r="I104" s="52"/>
       <c r="J104" s="52"/>
     </row>
     <row r="105" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B105" s="52"/>
-      <c r="C105" s="102"/>
+      <c r="C105" s="101"/>
       <c r="I105" s="52"/>
       <c r="J105" s="52"/>
     </row>
     <row r="106" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B106" s="52"/>
-      <c r="C106" s="102"/>
+      <c r="C106" s="101"/>
       <c r="I106" s="52"/>
       <c r="J106" s="52"/>
     </row>
     <row r="107" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B107" s="52"/>
-      <c r="C107" s="102"/>
+      <c r="C107" s="101"/>
       <c r="I107" s="52"/>
       <c r="J107" s="52"/>
     </row>
     <row r="108" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B108" s="52"/>
-      <c r="C108" s="102"/>
+      <c r="C108" s="101"/>
       <c r="I108" s="52"/>
       <c r="J108" s="52"/>
     </row>
     <row r="109" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B109" s="52"/>
-      <c r="C109" s="102"/>
+      <c r="C109" s="101"/>
       <c r="I109" s="52"/>
       <c r="J109" s="52"/>
     </row>
     <row r="110" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B110" s="52"/>
-      <c r="C110" s="102"/>
+      <c r="C110" s="101"/>
       <c r="I110" s="52"/>
       <c r="J110" s="52"/>
     </row>
     <row r="111" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B111" s="52"/>
-      <c r="C111" s="102"/>
+      <c r="C111" s="101"/>
       <c r="I111" s="52"/>
       <c r="J111" s="52"/>
     </row>
     <row r="112" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B112" s="52"/>
-      <c r="C112" s="102"/>
+      <c r="C112" s="101"/>
       <c r="I112" s="52"/>
       <c r="J112" s="52"/>
     </row>
     <row r="113" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B113" s="52"/>
-      <c r="C113" s="102"/>
+      <c r="C113" s="101"/>
       <c r="I113" s="52"/>
       <c r="J113" s="52"/>
     </row>
     <row r="114" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B114" s="52"/>
-      <c r="C114" s="102"/>
+      <c r="C114" s="101"/>
       <c r="I114" s="52"/>
       <c r="J114" s="52"/>
     </row>
     <row r="115" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B115" s="52"/>
-      <c r="C115" s="102"/>
+      <c r="C115" s="101"/>
       <c r="I115" s="52"/>
       <c r="J115" s="52"/>
     </row>
     <row r="116" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B116" s="52"/>
-      <c r="C116" s="102"/>
+      <c r="C116" s="101"/>
       <c r="I116" s="52"/>
       <c r="J116" s="52"/>
     </row>
     <row r="117" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B117" s="52"/>
-      <c r="C117" s="102"/>
+      <c r="C117" s="101"/>
       <c r="I117" s="52"/>
       <c r="J117" s="52"/>
     </row>
     <row r="118" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B118" s="52"/>
-      <c r="C118" s="102"/>
+      <c r="C118" s="101"/>
       <c r="I118" s="52"/>
       <c r="J118" s="52"/>
     </row>
     <row r="119" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B119" s="52"/>
-      <c r="C119" s="102"/>
+      <c r="C119" s="101"/>
       <c r="I119" s="52"/>
       <c r="J119" s="52"/>
     </row>
     <row r="120" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B120" s="52"/>
-      <c r="C120" s="102"/>
+      <c r="C120" s="101"/>
       <c r="I120" s="52"/>
       <c r="J120" s="52"/>
     </row>
     <row r="121" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B121" s="52"/>
-      <c r="C121" s="102"/>
+      <c r="C121" s="101"/>
       <c r="I121" s="52"/>
       <c r="J121" s="52"/>
     </row>
     <row r="122" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B122" s="52"/>
-      <c r="C122" s="102"/>
+      <c r="C122" s="101"/>
       <c r="I122" s="52"/>
       <c r="J122" s="52"/>
     </row>
     <row r="123" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B123" s="52"/>
-      <c r="C123" s="102"/>
+      <c r="C123" s="101"/>
       <c r="I123" s="52"/>
       <c r="J123" s="52"/>
     </row>
     <row r="124" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B124" s="52"/>
-      <c r="C124" s="102"/>
+      <c r="C124" s="101"/>
       <c r="I124" s="52"/>
       <c r="J124" s="52"/>
     </row>
     <row r="125" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B125" s="52"/>
-      <c r="C125" s="102"/>
+      <c r="C125" s="101"/>
       <c r="I125" s="52"/>
       <c r="J125" s="52"/>
     </row>
     <row r="126" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B126" s="52"/>
-      <c r="C126" s="102"/>
+      <c r="C126" s="101"/>
       <c r="I126" s="52"/>
       <c r="J126" s="52"/>
     </row>
     <row r="127" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B127" s="52"/>
-      <c r="C127" s="102"/>
+      <c r="C127" s="101"/>
       <c r="I127" s="52"/>
       <c r="J127" s="52"/>
     </row>
     <row r="128" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B128" s="52"/>
-      <c r="C128" s="102"/>
+      <c r="C128" s="101"/>
       <c r="I128" s="52"/>
       <c r="J128" s="52"/>
     </row>
     <row r="129" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B129" s="52"/>
-      <c r="C129" s="102"/>
+      <c r="C129" s="101"/>
       <c r="I129" s="52"/>
       <c r="J129" s="52"/>
     </row>
     <row r="130" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B130" s="52"/>
-      <c r="C130" s="102"/>
+      <c r="C130" s="101"/>
       <c r="I130" s="52"/>
       <c r="J130" s="52"/>
     </row>
     <row r="131" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B131" s="52"/>
-      <c r="C131" s="102"/>
+      <c r="C131" s="101"/>
       <c r="I131" s="52"/>
       <c r="J131" s="52"/>
     </row>
     <row r="132" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B132" s="52"/>
-      <c r="C132" s="102"/>
+      <c r="C132" s="101"/>
       <c r="I132" s="52"/>
       <c r="J132" s="52"/>
     </row>
     <row r="133" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B133" s="52"/>
-      <c r="C133" s="102"/>
+      <c r="C133" s="101"/>
       <c r="I133" s="52"/>
       <c r="J133" s="52"/>
     </row>
     <row r="134" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B134" s="52"/>
-      <c r="C134" s="102"/>
+      <c r="C134" s="101"/>
       <c r="I134" s="52"/>
       <c r="J134" s="52"/>
     </row>
     <row r="135" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B135" s="52"/>
-      <c r="C135" s="102"/>
+      <c r="C135" s="101"/>
       <c r="I135" s="52"/>
       <c r="J135" s="52"/>
     </row>
     <row r="136" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B136" s="52"/>
-      <c r="C136" s="102"/>
+      <c r="C136" s="101"/>
       <c r="I136" s="52"/>
       <c r="J136" s="52"/>
     </row>
     <row r="137" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B137" s="52"/>
-      <c r="C137" s="102"/>
+      <c r="C137" s="101"/>
       <c r="I137" s="52"/>
       <c r="J137" s="52"/>
     </row>
     <row r="138" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B138" s="52"/>
-      <c r="C138" s="102"/>
+      <c r="C138" s="101"/>
       <c r="I138" s="52"/>
       <c r="J138" s="52"/>
     </row>
     <row r="139" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B139" s="52"/>
-      <c r="C139" s="102"/>
+      <c r="C139" s="101"/>
       <c r="I139" s="52"/>
       <c r="J139" s="52"/>
     </row>
     <row r="140" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B140" s="52"/>
-      <c r="C140" s="102"/>
+      <c r="C140" s="101"/>
       <c r="I140" s="52"/>
       <c r="J140" s="52"/>
     </row>
     <row r="141" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B141" s="52"/>
-      <c r="C141" s="102"/>
+      <c r="C141" s="101"/>
       <c r="I141" s="52"/>
       <c r="J141" s="52"/>
     </row>
     <row r="142" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B142" s="52"/>
-      <c r="C142" s="102"/>
+      <c r="C142" s="101"/>
       <c r="I142" s="52"/>
       <c r="J142" s="52"/>
     </row>
     <row r="143" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B143" s="52"/>
-      <c r="C143" s="102"/>
+      <c r="C143" s="101"/>
       <c r="I143" s="52"/>
       <c r="J143" s="52"/>
     </row>
     <row r="144" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B144" s="52"/>
-      <c r="C144" s="102"/>
+      <c r="C144" s="101"/>
       <c r="I144" s="52"/>
       <c r="J144" s="52"/>
     </row>
     <row r="145" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B145" s="52"/>
-      <c r="C145" s="102"/>
+      <c r="C145" s="101"/>
       <c r="I145" s="52"/>
       <c r="J145" s="52"/>
     </row>
     <row r="146" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B146" s="52"/>
-      <c r="C146" s="102"/>
+      <c r="C146" s="101"/>
       <c r="I146" s="52"/>
       <c r="J146" s="52"/>
     </row>
     <row r="147" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B147" s="52"/>
-      <c r="C147" s="102"/>
+      <c r="C147" s="101"/>
       <c r="I147" s="52"/>
       <c r="J147" s="52"/>
     </row>
     <row r="148" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B148" s="52"/>
-      <c r="C148" s="102"/>
+      <c r="C148" s="101"/>
       <c r="I148" s="52"/>
       <c r="J148" s="52"/>
     </row>
     <row r="149" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B149" s="52"/>
-      <c r="C149" s="102"/>
+      <c r="C149" s="101"/>
       <c r="I149" s="52"/>
       <c r="J149" s="52"/>
     </row>
     <row r="150" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B150" s="52"/>
-      <c r="C150" s="102"/>
+      <c r="C150" s="101"/>
       <c r="I150" s="52"/>
       <c r="J150" s="52"/>
     </row>
     <row r="151" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B151" s="52"/>
-      <c r="C151" s="102"/>
+      <c r="C151" s="101"/>
       <c r="I151" s="52"/>
       <c r="J151" s="52"/>
     </row>
     <row r="152" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B152" s="52"/>
-      <c r="C152" s="102"/>
+      <c r="C152" s="101"/>
       <c r="I152" s="52"/>
       <c r="J152" s="52"/>
     </row>
     <row r="153" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B153" s="52"/>
-      <c r="C153" s="102"/>
+      <c r="C153" s="101"/>
       <c r="I153" s="52"/>
       <c r="J153" s="52"/>
     </row>
     <row r="154" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B154" s="52"/>
-      <c r="C154" s="102"/>
+      <c r="C154" s="101"/>
       <c r="I154" s="52"/>
       <c r="J154" s="52"/>
     </row>
     <row r="155" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B155" s="52"/>
-      <c r="C155" s="102"/>
+      <c r="C155" s="101"/>
       <c r="I155" s="52"/>
       <c r="J155" s="52"/>
     </row>
     <row r="156" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B156" s="52"/>
-      <c r="C156" s="102"/>
+      <c r="C156" s="101"/>
       <c r="I156" s="52"/>
       <c r="J156" s="52"/>
     </row>
     <row r="157" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B157" s="52"/>
-      <c r="C157" s="102"/>
+      <c r="C157" s="101"/>
       <c r="I157" s="52"/>
       <c r="J157" s="52"/>
     </row>
     <row r="158" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B158" s="52"/>
-      <c r="C158" s="102"/>
+      <c r="C158" s="101"/>
       <c r="I158" s="52"/>
       <c r="J158" s="52"/>
     </row>
     <row r="159" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B159" s="52"/>
-      <c r="C159" s="102"/>
+      <c r="C159" s="101"/>
       <c r="I159" s="52"/>
       <c r="J159" s="52"/>
     </row>
     <row r="160" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B160" s="52"/>
-      <c r="C160" s="102"/>
+      <c r="C160" s="101"/>
       <c r="I160" s="52"/>
       <c r="J160" s="52"/>
     </row>
     <row r="161" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B161" s="52"/>
-      <c r="C161" s="102"/>
+      <c r="C161" s="101"/>
       <c r="I161" s="52"/>
       <c r="J161" s="52"/>
     </row>
     <row r="162" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B162" s="52"/>
-      <c r="C162" s="102"/>
+      <c r="C162" s="101"/>
       <c r="I162" s="52"/>
       <c r="J162" s="52"/>
     </row>
     <row r="163" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B163" s="52"/>
-      <c r="C163" s="102"/>
+      <c r="C163" s="101"/>
       <c r="I163" s="52"/>
       <c r="J163" s="52"/>
     </row>
     <row r="164" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B164" s="52"/>
-      <c r="C164" s="102"/>
+      <c r="C164" s="101"/>
       <c r="I164" s="52"/>
       <c r="J164" s="52"/>
     </row>
     <row r="165" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B165" s="52"/>
-      <c r="C165" s="102"/>
+      <c r="C165" s="101"/>
       <c r="I165" s="52"/>
       <c r="J165" s="52"/>
     </row>
     <row r="166" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B166" s="52"/>
-      <c r="C166" s="102"/>
+      <c r="C166" s="101"/>
       <c r="I166" s="52"/>
       <c r="J166" s="52"/>
     </row>
     <row r="167" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B167" s="52"/>
-      <c r="C167" s="102"/>
+      <c r="C167" s="101"/>
       <c r="I167" s="52"/>
       <c r="J167" s="52"/>
     </row>
     <row r="168" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B168" s="52"/>
-      <c r="C168" s="102"/>
+      <c r="C168" s="101"/>
       <c r="I168" s="52"/>
       <c r="J168" s="52"/>
     </row>
     <row r="169" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B169" s="52"/>
-      <c r="C169" s="102"/>
+      <c r="C169" s="101"/>
       <c r="I169" s="52"/>
       <c r="J169" s="52"/>
     </row>
     <row r="170" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B170" s="52"/>
-      <c r="C170" s="102"/>
+      <c r="C170" s="101"/>
       <c r="I170" s="52"/>
       <c r="J170" s="52"/>
     </row>
     <row r="171" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B171" s="52"/>
-      <c r="C171" s="102"/>
+      <c r="C171" s="101"/>
       <c r="I171" s="52"/>
       <c r="J171" s="52"/>
     </row>
     <row r="172" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B172" s="52"/>
-      <c r="C172" s="102"/>
+      <c r="C172" s="101"/>
       <c r="I172" s="52"/>
       <c r="J172" s="52"/>
     </row>
     <row r="173" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B173" s="52"/>
-      <c r="C173" s="102"/>
+      <c r="C173" s="101"/>
       <c r="I173" s="52"/>
       <c r="J173" s="52"/>
     </row>
     <row r="174" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B174" s="52"/>
-      <c r="C174" s="102"/>
+      <c r="C174" s="101"/>
       <c r="I174" s="52"/>
       <c r="J174" s="52"/>
     </row>
     <row r="175" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B175" s="52"/>
-      <c r="C175" s="102"/>
+      <c r="C175" s="101"/>
       <c r="I175" s="52"/>
       <c r="J175" s="52"/>
     </row>
     <row r="176" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B176" s="52"/>
-      <c r="C176" s="102"/>
+      <c r="C176" s="101"/>
       <c r="I176" s="52"/>
       <c r="J176" s="52"/>
     </row>
     <row r="177" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B177" s="52"/>
-      <c r="C177" s="102"/>
+      <c r="C177" s="101"/>
       <c r="I177" s="52"/>
       <c r="J177" s="52"/>
     </row>
     <row r="178" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B178" s="52"/>
-      <c r="C178" s="102"/>
+      <c r="C178" s="101"/>
       <c r="I178" s="52"/>
       <c r="J178" s="52"/>
     </row>
     <row r="179" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B179" s="52"/>
-      <c r="C179" s="102"/>
+      <c r="C179" s="101"/>
       <c r="I179" s="52"/>
       <c r="J179" s="52"/>
     </row>
     <row r="180" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B180" s="52"/>
-      <c r="C180" s="102"/>
+      <c r="C180" s="101"/>
       <c r="I180" s="52"/>
       <c r="J180" s="52"/>
     </row>
     <row r="181" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B181" s="52"/>
-      <c r="C181" s="102"/>
+      <c r="C181" s="101"/>
       <c r="I181" s="52"/>
       <c r="J181" s="52"/>
     </row>
     <row r="182" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B182" s="52"/>
-      <c r="C182" s="102"/>
+      <c r="C182" s="101"/>
       <c r="I182" s="52"/>
       <c r="J182" s="52"/>
     </row>
     <row r="183" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B183" s="52"/>
-      <c r="C183" s="102"/>
+      <c r="C183" s="101"/>
       <c r="I183" s="52"/>
       <c r="J183" s="52"/>
     </row>
     <row r="184" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B184" s="52"/>
-      <c r="C184" s="102"/>
+      <c r="C184" s="101"/>
       <c r="I184" s="52"/>
       <c r="J184" s="52"/>
     </row>
     <row r="185" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B185" s="52"/>
-      <c r="C185" s="102"/>
+      <c r="C185" s="101"/>
       <c r="I185" s="52"/>
       <c r="J185" s="52"/>
     </row>
     <row r="186" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B186" s="52"/>
-      <c r="C186" s="102"/>
+      <c r="C186" s="101"/>
       <c r="I186" s="52"/>
       <c r="J186" s="52"/>
     </row>
     <row r="187" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B187" s="52"/>
-      <c r="C187" s="102"/>
+      <c r="C187" s="101"/>
       <c r="I187" s="52"/>
       <c r="J187" s="52"/>
     </row>
     <row r="188" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B188" s="52"/>
-      <c r="C188" s="102"/>
+      <c r="C188" s="101"/>
       <c r="I188" s="52"/>
       <c r="J188" s="52"/>
     </row>
     <row r="189" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B189" s="52"/>
-      <c r="C189" s="102"/>
+      <c r="C189" s="101"/>
       <c r="I189" s="52"/>
       <c r="J189" s="52"/>
     </row>
     <row r="190" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B190" s="52"/>
-      <c r="C190" s="102"/>
+      <c r="C190" s="101"/>
       <c r="I190" s="52"/>
       <c r="J190" s="52"/>
     </row>
     <row r="191" spans="2:10" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B191" s="52"/>
-      <c r="C191" s="102"/>
+      <c r="C191" s="101"/>
       <c r="I191" s="52"/>
       <c r="J191" s="52"/>
     </row>
@@ -12431,7 +12434,7 @@
     <col min="8" max="8" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.25" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="79.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.625" style="83" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.625" style="82" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="45.875" style="1"/>
   </cols>
   <sheetData>
@@ -12443,18 +12446,18 @@
       <c r="F1" s="44"/>
     </row>
     <row r="2" spans="2:11" ht="33.75" customHeight="1">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>423</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
     </row>
     <row r="3" spans="2:11" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="45"/>
@@ -12467,10 +12470,10 @@
       <c r="B4" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="87" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="48" t="s">
@@ -12491,1040 +12494,1040 @@
       <c r="J4" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="90" t="s">
+      <c r="K4" s="89" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="5" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B5" s="84">
+      <c r="B5" s="83">
         <v>1</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="78" t="s">
         <v>424</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="78" t="s">
         <v>424</v>
       </c>
-      <c r="E5" s="85"/>
+      <c r="E5" s="84"/>
       <c r="F5" s="58"/>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="78" t="s">
         <v>627</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="H5" s="78" t="s">
         <v>628</v>
       </c>
       <c r="I5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="79" t="s">
+      <c r="J5" s="78" t="s">
         <v>425</v>
       </c>
-      <c r="K5" s="80"/>
+      <c r="K5" s="79"/>
     </row>
     <row r="6" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B6" s="84">
+      <c r="B6" s="83">
         <v>2</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="91" t="s">
         <v>452</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="78" t="s">
         <v>615</v>
       </c>
-      <c r="E6" s="100"/>
+      <c r="E6" s="99"/>
       <c r="F6" s="58"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="78" t="s">
         <v>552</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="78" t="s">
         <v>617</v>
       </c>
-      <c r="I6" s="78" t="s">
+      <c r="I6" s="77" t="s">
         <v>450</v>
       </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="91"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="90"/>
     </row>
     <row r="7" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B7" s="84">
+      <c r="B7" s="83">
         <v>3</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="79" t="s">
+      <c r="C7" s="93"/>
+      <c r="D7" s="78" t="s">
         <v>616</v>
       </c>
-      <c r="E7" s="100"/>
+      <c r="E7" s="99"/>
       <c r="F7" s="58"/>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="78" t="s">
         <v>553</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="78" t="s">
         <v>618</v>
       </c>
-      <c r="I7" s="78" t="s">
+      <c r="I7" s="77" t="s">
         <v>450</v>
       </c>
-      <c r="J7" s="79" t="s">
+      <c r="J7" s="78" t="s">
         <v>451</v>
       </c>
-      <c r="K7" s="91"/>
+      <c r="K7" s="90"/>
     </row>
     <row r="8" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B8" s="84">
+      <c r="B8" s="83">
         <v>4</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="92" t="s">
         <v>426</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="88" t="s">
         <v>565</v>
       </c>
-      <c r="E8" s="123"/>
+      <c r="E8" s="122"/>
       <c r="F8" s="58"/>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="78" t="s">
         <v>568</v>
       </c>
-      <c r="H8" s="79" t="s">
+      <c r="H8" s="78" t="s">
         <v>525</v>
       </c>
       <c r="I8" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="79" t="s">
+      <c r="J8" s="78" t="s">
         <v>555</v>
       </c>
-      <c r="K8" s="80"/>
+      <c r="K8" s="79"/>
     </row>
     <row r="9" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B9" s="84">
+      <c r="B9" s="83">
         <v>5</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="79" t="s">
+      <c r="C9" s="92"/>
+      <c r="D9" s="78" t="s">
         <v>566</v>
       </c>
-      <c r="E9" s="121"/>
+      <c r="E9" s="120"/>
       <c r="F9" s="58"/>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="78" t="s">
         <v>569</v>
       </c>
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="78" t="s">
         <v>526</v>
       </c>
       <c r="I9" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="79" t="s">
+      <c r="J9" s="78" t="s">
         <v>428</v>
       </c>
-      <c r="K9" s="80"/>
+      <c r="K9" s="79"/>
     </row>
     <row r="10" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B10" s="84">
+      <c r="B10" s="83">
         <v>6</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="89" t="s">
+      <c r="C10" s="92"/>
+      <c r="D10" s="88" t="s">
         <v>509</v>
       </c>
-      <c r="E10" s="121"/>
+      <c r="E10" s="120"/>
       <c r="F10" s="58"/>
-      <c r="G10" s="79" t="s">
+      <c r="G10" s="78" t="s">
         <v>567</v>
       </c>
-      <c r="H10" s="79" t="s">
+      <c r="H10" s="78" t="s">
         <v>527</v>
       </c>
       <c r="I10" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="78" t="s">
         <v>556</v>
       </c>
-      <c r="K10" s="80"/>
+      <c r="K10" s="79"/>
     </row>
     <row r="11" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B11" s="84">
+      <c r="B11" s="83">
         <v>7</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="86" t="s">
+      <c r="C11" s="92"/>
+      <c r="D11" s="85" t="s">
         <v>570</v>
       </c>
-      <c r="E11" s="121" t="s">
+      <c r="E11" s="120" t="s">
         <v>571</v>
       </c>
       <c r="F11" s="58"/>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="78" t="s">
         <v>573</v>
       </c>
-      <c r="H11" s="79" t="s">
+      <c r="H11" s="78" t="s">
         <v>528</v>
       </c>
       <c r="I11" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="79"/>
-      <c r="K11" s="80"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="79"/>
     </row>
     <row r="12" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B12" s="84">
+      <c r="B12" s="83">
         <v>8</v>
       </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="121" t="s">
+      <c r="C12" s="92"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="120" t="s">
         <v>572</v>
       </c>
       <c r="F12" s="58"/>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="78" t="s">
         <v>574</v>
       </c>
-      <c r="H12" s="79" t="s">
+      <c r="H12" s="78" t="s">
         <v>529</v>
       </c>
       <c r="I12" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="79" t="s">
+      <c r="J12" s="78" t="s">
         <v>429</v>
       </c>
-      <c r="K12" s="80"/>
+      <c r="K12" s="79"/>
     </row>
     <row r="13" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B13" s="84">
+      <c r="B13" s="83">
         <v>9</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="85" t="s">
         <v>590</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="85" t="s">
         <v>594</v>
       </c>
-      <c r="E13" s="121" t="s">
+      <c r="E13" s="120" t="s">
         <v>592</v>
       </c>
       <c r="F13" s="58"/>
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="78" t="s">
         <v>543</v>
       </c>
-      <c r="H13" s="79" t="s">
+      <c r="H13" s="78" t="s">
         <v>530</v>
       </c>
       <c r="I13" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="79" t="s">
+      <c r="J13" s="78" t="s">
         <v>639</v>
       </c>
-      <c r="K13" s="80"/>
+      <c r="K13" s="79"/>
     </row>
     <row r="14" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B14" s="84">
+      <c r="B14" s="83">
         <v>10</v>
       </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="121" t="s">
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="120" t="s">
         <v>431</v>
       </c>
       <c r="F14" s="58"/>
-      <c r="G14" s="79" t="s">
+      <c r="G14" s="78" t="s">
         <v>544</v>
       </c>
-      <c r="H14" s="79" t="s">
+      <c r="H14" s="78" t="s">
         <v>531</v>
       </c>
-      <c r="I14" s="78" t="s">
+      <c r="I14" s="77" t="s">
         <v>593</v>
       </c>
-      <c r="J14" s="79"/>
-      <c r="K14" s="80"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="79"/>
     </row>
     <row r="15" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B15" s="84">
+      <c r="B15" s="83">
         <v>11</v>
       </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="86" t="s">
+      <c r="C15" s="88"/>
+      <c r="D15" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="121" t="s">
+      <c r="E15" s="120" t="s">
         <v>537</v>
       </c>
       <c r="F15" s="58"/>
-      <c r="G15" s="79" t="s">
+      <c r="G15" s="78" t="s">
         <v>604</v>
       </c>
-      <c r="H15" s="79" t="s">
+      <c r="H15" s="78" t="s">
         <v>532</v>
       </c>
       <c r="I15" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="79" t="s">
+      <c r="J15" s="78" t="s">
         <v>432</v>
       </c>
-      <c r="K15" s="80"/>
+      <c r="K15" s="79"/>
     </row>
     <row r="16" spans="2:11" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B16" s="84">
+      <c r="B16" s="83">
         <v>12</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="91" t="s">
         <v>591</v>
       </c>
-      <c r="D16" s="103" t="s">
+      <c r="D16" s="102" t="s">
         <v>433</v>
       </c>
-      <c r="E16" s="121" t="s">
+      <c r="E16" s="120" t="s">
         <v>595</v>
       </c>
       <c r="F16" s="58"/>
-      <c r="G16" s="79" t="s">
+      <c r="G16" s="78" t="s">
         <v>545</v>
       </c>
-      <c r="H16" s="79" t="s">
+      <c r="H16" s="78" t="s">
         <v>533</v>
       </c>
       <c r="I16" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="79"/>
-      <c r="K16" s="80"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="79"/>
     </row>
     <row r="17" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B17" s="84">
+      <c r="B17" s="83">
         <v>13</v>
       </c>
-      <c r="C17" s="93"/>
-      <c r="D17" s="103" t="s">
+      <c r="C17" s="92"/>
+      <c r="D17" s="102" t="s">
         <v>434</v>
       </c>
-      <c r="E17" s="121" t="s">
+      <c r="E17" s="120" t="s">
         <v>596</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="79" t="s">
+      <c r="G17" s="78" t="s">
         <v>546</v>
       </c>
-      <c r="H17" s="79" t="s">
+      <c r="H17" s="78" t="s">
         <v>534</v>
       </c>
       <c r="I17" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="79"/>
-      <c r="K17" s="80"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="79"/>
     </row>
     <row r="18" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B18" s="84">
+      <c r="B18" s="83">
         <v>14</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="121" t="s">
+      <c r="C18" s="92"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="120" t="s">
         <v>597</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="79" t="s">
+      <c r="G18" s="78" t="s">
         <v>598</v>
       </c>
-      <c r="H18" s="79" t="s">
+      <c r="H18" s="78" t="s">
         <v>535</v>
       </c>
       <c r="I18" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="79" t="s">
+      <c r="J18" s="78" t="s">
         <v>614</v>
       </c>
-      <c r="K18" s="80"/>
+      <c r="K18" s="79"/>
     </row>
     <row r="19" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B19" s="84">
+      <c r="B19" s="83">
         <v>15</v>
       </c>
-      <c r="C19" s="93"/>
-      <c r="D19" s="108" t="s">
+      <c r="C19" s="92"/>
+      <c r="D19" s="107" t="s">
         <v>600</v>
       </c>
-      <c r="E19" s="109" t="s">
+      <c r="E19" s="108" t="s">
         <v>538</v>
       </c>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110" t="s">
+      <c r="F19" s="109"/>
+      <c r="G19" s="109" t="s">
         <v>547</v>
       </c>
-      <c r="H19" s="110"/>
-      <c r="I19" s="111" t="s">
+      <c r="H19" s="109"/>
+      <c r="I19" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="110"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="114" t="s">
+      <c r="J19" s="109"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="20" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B20" s="84">
+      <c r="B20" s="83">
         <v>16</v>
       </c>
-      <c r="C20" s="93"/>
-      <c r="D20" s="113"/>
-      <c r="E20" s="109" t="s">
+      <c r="C20" s="92"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="108" t="s">
         <v>435</v>
       </c>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110" t="s">
+      <c r="F20" s="109"/>
+      <c r="G20" s="109" t="s">
         <v>548</v>
       </c>
-      <c r="H20" s="110"/>
-      <c r="I20" s="111" t="s">
+      <c r="H20" s="109"/>
+      <c r="I20" s="110" t="s">
         <v>430</v>
       </c>
-      <c r="J20" s="110"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="114" t="s">
+      <c r="J20" s="109"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="21" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B21" s="84">
+      <c r="B21" s="83">
         <v>17</v>
       </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="103" t="s">
+      <c r="C21" s="92"/>
+      <c r="D21" s="102" t="s">
         <v>603</v>
       </c>
-      <c r="E21" s="121" t="s">
+      <c r="E21" s="120" t="s">
         <v>601</v>
       </c>
       <c r="F21" s="58"/>
-      <c r="G21" s="79" t="s">
+      <c r="G21" s="78" t="s">
         <v>549</v>
       </c>
-      <c r="H21" s="79" t="s">
+      <c r="H21" s="78" t="s">
         <v>634</v>
       </c>
       <c r="I21" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="79"/>
-      <c r="K21" s="80"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="79"/>
     </row>
     <row r="22" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B22" s="84">
+      <c r="B22" s="83">
         <v>18</v>
       </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="121" t="s">
+      <c r="C22" s="92"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="120" t="s">
         <v>602</v>
       </c>
       <c r="F22" s="58"/>
-      <c r="G22" s="79" t="s">
+      <c r="G22" s="78" t="s">
         <v>550</v>
       </c>
-      <c r="H22" s="79" t="s">
+      <c r="H22" s="78" t="s">
         <v>635</v>
       </c>
-      <c r="I22" s="78" t="s">
+      <c r="I22" s="77" t="s">
         <v>430</v>
       </c>
-      <c r="J22" s="79"/>
-      <c r="K22" s="80"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="79"/>
     </row>
     <row r="23" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="84">
+      <c r="B23" s="83">
         <v>19</v>
       </c>
-      <c r="C23" s="93"/>
-      <c r="D23" s="75" t="s">
+      <c r="C23" s="92"/>
+      <c r="D23" s="74" t="s">
         <v>436</v>
       </c>
-      <c r="E23" s="122" t="s">
+      <c r="E23" s="121" t="s">
         <v>608</v>
       </c>
       <c r="F23" s="58"/>
-      <c r="G23" s="79" t="s">
+      <c r="G23" s="78" t="s">
         <v>611</v>
       </c>
-      <c r="H23" s="79" t="s">
+      <c r="H23" s="78" t="s">
         <v>636</v>
       </c>
       <c r="I23" s="68" t="s">
         <v>454</v>
       </c>
-      <c r="J23" s="79"/>
-      <c r="K23" s="80"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="79"/>
     </row>
     <row r="24" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B24" s="84">
+      <c r="B24" s="83">
         <v>20</v>
       </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="101" t="s">
+      <c r="C24" s="92"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="100" t="s">
         <v>609</v>
       </c>
       <c r="F24" s="58"/>
-      <c r="G24" s="79" t="s">
+      <c r="G24" s="78" t="s">
         <v>612</v>
       </c>
-      <c r="H24" s="79" t="s">
+      <c r="H24" s="78" t="s">
         <v>637</v>
       </c>
       <c r="I24" s="68" t="s">
         <v>454</v>
       </c>
-      <c r="J24" s="79"/>
-      <c r="K24" s="80"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="79"/>
     </row>
     <row r="25" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B25" s="84">
+      <c r="B25" s="83">
         <v>21</v>
       </c>
-      <c r="C25" s="93"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="122" t="s">
+      <c r="C25" s="92"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="121" t="s">
         <v>610</v>
       </c>
       <c r="F25" s="58"/>
-      <c r="G25" s="79" t="s">
+      <c r="G25" s="78" t="s">
         <v>551</v>
       </c>
-      <c r="H25" s="79" t="s">
+      <c r="H25" s="78" t="s">
         <v>638</v>
       </c>
       <c r="I25" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="79" t="s">
+      <c r="J25" s="78" t="s">
         <v>613</v>
       </c>
-      <c r="K25" s="80"/>
+      <c r="K25" s="79"/>
     </row>
     <row r="26" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B26" s="84">
+      <c r="B26" s="83">
         <v>22</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="91" t="s">
         <v>437</v>
       </c>
-      <c r="D26" s="104" t="s">
+      <c r="D26" s="103" t="s">
         <v>510</v>
       </c>
-      <c r="E26" s="121" t="s">
+      <c r="E26" s="120" t="s">
         <v>511</v>
       </c>
       <c r="F26" s="58"/>
-      <c r="G26" s="85" t="s">
+      <c r="G26" s="84" t="s">
         <v>512</v>
       </c>
-      <c r="H26" s="79" t="s">
+      <c r="H26" s="78" t="s">
         <v>523</v>
       </c>
       <c r="I26" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="79" t="s">
+      <c r="J26" s="78" t="s">
         <v>557</v>
       </c>
-      <c r="K26" s="80"/>
+      <c r="K26" s="79"/>
     </row>
     <row r="27" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B27" s="84">
+      <c r="B27" s="83">
         <v>23</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="121" t="s">
+      <c r="C27" s="92"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="120" t="s">
         <v>514</v>
       </c>
       <c r="F27" s="58"/>
-      <c r="G27" s="85" t="s">
+      <c r="G27" s="84" t="s">
         <v>513</v>
       </c>
-      <c r="H27" s="79" t="s">
+      <c r="H27" s="78" t="s">
         <v>524</v>
       </c>
       <c r="I27" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="79"/>
-      <c r="K27" s="80"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="79"/>
     </row>
     <row r="28" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B28" s="84">
+      <c r="B28" s="83">
         <v>24</v>
       </c>
-      <c r="C28" s="93"/>
-      <c r="D28" s="128" t="s">
+      <c r="C28" s="92"/>
+      <c r="D28" s="127" t="s">
         <v>502</v>
       </c>
-      <c r="E28" s="105" t="s">
+      <c r="E28" s="104" t="s">
         <v>503</v>
       </c>
-      <c r="F28" s="106"/>
-      <c r="G28" s="105" t="s">
+      <c r="F28" s="105"/>
+      <c r="G28" s="104" t="s">
         <v>505</v>
       </c>
-      <c r="H28" s="106"/>
-      <c r="I28" s="107" t="s">
+      <c r="H28" s="105"/>
+      <c r="I28" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="106"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="114" t="s">
+      <c r="J28" s="105"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="29" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B29" s="84">
+      <c r="B29" s="83">
         <v>25</v>
       </c>
-      <c r="C29" s="94"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="105" t="s">
+      <c r="C29" s="93"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="104" t="s">
         <v>504</v>
       </c>
-      <c r="F29" s="106"/>
-      <c r="G29" s="105" t="s">
+      <c r="F29" s="105"/>
+      <c r="G29" s="104" t="s">
         <v>554</v>
       </c>
-      <c r="H29" s="106"/>
-      <c r="I29" s="107" t="s">
+      <c r="H29" s="105"/>
+      <c r="I29" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="106" t="s">
+      <c r="J29" s="105" t="s">
         <v>558</v>
       </c>
-      <c r="K29" s="116"/>
-      <c r="L29" s="114" t="s">
+      <c r="K29" s="115"/>
+      <c r="L29" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="30" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B30" s="84">
+      <c r="B30" s="83">
         <v>26</v>
       </c>
-      <c r="C30" s="93" t="s">
+      <c r="C30" s="92" t="s">
         <v>490</v>
       </c>
-      <c r="D30" s="115" t="s">
+      <c r="D30" s="114" t="s">
         <v>491</v>
       </c>
-      <c r="E30" s="105" t="s">
+      <c r="E30" s="104" t="s">
         <v>493</v>
       </c>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106" t="s">
+      <c r="F30" s="105"/>
+      <c r="G30" s="105" t="s">
         <v>494</v>
       </c>
-      <c r="H30" s="106"/>
-      <c r="I30" s="107" t="s">
+      <c r="H30" s="105"/>
+      <c r="I30" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="106"/>
-      <c r="K30" s="116"/>
-      <c r="L30" s="114" t="s">
+      <c r="J30" s="105"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B31" s="84">
+      <c r="B31" s="83">
         <v>27</v>
       </c>
-      <c r="C31" s="93"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="105" t="s">
+      <c r="C31" s="92"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="104" t="s">
         <v>495</v>
       </c>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106" t="s">
+      <c r="F31" s="105"/>
+      <c r="G31" s="105" t="s">
         <v>496</v>
       </c>
-      <c r="H31" s="106"/>
-      <c r="I31" s="107" t="s">
+      <c r="H31" s="105"/>
+      <c r="I31" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="106" t="s">
+      <c r="J31" s="105" t="s">
         <v>559</v>
       </c>
-      <c r="K31" s="116"/>
-      <c r="L31" s="114" t="s">
+      <c r="K31" s="115"/>
+      <c r="L31" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="32" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="84">
+      <c r="B32" s="83">
         <v>28</v>
       </c>
-      <c r="C32" s="119"/>
-      <c r="D32" s="115" t="s">
+      <c r="C32" s="118"/>
+      <c r="D32" s="114" t="s">
         <v>438</v>
       </c>
-      <c r="E32" s="105" t="s">
+      <c r="E32" s="104" t="s">
         <v>619</v>
       </c>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106" t="s">
+      <c r="F32" s="105"/>
+      <c r="G32" s="105" t="s">
         <v>498</v>
       </c>
-      <c r="H32" s="106"/>
-      <c r="I32" s="107" t="s">
+      <c r="H32" s="105"/>
+      <c r="I32" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="106"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="114" t="s">
+      <c r="J32" s="105"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="33" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="84">
+      <c r="B33" s="83">
         <v>29</v>
       </c>
-      <c r="C33" s="119"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="105" t="s">
+      <c r="C33" s="118"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="104" t="s">
         <v>620</v>
       </c>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106" t="s">
+      <c r="F33" s="105"/>
+      <c r="G33" s="105" t="s">
         <v>497</v>
       </c>
-      <c r="H33" s="106"/>
-      <c r="I33" s="107" t="s">
+      <c r="H33" s="105"/>
+      <c r="I33" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="106" t="s">
+      <c r="J33" s="105" t="s">
         <v>564</v>
       </c>
-      <c r="K33" s="116"/>
-      <c r="L33" s="114" t="s">
+      <c r="K33" s="115"/>
+      <c r="L33" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="34" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="84">
+      <c r="B34" s="83">
         <v>30</v>
       </c>
-      <c r="C34" s="119"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="105" t="s">
+      <c r="C34" s="118"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="104" t="s">
         <v>499</v>
       </c>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106" t="s">
+      <c r="F34" s="105"/>
+      <c r="G34" s="105" t="s">
         <v>500</v>
       </c>
-      <c r="H34" s="106"/>
-      <c r="I34" s="107" t="s">
+      <c r="H34" s="105"/>
+      <c r="I34" s="106" t="s">
         <v>430</v>
       </c>
-      <c r="J34" s="106" t="s">
+      <c r="J34" s="105" t="s">
         <v>560</v>
       </c>
-      <c r="K34" s="116"/>
-      <c r="L34" s="114" t="s">
+      <c r="K34" s="115"/>
+      <c r="L34" s="113" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="35" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="84">
+      <c r="B35" s="83">
         <v>31</v>
       </c>
-      <c r="C35" s="94"/>
-      <c r="D35" s="89" t="s">
+      <c r="C35" s="93"/>
+      <c r="D35" s="88" t="s">
         <v>439</v>
       </c>
-      <c r="E35" s="122"/>
+      <c r="E35" s="121"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="79" t="s">
+      <c r="G35" s="78" t="s">
         <v>501</v>
       </c>
-      <c r="H35" s="79" t="s">
+      <c r="H35" s="78" t="s">
         <v>492</v>
       </c>
       <c r="I35" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="79" t="s">
+      <c r="J35" s="78" t="s">
         <v>561</v>
       </c>
-      <c r="K35" s="80"/>
+      <c r="K35" s="79"/>
     </row>
     <row r="36" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B36" s="84">
+      <c r="B36" s="83">
         <v>32</v>
       </c>
-      <c r="C36" s="92" t="s">
+      <c r="C36" s="91" t="s">
         <v>485</v>
       </c>
-      <c r="D36" s="86" t="s">
+      <c r="D36" s="85" t="s">
         <v>486</v>
       </c>
-      <c r="E36" s="122" t="s">
+      <c r="E36" s="121" t="s">
         <v>621</v>
       </c>
       <c r="F36" s="58"/>
-      <c r="G36" s="79" t="s">
+      <c r="G36" s="78" t="s">
         <v>622</v>
       </c>
-      <c r="H36" s="79" t="s">
+      <c r="H36" s="78" t="s">
         <v>487</v>
       </c>
       <c r="I36" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="79"/>
-      <c r="K36" s="80"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="79"/>
     </row>
     <row r="37" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B37" s="84">
+      <c r="B37" s="83">
         <v>33</v>
       </c>
-      <c r="C37" s="94"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="122" t="s">
+      <c r="C37" s="93"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="121" t="s">
         <v>623</v>
       </c>
       <c r="F37" s="58"/>
-      <c r="G37" s="79" t="s">
+      <c r="G37" s="78" t="s">
         <v>624</v>
       </c>
-      <c r="H37" s="79" t="s">
+      <c r="H37" s="78" t="s">
         <v>488</v>
       </c>
       <c r="I37" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="79" t="s">
+      <c r="J37" s="78" t="s">
         <v>489</v>
       </c>
-      <c r="K37" s="80"/>
+      <c r="K37" s="79"/>
     </row>
     <row r="38" spans="2:12" s="60" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B38" s="84">
+      <c r="B38" s="83">
         <v>34</v>
       </c>
-      <c r="C38" s="120" t="s">
+      <c r="C38" s="119" t="s">
         <v>440</v>
       </c>
-      <c r="D38" s="86" t="s">
+      <c r="D38" s="85" t="s">
         <v>441</v>
       </c>
-      <c r="E38" s="122" t="s">
+      <c r="E38" s="121" t="s">
         <v>626</v>
       </c>
       <c r="F38" s="58"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79" t="s">
+      <c r="G38" s="78"/>
+      <c r="H38" s="78" t="s">
         <v>508</v>
       </c>
       <c r="I38" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J38" s="79"/>
-      <c r="K38" s="80"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="79"/>
     </row>
     <row r="39" spans="2:12" s="60" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B39" s="84">
+      <c r="B39" s="83">
         <v>35</v>
       </c>
-      <c r="C39" s="96"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="122" t="s">
+      <c r="C39" s="95"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="121" t="s">
         <v>625</v>
       </c>
       <c r="F39" s="58"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79" t="s">
+      <c r="G39" s="78"/>
+      <c r="H39" s="78" t="s">
         <v>519</v>
       </c>
       <c r="I39" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="79"/>
-      <c r="K39" s="80"/>
+      <c r="J39" s="78"/>
+      <c r="K39" s="79"/>
     </row>
     <row r="40" spans="2:12" s="60" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B40" s="84">
+      <c r="B40" s="83">
         <v>36</v>
       </c>
-      <c r="C40" s="96"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="122" t="s">
+      <c r="C40" s="95"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="121" t="s">
         <v>442</v>
       </c>
       <c r="F40" s="58"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79" t="s">
+      <c r="G40" s="78"/>
+      <c r="H40" s="78" t="s">
         <v>520</v>
       </c>
       <c r="I40" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J40" s="79" t="s">
+      <c r="J40" s="78" t="s">
         <v>443</v>
       </c>
-      <c r="K40" s="80"/>
+      <c r="K40" s="79"/>
     </row>
     <row r="41" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B41" s="84">
+      <c r="B41" s="83">
         <v>37</v>
       </c>
-      <c r="C41" s="96"/>
-      <c r="D41" s="89" t="s">
+      <c r="C41" s="95"/>
+      <c r="D41" s="88" t="s">
         <v>444</v>
       </c>
-      <c r="E41" s="122" t="s">
+      <c r="E41" s="121" t="s">
         <v>427</v>
       </c>
       <c r="F41" s="58"/>
-      <c r="G41" s="85" t="s">
+      <c r="G41" s="84" t="s">
         <v>539</v>
       </c>
-      <c r="H41" s="79" t="s">
+      <c r="H41" s="78" t="s">
         <v>521</v>
       </c>
       <c r="I41" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J41" s="79"/>
-      <c r="K41" s="80"/>
+      <c r="J41" s="78"/>
+      <c r="K41" s="79"/>
     </row>
     <row r="42" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B42" s="84">
+      <c r="B42" s="83">
         <v>38</v>
       </c>
-      <c r="C42" s="97"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="122" t="s">
+      <c r="C42" s="96"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="121" t="s">
         <v>506</v>
       </c>
       <c r="F42" s="58"/>
-      <c r="G42" s="79" t="s">
+      <c r="G42" s="78" t="s">
         <v>507</v>
       </c>
-      <c r="H42" s="79" t="s">
+      <c r="H42" s="78" t="s">
         <v>522</v>
       </c>
       <c r="I42" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="79" t="s">
+      <c r="J42" s="78" t="s">
         <v>562</v>
       </c>
-      <c r="K42" s="80"/>
+      <c r="K42" s="79"/>
     </row>
     <row r="43" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B43" s="84">
+      <c r="B43" s="83">
         <v>39</v>
       </c>
-      <c r="C43" s="124" t="s">
+      <c r="C43" s="123" t="s">
         <v>445</v>
       </c>
-      <c r="D43" s="86" t="s">
+      <c r="D43" s="85" t="s">
         <v>446</v>
       </c>
-      <c r="E43" s="122" t="s">
+      <c r="E43" s="121" t="s">
         <v>540</v>
       </c>
       <c r="F43" s="58"/>
-      <c r="G43" s="79" t="s">
+      <c r="G43" s="78" t="s">
         <v>605</v>
       </c>
-      <c r="H43" s="79" t="s">
+      <c r="H43" s="78" t="s">
         <v>515</v>
       </c>
       <c r="I43" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J43" s="79"/>
-      <c r="K43" s="80"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="79"/>
     </row>
     <row r="44" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B44" s="84">
+      <c r="B44" s="83">
         <v>40</v>
       </c>
-      <c r="C44" s="125"/>
-      <c r="D44" s="87"/>
-      <c r="E44" s="122" t="s">
+      <c r="C44" s="124"/>
+      <c r="D44" s="86"/>
+      <c r="E44" s="121" t="s">
         <v>447</v>
       </c>
       <c r="F44" s="58"/>
-      <c r="G44" s="79" t="s">
+      <c r="G44" s="78" t="s">
         <v>481</v>
       </c>
-      <c r="H44" s="79" t="s">
+      <c r="H44" s="78" t="s">
         <v>516</v>
       </c>
       <c r="I44" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J44" s="79"/>
-      <c r="K44" s="80"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="79"/>
     </row>
     <row r="45" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B45" s="84">
+      <c r="B45" s="83">
         <v>41</v>
       </c>
-      <c r="C45" s="125"/>
-      <c r="D45" s="86" t="s">
+      <c r="C45" s="124"/>
+      <c r="D45" s="85" t="s">
         <v>448</v>
       </c>
-      <c r="E45" s="122" t="s">
+      <c r="E45" s="121" t="s">
         <v>541</v>
       </c>
       <c r="F45" s="58"/>
-      <c r="G45" s="79" t="s">
+      <c r="G45" s="78" t="s">
         <v>542</v>
       </c>
-      <c r="H45" s="79" t="s">
+      <c r="H45" s="78" t="s">
         <v>517</v>
       </c>
       <c r="I45" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="79"/>
-      <c r="K45" s="80"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="79"/>
     </row>
     <row r="46" spans="2:12" s="60" customFormat="1" ht="21" customHeight="1">
-      <c r="B46" s="84">
+      <c r="B46" s="83">
         <v>42</v>
       </c>
-      <c r="C46" s="126"/>
-      <c r="D46" s="87"/>
-      <c r="E46" s="122" t="s">
+      <c r="C46" s="125"/>
+      <c r="D46" s="86"/>
+      <c r="E46" s="121" t="s">
         <v>449</v>
       </c>
       <c r="F46" s="58"/>
-      <c r="G46" s="79" t="s">
+      <c r="G46" s="78" t="s">
         <v>480</v>
       </c>
-      <c r="H46" s="79" t="s">
+      <c r="H46" s="78" t="s">
         <v>518</v>
       </c>
       <c r="I46" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="J46" s="79"/>
-      <c r="K46" s="80"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="79"/>
     </row>
     <row r="47" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B47" s="84">
+      <c r="B47" s="83">
         <v>43</v>
       </c>
-      <c r="C47" s="100" t="s">
+      <c r="C47" s="99" t="s">
         <v>482</v>
       </c>
       <c r="D47" s="58" t="s">
         <v>483</v>
       </c>
-      <c r="E47" s="100"/>
+      <c r="E47" s="99"/>
       <c r="F47" s="58"/>
       <c r="G47" s="58" t="s">
         <v>484</v>
@@ -13532,723 +13535,723 @@
       <c r="H47" s="58" t="s">
         <v>536</v>
       </c>
-      <c r="I47" s="78" t="s">
+      <c r="I47" s="77" t="s">
         <v>430</v>
       </c>
       <c r="J47" s="58" t="s">
         <v>563</v>
       </c>
-      <c r="K47" s="91"/>
+      <c r="K47" s="90"/>
     </row>
     <row r="48" spans="2:12" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="K48" s="81"/>
+      <c r="B48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="K48" s="80"/>
     </row>
     <row r="49" spans="2:11" s="60" customFormat="1" ht="18" customHeight="1">
-      <c r="B49" s="77"/>
-      <c r="I49" s="77"/>
-      <c r="K49" s="81"/>
+      <c r="B49" s="76"/>
+      <c r="I49" s="76"/>
+      <c r="K49" s="80"/>
     </row>
     <row r="50" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
-      <c r="B50" s="77"/>
+      <c r="B50" s="76"/>
       <c r="I50" s="52"/>
-      <c r="K50" s="82"/>
+      <c r="K50" s="81"/>
     </row>
     <row r="51" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B51" s="52"/>
       <c r="I51" s="52"/>
-      <c r="K51" s="82"/>
+      <c r="K51" s="81"/>
     </row>
     <row r="52" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B52" s="52"/>
       <c r="I52" s="52"/>
-      <c r="K52" s="82"/>
+      <c r="K52" s="81"/>
     </row>
     <row r="53" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B53" s="52"/>
       <c r="I53" s="52"/>
-      <c r="K53" s="82"/>
+      <c r="K53" s="81"/>
     </row>
     <row r="54" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B54" s="52"/>
       <c r="I54" s="52"/>
-      <c r="K54" s="82"/>
+      <c r="K54" s="81"/>
     </row>
     <row r="55" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B55" s="52"/>
       <c r="I55" s="52"/>
-      <c r="K55" s="82"/>
+      <c r="K55" s="81"/>
     </row>
     <row r="56" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B56" s="52"/>
       <c r="I56" s="52"/>
-      <c r="K56" s="82"/>
+      <c r="K56" s="81"/>
     </row>
     <row r="57" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B57" s="52"/>
       <c r="I57" s="52"/>
-      <c r="K57" s="82"/>
+      <c r="K57" s="81"/>
     </row>
     <row r="58" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B58" s="52"/>
       <c r="I58" s="52"/>
-      <c r="K58" s="82"/>
+      <c r="K58" s="81"/>
     </row>
     <row r="59" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B59" s="52"/>
       <c r="I59" s="52"/>
-      <c r="K59" s="82"/>
+      <c r="K59" s="81"/>
     </row>
     <row r="60" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B60" s="52"/>
       <c r="I60" s="52"/>
-      <c r="K60" s="82"/>
+      <c r="K60" s="81"/>
     </row>
     <row r="61" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B61" s="52"/>
       <c r="I61" s="52"/>
-      <c r="K61" s="82"/>
+      <c r="K61" s="81"/>
     </row>
     <row r="62" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B62" s="52"/>
       <c r="I62" s="52"/>
-      <c r="K62" s="82"/>
+      <c r="K62" s="81"/>
     </row>
     <row r="63" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B63" s="52"/>
       <c r="I63" s="52"/>
-      <c r="K63" s="82"/>
+      <c r="K63" s="81"/>
     </row>
     <row r="64" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B64" s="52"/>
       <c r="I64" s="52"/>
-      <c r="K64" s="82"/>
+      <c r="K64" s="81"/>
     </row>
     <row r="65" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B65" s="52"/>
       <c r="I65" s="52"/>
-      <c r="K65" s="82"/>
+      <c r="K65" s="81"/>
     </row>
     <row r="66" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B66" s="52"/>
       <c r="I66" s="52"/>
-      <c r="K66" s="82"/>
+      <c r="K66" s="81"/>
     </row>
     <row r="67" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B67" s="52"/>
       <c r="I67" s="52"/>
-      <c r="K67" s="82"/>
+      <c r="K67" s="81"/>
     </row>
     <row r="68" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B68" s="52"/>
       <c r="I68" s="52"/>
-      <c r="K68" s="82"/>
+      <c r="K68" s="81"/>
     </row>
     <row r="69" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B69" s="52"/>
       <c r="I69" s="52"/>
-      <c r="K69" s="82"/>
+      <c r="K69" s="81"/>
     </row>
     <row r="70" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B70" s="52"/>
       <c r="I70" s="52"/>
-      <c r="K70" s="82"/>
+      <c r="K70" s="81"/>
     </row>
     <row r="71" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B71" s="52"/>
       <c r="I71" s="52"/>
-      <c r="K71" s="82"/>
+      <c r="K71" s="81"/>
     </row>
     <row r="72" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B72" s="52"/>
       <c r="I72" s="52"/>
-      <c r="K72" s="82"/>
+      <c r="K72" s="81"/>
     </row>
     <row r="73" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B73" s="52"/>
       <c r="I73" s="52"/>
-      <c r="K73" s="82"/>
+      <c r="K73" s="81"/>
     </row>
     <row r="74" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B74" s="52"/>
       <c r="I74" s="52"/>
-      <c r="K74" s="82"/>
+      <c r="K74" s="81"/>
     </row>
     <row r="75" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B75" s="52"/>
       <c r="I75" s="52"/>
-      <c r="K75" s="82"/>
+      <c r="K75" s="81"/>
     </row>
     <row r="76" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B76" s="52"/>
       <c r="I76" s="52"/>
-      <c r="K76" s="82"/>
+      <c r="K76" s="81"/>
     </row>
     <row r="77" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B77" s="52"/>
       <c r="I77" s="52"/>
-      <c r="K77" s="82"/>
+      <c r="K77" s="81"/>
     </row>
     <row r="78" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B78" s="52"/>
       <c r="I78" s="52"/>
-      <c r="K78" s="82"/>
+      <c r="K78" s="81"/>
     </row>
     <row r="79" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B79" s="52"/>
       <c r="I79" s="52"/>
-      <c r="K79" s="82"/>
+      <c r="K79" s="81"/>
     </row>
     <row r="80" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B80" s="52"/>
       <c r="I80" s="52"/>
-      <c r="K80" s="82"/>
+      <c r="K80" s="81"/>
     </row>
     <row r="81" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B81" s="52"/>
       <c r="I81" s="52"/>
-      <c r="K81" s="82"/>
+      <c r="K81" s="81"/>
     </row>
     <row r="82" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B82" s="52"/>
       <c r="I82" s="52"/>
-      <c r="K82" s="82"/>
+      <c r="K82" s="81"/>
     </row>
     <row r="83" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B83" s="52"/>
       <c r="I83" s="52"/>
-      <c r="K83" s="82"/>
+      <c r="K83" s="81"/>
     </row>
     <row r="84" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B84" s="52"/>
       <c r="I84" s="52"/>
-      <c r="K84" s="82"/>
+      <c r="K84" s="81"/>
     </row>
     <row r="85" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B85" s="52"/>
       <c r="I85" s="52"/>
-      <c r="K85" s="82"/>
+      <c r="K85" s="81"/>
     </row>
     <row r="86" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B86" s="52"/>
       <c r="I86" s="52"/>
-      <c r="K86" s="82"/>
+      <c r="K86" s="81"/>
     </row>
     <row r="87" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B87" s="52"/>
       <c r="I87" s="52"/>
-      <c r="K87" s="82"/>
+      <c r="K87" s="81"/>
     </row>
     <row r="88" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B88" s="52"/>
       <c r="I88" s="52"/>
-      <c r="K88" s="82"/>
+      <c r="K88" s="81"/>
     </row>
     <row r="89" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B89" s="52"/>
       <c r="I89" s="52"/>
-      <c r="K89" s="82"/>
+      <c r="K89" s="81"/>
     </row>
     <row r="90" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B90" s="52"/>
       <c r="I90" s="52"/>
-      <c r="K90" s="82"/>
+      <c r="K90" s="81"/>
     </row>
     <row r="91" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B91" s="52"/>
       <c r="I91" s="52"/>
-      <c r="K91" s="82"/>
+      <c r="K91" s="81"/>
     </row>
     <row r="92" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B92" s="52"/>
       <c r="I92" s="52"/>
-      <c r="K92" s="82"/>
+      <c r="K92" s="81"/>
     </row>
     <row r="93" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B93" s="52"/>
       <c r="I93" s="52"/>
-      <c r="K93" s="82"/>
+      <c r="K93" s="81"/>
     </row>
     <row r="94" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B94" s="52"/>
       <c r="I94" s="52"/>
-      <c r="K94" s="82"/>
+      <c r="K94" s="81"/>
     </row>
     <row r="95" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B95" s="52"/>
       <c r="I95" s="52"/>
-      <c r="K95" s="82"/>
+      <c r="K95" s="81"/>
     </row>
     <row r="96" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B96" s="52"/>
       <c r="I96" s="52"/>
-      <c r="K96" s="82"/>
+      <c r="K96" s="81"/>
     </row>
     <row r="97" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B97" s="52"/>
       <c r="I97" s="52"/>
-      <c r="K97" s="82"/>
+      <c r="K97" s="81"/>
     </row>
     <row r="98" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B98" s="52"/>
       <c r="I98" s="52"/>
-      <c r="K98" s="82"/>
+      <c r="K98" s="81"/>
     </row>
     <row r="99" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B99" s="52"/>
       <c r="I99" s="52"/>
-      <c r="K99" s="82"/>
+      <c r="K99" s="81"/>
     </row>
     <row r="100" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B100" s="52"/>
       <c r="I100" s="52"/>
-      <c r="K100" s="82"/>
+      <c r="K100" s="81"/>
     </row>
     <row r="101" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B101" s="52"/>
       <c r="I101" s="52"/>
-      <c r="K101" s="82"/>
+      <c r="K101" s="81"/>
     </row>
     <row r="102" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B102" s="52"/>
       <c r="I102" s="52"/>
-      <c r="K102" s="82"/>
+      <c r="K102" s="81"/>
     </row>
     <row r="103" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B103" s="52"/>
       <c r="I103" s="52"/>
-      <c r="K103" s="82"/>
+      <c r="K103" s="81"/>
     </row>
     <row r="104" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B104" s="52"/>
       <c r="I104" s="52"/>
-      <c r="K104" s="82"/>
+      <c r="K104" s="81"/>
     </row>
     <row r="105" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B105" s="52"/>
       <c r="I105" s="52"/>
-      <c r="K105" s="82"/>
+      <c r="K105" s="81"/>
     </row>
     <row r="106" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B106" s="52"/>
       <c r="I106" s="52"/>
-      <c r="K106" s="82"/>
+      <c r="K106" s="81"/>
     </row>
     <row r="107" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B107" s="52"/>
       <c r="I107" s="52"/>
-      <c r="K107" s="82"/>
+      <c r="K107" s="81"/>
     </row>
     <row r="108" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B108" s="52"/>
       <c r="I108" s="52"/>
-      <c r="K108" s="82"/>
+      <c r="K108" s="81"/>
     </row>
     <row r="109" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B109" s="52"/>
       <c r="I109" s="52"/>
-      <c r="K109" s="82"/>
+      <c r="K109" s="81"/>
     </row>
     <row r="110" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B110" s="52"/>
       <c r="I110" s="52"/>
-      <c r="K110" s="82"/>
+      <c r="K110" s="81"/>
     </row>
     <row r="111" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B111" s="52"/>
       <c r="I111" s="52"/>
-      <c r="K111" s="82"/>
+      <c r="K111" s="81"/>
     </row>
     <row r="112" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B112" s="52"/>
       <c r="I112" s="52"/>
-      <c r="K112" s="82"/>
+      <c r="K112" s="81"/>
     </row>
     <row r="113" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B113" s="52"/>
       <c r="I113" s="52"/>
-      <c r="K113" s="82"/>
+      <c r="K113" s="81"/>
     </row>
     <row r="114" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B114" s="52"/>
       <c r="I114" s="52"/>
-      <c r="K114" s="82"/>
+      <c r="K114" s="81"/>
     </row>
     <row r="115" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B115" s="52"/>
       <c r="I115" s="52"/>
-      <c r="K115" s="82"/>
+      <c r="K115" s="81"/>
     </row>
     <row r="116" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B116" s="52"/>
       <c r="I116" s="52"/>
-      <c r="K116" s="82"/>
+      <c r="K116" s="81"/>
     </row>
     <row r="117" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B117" s="52"/>
       <c r="I117" s="52"/>
-      <c r="K117" s="82"/>
+      <c r="K117" s="81"/>
     </row>
     <row r="118" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B118" s="52"/>
       <c r="I118" s="52"/>
-      <c r="K118" s="82"/>
+      <c r="K118" s="81"/>
     </row>
     <row r="119" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B119" s="52"/>
       <c r="I119" s="52"/>
-      <c r="K119" s="82"/>
+      <c r="K119" s="81"/>
     </row>
     <row r="120" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B120" s="52"/>
       <c r="I120" s="52"/>
-      <c r="K120" s="82"/>
+      <c r="K120" s="81"/>
     </row>
     <row r="121" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B121" s="52"/>
       <c r="I121" s="52"/>
-      <c r="K121" s="82"/>
+      <c r="K121" s="81"/>
     </row>
     <row r="122" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B122" s="52"/>
       <c r="I122" s="52"/>
-      <c r="K122" s="82"/>
+      <c r="K122" s="81"/>
     </row>
     <row r="123" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B123" s="52"/>
       <c r="I123" s="52"/>
-      <c r="K123" s="82"/>
+      <c r="K123" s="81"/>
     </row>
     <row r="124" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B124" s="52"/>
       <c r="I124" s="52"/>
-      <c r="K124" s="82"/>
+      <c r="K124" s="81"/>
     </row>
     <row r="125" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B125" s="52"/>
       <c r="I125" s="52"/>
-      <c r="K125" s="82"/>
+      <c r="K125" s="81"/>
     </row>
     <row r="126" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B126" s="52"/>
       <c r="I126" s="52"/>
-      <c r="K126" s="82"/>
+      <c r="K126" s="81"/>
     </row>
     <row r="127" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B127" s="52"/>
       <c r="I127" s="52"/>
-      <c r="K127" s="82"/>
+      <c r="K127" s="81"/>
     </row>
     <row r="128" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B128" s="52"/>
       <c r="I128" s="52"/>
-      <c r="K128" s="82"/>
+      <c r="K128" s="81"/>
     </row>
     <row r="129" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B129" s="52"/>
       <c r="I129" s="52"/>
-      <c r="K129" s="82"/>
+      <c r="K129" s="81"/>
     </row>
     <row r="130" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B130" s="52"/>
       <c r="I130" s="52"/>
-      <c r="K130" s="82"/>
+      <c r="K130" s="81"/>
     </row>
     <row r="131" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B131" s="52"/>
       <c r="I131" s="52"/>
-      <c r="K131" s="82"/>
+      <c r="K131" s="81"/>
     </row>
     <row r="132" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B132" s="52"/>
       <c r="I132" s="52"/>
-      <c r="K132" s="82"/>
+      <c r="K132" s="81"/>
     </row>
     <row r="133" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B133" s="52"/>
       <c r="I133" s="52"/>
-      <c r="K133" s="82"/>
+      <c r="K133" s="81"/>
     </row>
     <row r="134" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B134" s="52"/>
       <c r="I134" s="52"/>
-      <c r="K134" s="82"/>
+      <c r="K134" s="81"/>
     </row>
     <row r="135" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B135" s="52"/>
       <c r="I135" s="52"/>
-      <c r="K135" s="82"/>
+      <c r="K135" s="81"/>
     </row>
     <row r="136" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B136" s="52"/>
       <c r="I136" s="52"/>
-      <c r="K136" s="82"/>
+      <c r="K136" s="81"/>
     </row>
     <row r="137" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B137" s="52"/>
       <c r="I137" s="52"/>
-      <c r="K137" s="82"/>
+      <c r="K137" s="81"/>
     </row>
     <row r="138" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B138" s="52"/>
       <c r="I138" s="52"/>
-      <c r="K138" s="82"/>
+      <c r="K138" s="81"/>
     </row>
     <row r="139" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B139" s="52"/>
       <c r="I139" s="52"/>
-      <c r="K139" s="82"/>
+      <c r="K139" s="81"/>
     </row>
     <row r="140" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B140" s="52"/>
       <c r="I140" s="52"/>
-      <c r="K140" s="82"/>
+      <c r="K140" s="81"/>
     </row>
     <row r="141" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B141" s="52"/>
       <c r="I141" s="52"/>
-      <c r="K141" s="82"/>
+      <c r="K141" s="81"/>
     </row>
     <row r="142" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B142" s="52"/>
       <c r="I142" s="52"/>
-      <c r="K142" s="82"/>
+      <c r="K142" s="81"/>
     </row>
     <row r="143" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B143" s="52"/>
       <c r="I143" s="52"/>
-      <c r="K143" s="82"/>
+      <c r="K143" s="81"/>
     </row>
     <row r="144" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B144" s="52"/>
       <c r="I144" s="52"/>
-      <c r="K144" s="82"/>
+      <c r="K144" s="81"/>
     </row>
     <row r="145" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B145" s="52"/>
       <c r="I145" s="52"/>
-      <c r="K145" s="82"/>
+      <c r="K145" s="81"/>
     </row>
     <row r="146" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B146" s="52"/>
       <c r="I146" s="52"/>
-      <c r="K146" s="82"/>
+      <c r="K146" s="81"/>
     </row>
     <row r="147" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B147" s="52"/>
       <c r="I147" s="52"/>
-      <c r="K147" s="82"/>
+      <c r="K147" s="81"/>
     </row>
     <row r="148" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B148" s="52"/>
       <c r="I148" s="52"/>
-      <c r="K148" s="82"/>
+      <c r="K148" s="81"/>
     </row>
     <row r="149" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B149" s="52"/>
       <c r="I149" s="52"/>
-      <c r="K149" s="82"/>
+      <c r="K149" s="81"/>
     </row>
     <row r="150" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B150" s="52"/>
       <c r="I150" s="52"/>
-      <c r="K150" s="82"/>
+      <c r="K150" s="81"/>
     </row>
     <row r="151" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B151" s="52"/>
       <c r="I151" s="52"/>
-      <c r="K151" s="82"/>
+      <c r="K151" s="81"/>
     </row>
     <row r="152" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B152" s="52"/>
       <c r="I152" s="52"/>
-      <c r="K152" s="82"/>
+      <c r="K152" s="81"/>
     </row>
     <row r="153" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B153" s="52"/>
       <c r="I153" s="52"/>
-      <c r="K153" s="82"/>
+      <c r="K153" s="81"/>
     </row>
     <row r="154" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B154" s="52"/>
       <c r="I154" s="52"/>
-      <c r="K154" s="82"/>
+      <c r="K154" s="81"/>
     </row>
     <row r="155" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B155" s="52"/>
       <c r="I155" s="52"/>
-      <c r="K155" s="82"/>
+      <c r="K155" s="81"/>
     </row>
     <row r="156" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B156" s="52"/>
       <c r="I156" s="52"/>
-      <c r="K156" s="82"/>
+      <c r="K156" s="81"/>
     </row>
     <row r="157" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B157" s="52"/>
       <c r="I157" s="52"/>
-      <c r="K157" s="82"/>
+      <c r="K157" s="81"/>
     </row>
     <row r="158" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B158" s="52"/>
       <c r="I158" s="52"/>
-      <c r="K158" s="82"/>
+      <c r="K158" s="81"/>
     </row>
     <row r="159" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B159" s="52"/>
       <c r="I159" s="52"/>
-      <c r="K159" s="82"/>
+      <c r="K159" s="81"/>
     </row>
     <row r="160" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B160" s="52"/>
       <c r="I160" s="52"/>
-      <c r="K160" s="82"/>
+      <c r="K160" s="81"/>
     </row>
     <row r="161" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B161" s="52"/>
       <c r="I161" s="52"/>
-      <c r="K161" s="82"/>
+      <c r="K161" s="81"/>
     </row>
     <row r="162" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B162" s="52"/>
       <c r="I162" s="52"/>
-      <c r="K162" s="82"/>
+      <c r="K162" s="81"/>
     </row>
     <row r="163" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B163" s="52"/>
       <c r="I163" s="52"/>
-      <c r="K163" s="82"/>
+      <c r="K163" s="81"/>
     </row>
     <row r="164" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B164" s="52"/>
       <c r="I164" s="52"/>
-      <c r="K164" s="82"/>
+      <c r="K164" s="81"/>
     </row>
     <row r="165" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B165" s="52"/>
       <c r="I165" s="52"/>
-      <c r="K165" s="82"/>
+      <c r="K165" s="81"/>
     </row>
     <row r="166" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B166" s="52"/>
       <c r="I166" s="52"/>
-      <c r="K166" s="82"/>
+      <c r="K166" s="81"/>
     </row>
     <row r="167" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B167" s="52"/>
       <c r="I167" s="52"/>
-      <c r="K167" s="82"/>
+      <c r="K167" s="81"/>
     </row>
     <row r="168" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B168" s="52"/>
       <c r="I168" s="52"/>
-      <c r="K168" s="82"/>
+      <c r="K168" s="81"/>
     </row>
     <row r="169" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B169" s="52"/>
       <c r="I169" s="52"/>
-      <c r="K169" s="82"/>
+      <c r="K169" s="81"/>
     </row>
     <row r="170" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B170" s="52"/>
       <c r="I170" s="52"/>
-      <c r="K170" s="82"/>
+      <c r="K170" s="81"/>
     </row>
     <row r="171" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B171" s="52"/>
       <c r="I171" s="52"/>
-      <c r="K171" s="82"/>
+      <c r="K171" s="81"/>
     </row>
     <row r="172" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B172" s="52"/>
       <c r="I172" s="52"/>
-      <c r="K172" s="82"/>
+      <c r="K172" s="81"/>
     </row>
     <row r="173" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B173" s="52"/>
       <c r="I173" s="52"/>
-      <c r="K173" s="82"/>
+      <c r="K173" s="81"/>
     </row>
     <row r="174" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B174" s="52"/>
       <c r="I174" s="52"/>
-      <c r="K174" s="82"/>
+      <c r="K174" s="81"/>
     </row>
     <row r="175" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B175" s="52"/>
       <c r="I175" s="52"/>
-      <c r="K175" s="82"/>
+      <c r="K175" s="81"/>
     </row>
     <row r="176" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B176" s="52"/>
       <c r="I176" s="52"/>
-      <c r="K176" s="82"/>
+      <c r="K176" s="81"/>
     </row>
     <row r="177" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B177" s="52"/>
       <c r="I177" s="52"/>
-      <c r="K177" s="82"/>
+      <c r="K177" s="81"/>
     </row>
     <row r="178" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B178" s="52"/>
       <c r="I178" s="52"/>
-      <c r="K178" s="82"/>
+      <c r="K178" s="81"/>
     </row>
     <row r="179" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B179" s="52"/>
       <c r="I179" s="52"/>
-      <c r="K179" s="82"/>
+      <c r="K179" s="81"/>
     </row>
     <row r="180" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B180" s="52"/>
       <c r="I180" s="52"/>
-      <c r="K180" s="82"/>
+      <c r="K180" s="81"/>
     </row>
     <row r="181" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B181" s="52"/>
       <c r="I181" s="52"/>
-      <c r="K181" s="82"/>
+      <c r="K181" s="81"/>
     </row>
     <row r="182" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B182" s="52"/>
       <c r="I182" s="52"/>
-      <c r="K182" s="82"/>
+      <c r="K182" s="81"/>
     </row>
     <row r="183" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B183" s="52"/>
       <c r="I183" s="52"/>
-      <c r="K183" s="82"/>
+      <c r="K183" s="81"/>
     </row>
     <row r="184" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B184" s="52"/>
       <c r="I184" s="52"/>
-      <c r="K184" s="82"/>
+      <c r="K184" s="81"/>
     </row>
     <row r="185" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B185" s="52"/>
       <c r="I185" s="52"/>
-      <c r="K185" s="82"/>
+      <c r="K185" s="81"/>
     </row>
     <row r="186" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B186" s="52"/>
       <c r="I186" s="52"/>
-      <c r="K186" s="82"/>
+      <c r="K186" s="81"/>
     </row>
     <row r="187" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B187" s="52"/>
       <c r="I187" s="52"/>
-      <c r="K187" s="82"/>
+      <c r="K187" s="81"/>
     </row>
     <row r="188" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B188" s="52"/>
       <c r="I188" s="52"/>
-      <c r="K188" s="82"/>
+      <c r="K188" s="81"/>
     </row>
     <row r="189" spans="2:11" s="51" customFormat="1" ht="18" customHeight="1">
       <c r="B189" s="52"/>
       <c r="I189" s="52"/>
-      <c r="K189" s="82"/>
+      <c r="K189" s="81"/>
     </row>
     <row r="190" spans="2:11" ht="0" hidden="1" customHeight="1">
       <c r="B190" s="52"/>
